--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -205,7 +205,6 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -230,13 +229,13 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -606,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -764,19 +763,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>284.01</v>
+        <v>284.45</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>283.63</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>0.0013</v>
+        <v>0.0029</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>45441.6</v>
+        <v>45512</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.08416424385034597</v>
+        <v>0.08364205347195754</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -787,7 +786,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.3359</v>
+        <v>0.3338</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -805,7 +804,7 @@
         </is>
       </c>
       <c r="Q4" s="16" t="n">
-        <v>0.133</v>
+        <v>0.132</v>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
@@ -837,19 +836,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3452</v>
+        <v>3448</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>3427</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0073</v>
+        <v>0.0061</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>41424</v>
+        <v>41376</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.07672308275361633</v>
+        <v>0.07604090359588053</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -860,7 +859,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6869</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -910,19 +909,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>267.48</v>
+        <v>268.46</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>267.18</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.0011</v>
+        <v>0.0048</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>42796.8</v>
+        <v>42953.6</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.07926570171856817</v>
+        <v>0.0789402203377807</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -933,7 +932,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.54</v>
+        <v>0.5344</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -979,19 +978,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2121</v>
+        <v>2146.5</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>2119</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.013</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>42420</v>
+        <v>42930</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.0785678150446216</v>
+        <v>0.07889684820599265</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1002,7 +1001,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.349</v>
+        <v>0.333</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1020,7 +1019,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.289</v>
+        <v>0.286</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1052,19 +1051,19 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>104.78</v>
+        <v>106.39</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>104.58</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0019</v>
+        <v>0.0173</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>28290.6</v>
+        <v>28725.3</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.05239817605613795</v>
+        <v>0.05279141937506639</v>
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
@@ -1075,7 +1074,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.3408</v>
+        <v>0.3205</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1119,19 +1118,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6019</v>
+        <v>6029.5</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>6006</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0022</v>
+        <v>0.0039</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>24076</v>
+        <v>24118</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.04459214321108698</v>
+        <v>0.04432411332476428</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1142,7 +1141,7 @@
         <v>6221.5</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0.0336</v>
+        <v>0.0318</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1192,19 +1191,19 @@
         <v>140</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>154.33</v>
+        <v>154.69</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>153.51</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.0053</v>
+        <v>0.0077</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>21606.2</v>
+        <v>21656.6</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.04001772572883317</v>
+        <v>0.03980054700344515</v>
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
@@ -1215,7 +1214,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.2802</v>
+        <v>0.2772</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1265,19 +1264,19 @@
         <v>24</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1047.8</v>
+        <v>1061</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1053.4</v>
       </c>
-      <c r="H11" s="19" t="n">
-        <v>-0.0053</v>
+      <c r="H11" s="8" t="n">
+        <v>0.0072</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>25147.2</v>
+        <v>25464</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.04657615649434484</v>
+        <v>0.04679779507843924</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1287,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.4316</v>
+        <v>0.4138</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1306,7 +1305,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.195</v>
+        <v>0.192</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1338,19 +1337,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3489.5</v>
+        <v>3530</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>3481</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0024</v>
+        <v>0.0141</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>20937</v>
+        <v>21180</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03877827306905333</v>
+        <v>0.03892465047758966</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1361,7 +1360,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.5643</v>
+        <v>0.5464</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1379,7 +1378,7 @@
         </is>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="R12" s="15" t="inlineStr">
         <is>
@@ -1411,19 +1410,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>114.94</v>
+        <v>115.56</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>114.96</v>
       </c>
-      <c r="H13" s="19" t="n">
-        <v>-0.0002</v>
+      <c r="H13" s="8" t="n">
+        <v>0.0052</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>20689.2</v>
+        <v>20800.8</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.03831931256532733</v>
+        <v>0.03822775588546964</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1434,7 +1433,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3572</v>
+        <v>0.3499</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1480,19 +1479,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1.703</v>
+        <v>1.722</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1.6975</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.0032</v>
+        <v>0.0144</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>20436</v>
+        <v>20664</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03785035050098743</v>
+        <v>0.03797634454527445</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1503,7 +1502,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.2096</v>
+        <v>0.1963</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1521,7 +1520,7 @@
         </is>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
@@ -1553,19 +1552,19 @@
         <v>28</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>567.15</v>
+        <v>573.6</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>571.2</v>
       </c>
-      <c r="H15" s="19" t="n">
-        <v>-0.0071</v>
+      <c r="H15" s="8" t="n">
+        <v>0.0042</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>15880.2</v>
+        <v>16060.8</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.02941236719640735</v>
+        <v>0.0295165734839694</v>
       </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
@@ -1575,8 +1574,8 @@
       <c r="L15" s="7" t="n">
         <v>563.15</v>
       </c>
-      <c r="M15" s="20" t="n">
-        <v>-0.0071</v>
+      <c r="M15" s="19" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1590,7 +1589,7 @@
         </is>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>0.125</v>
+        <v>0.123</v>
       </c>
       <c r="R15" s="15" t="inlineStr">
         <is>
@@ -1622,19 +1621,19 @@
         <v>3</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>5528</v>
+        <v>5603</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>5451</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.0141</v>
+        <v>0.0279</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>16584</v>
+        <v>16809</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.03071590392975022</v>
+        <v>0.03089161708582647</v>
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
@@ -1645,7 +1644,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.1191</v>
+        <v>0.1041</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -1693,19 +1692,19 @@
         <v>26</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>776</v>
+        <v>785.5</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>779</v>
       </c>
-      <c r="H17" s="19" t="n">
-        <v>-0.0039</v>
+      <c r="H17" s="8" t="n">
+        <v>0.0083</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>20176</v>
+        <v>20423</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.03736879387883747</v>
+        <v>0.03753343421642179</v>
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
@@ -1716,7 +1715,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.2023</v>
+        <v>0.1878</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -1734,7 +1733,7 @@
         </is>
       </c>
       <c r="Q17" s="16" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
@@ -1766,19 +1765,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>172.4</v>
+        <v>173</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>172.15</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0015</v>
+        <v>0.0049</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>20688</v>
+        <v>20760</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03831708999630202</v>
+        <v>0.03815277355593774</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -1789,7 +1788,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.4069</v>
+        <v>0.402</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -1807,7 +1806,7 @@
         </is>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>0.203</v>
+        <v>0.202</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -1839,19 +1838,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>62.95</v>
+        <v>63.23</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>62.96</v>
       </c>
-      <c r="H19" s="19" t="n">
-        <v>-0.0002</v>
+      <c r="H19" s="8" t="n">
+        <v>0.0043</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>19766.3</v>
+        <v>19854.22</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.03660997177078038</v>
+        <v>0.03648812908428566</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -1862,7 +1861,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.2708</v>
+        <v>0.2652</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -1905,31 +1904,31 @@
       <c r="E20" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="F20" s="21" t="n">
-        <v>0.6792</v>
-      </c>
-      <c r="G20" s="21" t="n">
+      <c r="F20" s="20" t="n">
+        <v>0.6818</v>
+      </c>
+      <c r="G20" s="20" t="n">
         <v>0.6742</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0074</v>
+        <v>0.0113</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>13584</v>
+        <v>13636</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.02515948136648137</v>
+        <v>0.02506027072296566</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
           <t>Покупать</t>
         </is>
       </c>
-      <c r="L20" s="21" t="n">
+      <c r="L20" s="20" t="n">
         <v>0.7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.0306</v>
+        <v>0.0267</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -1979,19 +1978,19 @@
         <v>160</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>76.26000000000001</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>76.26000000000001</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>12201.6</v>
+        <v>12268.8</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.02259908184932708</v>
+        <v>0.02254762756276922</v>
       </c>
       <c r="K21" s="18" t="inlineStr">
         <is>
@@ -2002,7 +2001,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1576</v>
+        <v>0.1513</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2045,22 +2044,22 @@
       <c r="E22" s="6" t="n">
         <v>370000</v>
       </c>
-      <c r="F22" s="21" t="n">
-        <v>0.05742</v>
-      </c>
-      <c r="G22" s="21" t="n">
+      <c r="F22" s="20" t="n">
+        <v>0.05806</v>
+      </c>
+      <c r="G22" s="20" t="n">
         <v>0.0567</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.0127</v>
+        <v>0.024</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>21245.4</v>
+        <v>21482.2</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.03934947330855737</v>
-      </c>
-      <c r="K22" s="22" t="inlineStr">
+        <v>0.03948003430074016</v>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
         <is>
           <t>нет прогноза</t>
         </is>
@@ -2109,19 +2108,19 @@
         <v>11</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1106.2</v>
+        <v>1142.8</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1093.6</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0115</v>
+        <v>0.045</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>12168.2</v>
+        <v>12570.8</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.02253722034478936</v>
+        <v>0.02310264382548084</v>
       </c>
       <c r="K23" s="18" t="inlineStr">
         <is>
@@ -2132,7 +2131,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.213</v>
+        <v>0.1741</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2150,7 +2149,7 @@
         </is>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>0.11</v>
+        <v>0.107</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -2182,19 +2181,19 @@
         <v>340</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>35.13</v>
+        <v>35.5</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>34.97</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.0046</v>
+        <v>0.0152</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>11944.2</v>
+        <v>12070</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02212234079339861</v>
+        <v>0.02218227248652064</v>
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
@@ -2205,7 +2204,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.2217</v>
+        <v>0.209</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2223,7 +2222,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.151</v>
+        <v>0.149</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2255,19 +2254,19 @@
         <v>363</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>54.845</v>
+        <v>55.025</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>54.6</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>19908.74</v>
+        <v>19974.08</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03687379071408439</v>
+        <v>0.03670840805530756</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2278,7 +2277,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.6328</v>
+        <v>0.6274000000000001</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2296,7 +2295,7 @@
         </is>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>0.177</v>
+        <v>0.176</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -2328,21 +2327,21 @@
         <v>20</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>440.1</v>
+        <v>451.1</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>439.1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0023</v>
+        <v>0.0273</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>8802</v>
+        <v>9022</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.01630254380063082</v>
-      </c>
-      <c r="K26" s="22" t="inlineStr">
+        <v>0.016580651397961</v>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
         <is>
           <t>нет прогноза</t>
         </is>
@@ -2361,7 +2360,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.132</v>
+        <v>0.129</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2397,19 +2396,19 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>43.05</v>
+        <v>43.3</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>43.3</v>
       </c>
-      <c r="H27" s="19" t="n">
-        <v>-0.0058</v>
+      <c r="H27" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7318.5</v>
+        <v>7361</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.01355489284309437</v>
+        <v>0.0135280619530471</v>
       </c>
       <c r="K27" s="18" t="inlineStr">
         <is>
@@ -2419,8 +2418,8 @@
       <c r="L27" s="7" t="n">
         <v>42.5</v>
       </c>
-      <c r="M27" s="20" t="n">
-        <v>-0.0128</v>
+      <c r="M27" s="19" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2464,19 +2463,19 @@
         <v>160</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>39.9</v>
+        <v>40.35</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>39.7</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.005</v>
+        <v>0.0164</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>6384</v>
+        <v>6456</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.01182406721463612</v>
+        <v>0.01186485096710665</v>
       </c>
       <c r="K28" s="18" t="inlineStr">
         <is>
@@ -2487,7 +2486,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.2531</v>
+        <v>0.2392</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2509,37 +2508,37 @@
       <c r="S28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>ИТОГО АКЦИИ (25 позиций)</t>
         </is>
       </c>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
-      <c r="G29" s="24" t="n"/>
-      <c r="H29" s="24" t="n"/>
-      <c r="I29" s="25" t="n">
-        <v>539915.74</v>
-      </c>
-      <c r="J29" s="26" t="n">
-        <v>0.3765140309522331</v>
-      </c>
-      <c r="K29" s="27" t="inlineStr">
-        <is>
-          <t>Срвзв. потенциал: +34.1% · Покупать 13 / Держать 10 / без прогноза 2</t>
-        </is>
-      </c>
-      <c r="L29" s="28" t="n"/>
-      <c r="M29" s="28" t="n"/>
-      <c r="N29" s="28" t="n"/>
-      <c r="O29" s="28" t="n"/>
-      <c r="P29" s="28" t="n"/>
-      <c r="Q29" s="28" t="n"/>
-      <c r="R29" s="28" t="n"/>
-      <c r="S29" s="28" t="n"/>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="23" t="n"/>
+      <c r="I29" s="24" t="n">
+        <v>544128.2</v>
+      </c>
+      <c r="J29" s="25" t="n">
+        <v>0.3783402116274421</v>
+      </c>
+      <c r="K29" s="26" t="inlineStr">
+        <is>
+          <t>Срвзв. потенциал: +33.1% · Покупать 13 / Держать 10 / без прогноза 2</t>
+        </is>
+      </c>
+      <c r="L29" s="27" t="n"/>
+      <c r="M29" s="27" t="n"/>
+      <c r="N29" s="27" t="n"/>
+      <c r="O29" s="27" t="n"/>
+      <c r="P29" s="27" t="n"/>
+      <c r="Q29" s="27" t="n"/>
+      <c r="R29" s="27" t="n"/>
+      <c r="S29" s="27" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2794,33 +2793,33 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>ИТОГО ФОНДЫ (4 позиции)</t>
         </is>
       </c>
-      <c r="B34" s="24" t="n"/>
-      <c r="C34" s="24" t="n"/>
-      <c r="D34" s="24" t="n"/>
-      <c r="E34" s="24" t="n"/>
-      <c r="F34" s="24" t="n"/>
-      <c r="G34" s="24" t="n"/>
-      <c r="H34" s="24" t="n"/>
-      <c r="I34" s="25" t="n">
+      <c r="B34" s="23" t="n"/>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="23" t="n"/>
+      <c r="I34" s="24" t="n">
         <v>714069.97</v>
       </c>
-      <c r="J34" s="26" t="n">
-        <v>0.4979617056295491</v>
-      </c>
-      <c r="K34" s="28" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="28" t="n"/>
-      <c r="N34" s="28" t="n"/>
-      <c r="O34" s="28" t="n"/>
-      <c r="P34" s="28" t="n"/>
-      <c r="Q34" s="28" t="n"/>
-      <c r="R34" s="28" t="n"/>
-      <c r="S34" s="28" t="n"/>
+      <c r="J34" s="25" t="n">
+        <v>0.4965031835633611</v>
+      </c>
+      <c r="K34" s="27" t="n"/>
+      <c r="L34" s="27" t="n"/>
+      <c r="M34" s="27" t="n"/>
+      <c r="N34" s="27" t="n"/>
+      <c r="O34" s="27" t="n"/>
+      <c r="P34" s="27" t="n"/>
+      <c r="Q34" s="27" t="n"/>
+      <c r="R34" s="27" t="n"/>
+      <c r="S34" s="27" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -2849,7 +2848,7 @@
         <v>180000</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.1255242634182177</v>
+        <v>0.1251566048091968</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2882,192 +2881,283 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>ИТОГО CASH</t>
         </is>
       </c>
-      <c r="B36" s="24" t="n"/>
-      <c r="C36" s="24" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="24" t="n"/>
-      <c r="F36" s="24" t="n"/>
-      <c r="G36" s="24" t="n"/>
-      <c r="H36" s="24" t="n"/>
-      <c r="I36" s="25" t="n">
+      <c r="B36" s="23" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="23" t="n"/>
+      <c r="H36" s="23" t="n"/>
+      <c r="I36" s="24" t="n">
         <v>180000</v>
       </c>
-      <c r="J36" s="26" t="n">
-        <v>0.1255242634182177</v>
-      </c>
-      <c r="K36" s="28" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="28" t="n"/>
-      <c r="N36" s="28" t="n"/>
-      <c r="O36" s="28" t="n"/>
-      <c r="P36" s="28" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="28" t="n"/>
-      <c r="S36" s="28" t="n"/>
+      <c r="J36" s="25" t="n">
+        <v>0.1251566048091968</v>
+      </c>
+      <c r="K36" s="27" t="n"/>
+      <c r="L36" s="27" t="n"/>
+      <c r="M36" s="27" t="n"/>
+      <c r="N36" s="27" t="n"/>
+      <c r="O36" s="27" t="n"/>
+      <c r="P36" s="27" t="n"/>
+      <c r="Q36" s="27" t="n"/>
+      <c r="R36" s="27" t="n"/>
+      <c r="S36" s="27" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>ИТОГО ПОРТФЕЛЬ (ликвидная часть)</t>
         </is>
       </c>
-      <c r="B37" s="24" t="n"/>
-      <c r="C37" s="24" t="n"/>
-      <c r="D37" s="24" t="n"/>
-      <c r="E37" s="24" t="n"/>
-      <c r="F37" s="24" t="n"/>
-      <c r="G37" s="24" t="n"/>
-      <c r="H37" s="24" t="n"/>
-      <c r="I37" s="30" t="n">
-        <v>1433985.71</v>
-      </c>
-      <c r="J37" s="31" t="n">
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="23" t="n"/>
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="23" t="n"/>
+      <c r="H37" s="23" t="n"/>
+      <c r="I37" s="29" t="n">
+        <v>1438198.17</v>
+      </c>
+      <c r="J37" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="K37" s="32" t="n"/>
-      <c r="L37" s="32" t="n"/>
-      <c r="M37" s="32" t="n"/>
-      <c r="N37" s="32" t="n"/>
-      <c r="O37" s="33" t="inlineStr">
+      <c r="K37" s="31" t="n"/>
+      <c r="L37" s="31" t="n"/>
+      <c r="M37" s="31" t="n"/>
+      <c r="N37" s="31" t="n"/>
+      <c r="O37" s="32" t="inlineStr">
         <is>
           <t>Ближайших утверждённых отсечек нет</t>
         </is>
       </c>
-      <c r="P37" s="32" t="n"/>
-      <c r="Q37" s="32" t="n"/>
-      <c r="R37" s="32" t="n"/>
-      <c r="S37" s="32" t="n"/>
+      <c r="P37" s="31" t="n"/>
+      <c r="Q37" s="31" t="n"/>
+      <c r="R37" s="31" t="n"/>
+      <c r="S37" s="31" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="34" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Cash (жена)</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Сэйв — пенсионный счёт жены (Яндекс Банк)</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="9" t="n">
+        <v>593000</v>
+      </c>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q38" s="5" t="n"/>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S38" s="17" t="inlineStr">
+        <is>
+          <t>Отдельный блок: не учитывается в долях, потенциале и дивидендных расчётах основного портфеля; входит только в семейный итог. Доходность — по тарифу «Сэйв» её аккаунта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>ВСЕГО СЕМЕЙНЫЙ ПОРТФЕЛЬ (ликвидный)</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="n"/>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="23" t="n"/>
+      <c r="F39" s="23" t="n"/>
+      <c r="G39" s="23" t="n"/>
+      <c r="H39" s="23" t="n"/>
+      <c r="I39" s="29" t="n">
+        <v>2031198.17</v>
+      </c>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="33" t="inlineStr">
+        <is>
+          <t>ваш 1 438 198 ₽ + жены 593 000 ₽</t>
+        </is>
+      </c>
+      <c r="L39" s="31" t="n"/>
+      <c r="M39" s="31" t="n"/>
+      <c r="N39" s="31" t="n"/>
+      <c r="O39" s="31" t="n"/>
+      <c r="P39" s="31" t="n"/>
+      <c r="Q39" s="31" t="n"/>
+      <c r="R39" s="31" t="n"/>
+      <c r="S39" s="31" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>ЗАБЛОКИРОВАННЫЕ АКТИВЫ — справочно, вне ликвидного итога</t>
         </is>
       </c>
-      <c r="B38" s="35" t="n"/>
-      <c r="C38" s="35" t="n"/>
-      <c r="D38" s="35" t="n"/>
-      <c r="E38" s="35" t="n"/>
-      <c r="F38" s="35" t="n"/>
-      <c r="G38" s="35" t="n"/>
-      <c r="H38" s="35" t="n"/>
-      <c r="I38" s="35" t="n"/>
-      <c r="J38" s="35" t="n"/>
-      <c r="K38" s="35" t="n"/>
-      <c r="L38" s="35" t="n"/>
-      <c r="M38" s="35" t="n"/>
-      <c r="N38" s="35" t="n"/>
-      <c r="O38" s="35" t="n"/>
-      <c r="P38" s="35" t="n"/>
-      <c r="Q38" s="35" t="n"/>
-      <c r="R38" s="35" t="n"/>
-      <c r="S38" s="35" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="B40" s="35" t="n"/>
+      <c r="C40" s="35" t="n"/>
+      <c r="D40" s="35" t="n"/>
+      <c r="E40" s="35" t="n"/>
+      <c r="F40" s="35" t="n"/>
+      <c r="G40" s="35" t="n"/>
+      <c r="H40" s="35" t="n"/>
+      <c r="I40" s="35" t="n"/>
+      <c r="J40" s="35" t="n"/>
+      <c r="K40" s="35" t="n"/>
+      <c r="L40" s="35" t="n"/>
+      <c r="M40" s="35" t="n"/>
+      <c r="N40" s="35" t="n"/>
+      <c r="O40" s="35" t="n"/>
+      <c r="P40" s="35" t="n"/>
+      <c r="Q40" s="35" t="n"/>
+      <c r="R40" s="35" t="n"/>
+      <c r="S40" s="35" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Заблокировано</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>BLT · ISIN CA06849F1080</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Barrick Mining (Barrick Gold)</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E41" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F41" s="7" t="n">
         <v>3397.47</v>
       </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="9" t="n">
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="9" t="n">
         <v>20384.83</v>
       </c>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-      <c r="N39" s="5" t="n"/>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q39" s="5" t="n"/>
-      <c r="R39" s="17" t="inlineStr">
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="n"/>
+      <c r="R41" s="17" t="inlineStr">
         <is>
           <t>заблокировано</t>
         </is>
       </c>
-      <c r="S39" s="17" t="inlineStr">
+      <c r="S41" s="17" t="inlineStr">
         <is>
           <t>Заморожен из-за санкционных/инфраструктурных ограничений: продажа и вывод недоступны, дивиденды не поступают. Оценка по цене 40,51 $ и курсу ЦБ 83.8675 ₽/$ (14.10.2026).</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>ИТОГО С УЧЁТОМ ЗАБЛОКИРОВАННЫХ</t>
         </is>
       </c>
-      <c r="B40" s="32" t="n"/>
-      <c r="C40" s="32" t="n"/>
-      <c r="D40" s="32" t="n"/>
-      <c r="E40" s="32" t="n"/>
-      <c r="F40" s="32" t="n"/>
-      <c r="G40" s="32" t="n"/>
-      <c r="H40" s="32" t="n"/>
-      <c r="I40" s="30" t="n">
-        <v>1454370.54</v>
-      </c>
-      <c r="J40" s="36" t="inlineStr">
-        <is>
-          <t>ликвидная часть: 1 433 986 ₽ + заблокировано 20 385 ₽</t>
-        </is>
-      </c>
-      <c r="K40" s="32" t="n"/>
-      <c r="L40" s="32" t="n"/>
-      <c r="M40" s="32" t="n"/>
-      <c r="N40" s="32" t="n"/>
-      <c r="O40" s="32" t="n"/>
-      <c r="P40" s="32" t="n"/>
-      <c r="Q40" s="32" t="n"/>
-      <c r="R40" s="32" t="n"/>
-      <c r="S40" s="32" t="n"/>
+      <c r="B42" s="31" t="n"/>
+      <c r="C42" s="31" t="n"/>
+      <c r="D42" s="31" t="n"/>
+      <c r="E42" s="31" t="n"/>
+      <c r="F42" s="31" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="31" t="n"/>
+      <c r="I42" s="29" t="n">
+        <v>1458583</v>
+      </c>
+      <c r="J42" s="33" t="inlineStr">
+        <is>
+          <t>ликвидная часть: 1 438 198 ₽ + заблокировано 20 385 ₽</t>
+        </is>
+      </c>
+      <c r="K42" s="31" t="n"/>
+      <c r="L42" s="31" t="n"/>
+      <c r="M42" s="31" t="n"/>
+      <c r="N42" s="31" t="n"/>
+      <c r="O42" s="31" t="n"/>
+      <c r="P42" s="31" t="n"/>
+      <c r="Q42" s="31" t="n"/>
+      <c r="R42" s="31" t="n"/>
+      <c r="S42" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A40:S40"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A38:S38"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
@@ -3081,7 +3171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B24"/>
+  <dimension ref="B1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3089,133 +3179,154 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="37" t="inlineStr">
+      <c r="B1" s="36" t="inlineStr">
         <is>
           <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 16.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="38" t="inlineStr">
+      <c r="B2" s="37" t="inlineStr">
         <is>
           <t>• Рекомендации: ПОКУПАТЬ — 13; ДЕРЖАТЬ — 10; ПРОДАВАТЬ — 0; без прогноза — 2 (FEES, PMSB).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="B3" s="38" t="inlineStr">
-        <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +34.1% (без учёта дивидендов).</t>
+      <c r="B3" s="37" t="inlineStr">
+        <is>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +33.1% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>ДИВИДЕНДЫ</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>• Ближайших утверждённых отсечек нет. Выплаты T, GMKN (12.10) и SIBN (13.10) зафиксированы и придут в конце октября — начале ноября.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="38" t="inlineStr">
-        <is>
-          <t>• Дивиденды за 12 месяцев (факт): ≈ 54 925 ₽ — 3.83% годовых на портфель.</t>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>• Дивиденды за 12 месяцев (факт): ≈ 54 925 ₽ — 3.82% годовых на портфель.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>МАКРО И СТРАТЕГИЯ</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>• IMOEX: 2 300–2 500 п. к концу 2026; 2 600–2 900 п. за 12 мес (Т-Инвестиции, 01.08.2026). Ключевая ставка: 14,00% (11.09.2026).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>ФОНДЫ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>• ОПИФ «Флагманский»: пай 916.74 ₽ (14.10.2026); 1 мес +2.85%  1 год +7.51%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>• ОПИФ «Рублевые перспективы»: пай 1 715.32 ₽ (14.10.2026); 1 мес -0.03%  1 год +16.59%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
-      <c r="B15" s="38" t="inlineStr">
-        <is>
-          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.52 ₽ (14.10.2026); 1 мес +1.12%  1 год +15.49%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.52 ₽ (15.10.2026); 1 мес +1.12%  1 год +15.44%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="75" customHeight="1">
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 165.91 ₽ (14.10.2026); 1 мес +1.05%  1 год +14.67%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → позиция 159 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>СЕМЕЙНЫЙ БЛОК (вне расчётов основного портфеля)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>• Сэйв — пенсионный счёт жены (Яндекс Банк): 593 000 ₽. Отдельный блок: не учитывается в долях  потенциале и дивидендных расчётах основного портфеля; входит только в семейный итог. Доходность — по тарифу «Сэйв» её аккаунта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>• Семейный итог (ликвидный): 2 031 198 ₽ = ваш 1 438 198 ₽ + 593 000 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>ЗАБЛОКИРОВАННЫЕ АКТИВЫ</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="B19" s="38" t="inlineStr">
+    <row r="23" ht="45" customHeight="1">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>• Barrick Mining (Barrick Gold): 6 шт × 40.51 $ ≈ 20,385 ₽. Заморожен из-за санкционных/инфраструктурных ограничений: продажа и вывод недоступны, дивиденды не поступают. Оценка по цене 40,51 $ и курсу ЦБ 83.8675 ₽/$ (14.10.2026).</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="38" t="inlineStr">
-        <is>
-          <t>• Итого с учётом заблокированных: 1 454 371 ₽ (ликвидная часть 1 433 986 ₽).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="37" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>• Итого с учётом заблокированных: 1 458 583 ₽ (ликвидная часть 1 438 198 ₽).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>ИСТОЧНИКИ</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="38" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>• tbank.ru/invest (08.10.2026); MOEX ISS (16.10.2026, закрытие 15.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="38" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>⚠️ Материал информационный, не является индивидуальной инвестиционной рекомендацией.</t>
         </is>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -210,6 +210,7 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -763,19 +764,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>284.45</v>
+        <v>287.81</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>283.63</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>0.0029</v>
+        <v>0.0147</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>45512</v>
+        <v>46049.6</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.08364205347195754</v>
+        <v>0.08405419328474358</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -786,7 +787,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.3338</v>
+        <v>0.3182</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -804,7 +805,7 @@
         </is>
       </c>
       <c r="Q4" s="16" t="n">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
@@ -836,19 +837,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3448</v>
+        <v>3474.5</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>3427</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0061</v>
+        <v>0.0139</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>41376</v>
+        <v>41694</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.07604090359588053</v>
+        <v>0.07610392999752655</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -859,7 +860,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.6869</v>
+        <v>0.6740999999999999</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -877,7 +878,7 @@
         </is>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="R5" s="15" t="inlineStr">
         <is>
@@ -909,19 +910,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>268.46</v>
+        <v>269.72</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>267.18</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.0048</v>
+        <v>0.0095</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>42953.6</v>
+        <v>43155.2</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.0789402203377807</v>
+        <v>0.07877105386456702</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -932,7 +933,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.5344</v>
+        <v>0.5273</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -978,19 +979,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2146.5</v>
+        <v>2139</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>2119</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.013</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>42930</v>
+        <v>42780</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.07889684820599265</v>
+        <v>0.07808620245824785</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1001,7 +1002,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.333</v>
+        <v>0.3377000000000001</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1019,7 +1020,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.286</v>
+        <v>0.287</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1051,19 +1052,19 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>106.39</v>
+        <v>107.47</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>104.58</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0173</v>
+        <v>0.0276</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>28725.3</v>
+        <v>29016.9</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.05279141937506639</v>
+        <v>0.05296445834760945</v>
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
@@ -1074,7 +1075,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.3205</v>
+        <v>0.3072</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1118,19 +1119,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6029.5</v>
+        <v>6042</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>6006</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0039</v>
+        <v>0.006</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>24118</v>
+        <v>24168</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.04432411332476428</v>
+        <v>0.04411377608721211</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1141,7 +1142,7 @@
         <v>6221.5</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0.0318</v>
+        <v>0.0297</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1191,19 +1192,19 @@
         <v>140</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>154.69</v>
+        <v>155.4</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>153.51</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.0077</v>
+        <v>0.0123</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>21656.6</v>
+        <v>21756</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.03980054700344515</v>
+        <v>0.03971115990373165</v>
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
@@ -1214,7 +1215,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.2772</v>
+        <v>0.2714</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1232,7 +1233,7 @@
         </is>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>0.127</v>
+        <v>0.126</v>
       </c>
       <c r="R10" s="15" t="inlineStr">
         <is>
@@ -1264,19 +1265,19 @@
         <v>24</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1061</v>
+        <v>1054.8</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1053.4</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0072</v>
+        <v>0.0013</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>25464</v>
+        <v>25315.2</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.04679779507843924</v>
+        <v>0.04620775671975306</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1287,7 +1288,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.4138</v>
+        <v>0.4221</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1305,7 +1306,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.192</v>
+        <v>0.194</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1337,19 +1338,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3530</v>
+        <v>3527</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>3481</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0141</v>
+        <v>0.0132</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>21180</v>
+        <v>21162</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03892465047758966</v>
+        <v>0.03862693353018796</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1360,7 +1361,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.5464</v>
+        <v>0.5477000000000001</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1378,7 +1379,7 @@
         </is>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="R12" s="15" t="inlineStr">
         <is>
@@ -1410,19 +1411,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>115.56</v>
+        <v>115.8</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>114.96</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0052</v>
+        <v>0.0073</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>20800.8</v>
+        <v>20844</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.03822775588546964</v>
+        <v>0.0380464891079878</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1433,7 +1434,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3499</v>
+        <v>0.3472</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1479,19 +1480,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1.722</v>
+        <v>1.724</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1.6975</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.0144</v>
+        <v>0.0156</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>20664</v>
+        <v>20688</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03797634454527445</v>
+        <v>0.03776174278766319</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1502,7 +1503,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1963</v>
+        <v>0.1949</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1552,19 +1553,19 @@
         <v>28</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>573.6</v>
+        <v>575.4</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>571.2</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0042</v>
+        <v>0.0074</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>16060.8</v>
+        <v>16111.2</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.0295165734839694</v>
+        <v>0.02940772382060128</v>
       </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
@@ -1575,7 +1576,7 @@
         <v>563.15</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>-0.0182</v>
+        <v>-0.0213</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1621,19 +1622,19 @@
         <v>3</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>5603</v>
+        <v>5649</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>5451</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.0279</v>
+        <v>0.0363</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>16809</v>
+        <v>16947</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.03089161708582647</v>
+        <v>0.03093330699064811</v>
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
@@ -1644,7 +1645,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.1041</v>
+        <v>0.0951</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -1692,19 +1693,19 @@
         <v>26</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>785.5</v>
+        <v>782</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>779</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0083</v>
+        <v>0.0039</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>20423</v>
+        <v>20332</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.03753343421642179</v>
+        <v>0.03711193708230704</v>
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
@@ -1715,7 +1716,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1878</v>
+        <v>0.1931</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -1733,7 +1734,7 @@
         </is>
       </c>
       <c r="Q17" s="16" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
@@ -1765,19 +1766,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>173</v>
+        <v>174.05</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>172.15</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0049</v>
+        <v>0.011</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>20760</v>
+        <v>20886</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03815277355593774</v>
+        <v>0.03812315157884442</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -1788,7 +1789,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.402</v>
+        <v>0.3936</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -1806,7 +1807,7 @@
         </is>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -1838,19 +1839,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>63.23</v>
+        <v>67.55</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>62.96</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0043</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>19854.22</v>
+        <v>21210.7</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.03648812908428566</v>
+        <v>0.03871582549044314</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -1861,7 +1862,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.2652</v>
+        <v>0.1843</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -1905,19 +1906,19 @@
         <v>20000</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>0.6818</v>
+        <v>0.6796</v>
       </c>
       <c r="G20" s="20" t="n">
         <v>0.6742</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0113</v>
+        <v>0.008</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>13636</v>
+        <v>13592</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.02506027072296566</v>
+        <v>0.02480943580674392</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -1928,7 +1929,7 @@
         <v>0.7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.0267</v>
+        <v>0.03</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -1978,19 +1979,19 @@
         <v>160</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>76.68000000000001</v>
+        <v>77.28</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>76.26000000000001</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0134</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>12268.8</v>
+        <v>12364.8</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.02254762756276922</v>
+        <v>0.02256943142019035</v>
       </c>
       <c r="K21" s="18" t="inlineStr">
         <is>
@@ -2001,7 +2002,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1513</v>
+        <v>0.1423</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2045,19 +2046,19 @@
         <v>370000</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>0.05806</v>
+        <v>0.05854</v>
       </c>
       <c r="G22" s="20" t="n">
         <v>0.0567</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.024</v>
+        <v>0.0325</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>21482.2</v>
+        <v>21659.8</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.03948003430074016</v>
+        <v>0.03953556633953148</v>
       </c>
       <c r="K22" s="21" t="inlineStr">
         <is>
@@ -2108,19 +2109,19 @@
         <v>11</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1142.8</v>
+        <v>1158</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1093.6</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.045</v>
+        <v>0.05889999999999999</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>12570.8</v>
+        <v>12738</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.02310264382548084</v>
+        <v>0.02325063223265921</v>
       </c>
       <c r="K23" s="18" t="inlineStr">
         <is>
@@ -2131,7 +2132,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.1741</v>
+        <v>0.1587</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2149,7 +2150,7 @@
         </is>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -2181,19 +2182,19 @@
         <v>340</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>35.5</v>
+        <v>35.95</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>34.97</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.0152</v>
+        <v>0.028</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>12070</v>
+        <v>12223</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02218227248652064</v>
+        <v>0.02231060431620298</v>
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
@@ -2204,7 +2205,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.209</v>
+        <v>0.1939</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2222,7 +2223,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.149</v>
+        <v>0.147</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2254,19 +2255,19 @@
         <v>363</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>55.025</v>
+        <v>55.225</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>54.6</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0114</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>19974.08</v>
+        <v>20046.67</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03670840805530756</v>
+        <v>0.03659112511065178</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2277,7 +2278,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.6274000000000001</v>
+        <v>0.6214999999999999</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2327,19 +2328,19 @@
         <v>20</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>451.1</v>
+        <v>463.8</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>439.1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0273</v>
+        <v>0.0563</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>9022</v>
+        <v>9276</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.016580651397961</v>
+        <v>0.01693145427776314</v>
       </c>
       <c r="K26" s="21" t="inlineStr">
         <is>
@@ -2360,7 +2361,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.129</v>
+        <v>0.125</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2396,19 +2397,19 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>43.3</v>
       </c>
-      <c r="H27" s="8" t="n">
-        <v>0</v>
+      <c r="H27" s="22" t="n">
+        <v>-0.0023</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7361</v>
+        <v>7344</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.0135280619530471</v>
+        <v>0.0134049806183584</v>
       </c>
       <c r="K27" s="18" t="inlineStr">
         <is>
@@ -2419,7 +2420,7 @@
         <v>42.5</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>-0.0185</v>
+        <v>-0.0162</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2463,19 +2464,19 @@
         <v>160</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>40.35</v>
+        <v>40.6</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>39.7</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0164</v>
+        <v>0.0227</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>6456</v>
+        <v>6496</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.01186485096710665</v>
+        <v>0.01185712882582464</v>
       </c>
       <c r="K28" s="18" t="inlineStr">
         <is>
@@ -2486,7 +2487,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.2392</v>
+        <v>0.2315</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2508,37 +2509,37 @@
       <c r="S28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>ИТОГО АКЦИИ (25 позиций)</t>
         </is>
       </c>
-      <c r="B29" s="23" t="n"/>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="n"/>
-      <c r="F29" s="23" t="n"/>
-      <c r="G29" s="23" t="n"/>
-      <c r="H29" s="23" t="n"/>
-      <c r="I29" s="24" t="n">
-        <v>544128.2</v>
-      </c>
-      <c r="J29" s="25" t="n">
-        <v>0.3783402116274421</v>
-      </c>
-      <c r="K29" s="26" t="inlineStr">
-        <is>
-          <t>Срвзв. потенциал: +33.1% · Покупать 13 / Держать 10 / без прогноза 2</t>
-        </is>
-      </c>
-      <c r="L29" s="27" t="n"/>
-      <c r="M29" s="27" t="n"/>
-      <c r="N29" s="27" t="n"/>
-      <c r="O29" s="27" t="n"/>
-      <c r="P29" s="27" t="n"/>
-      <c r="Q29" s="27" t="n"/>
-      <c r="R29" s="27" t="n"/>
-      <c r="S29" s="27" t="n"/>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
+      <c r="I29" s="25" t="n">
+        <v>547856.0699999999</v>
+      </c>
+      <c r="J29" s="26" t="n">
+        <v>0.3805993359200463</v>
+      </c>
+      <c r="K29" s="27" t="inlineStr">
+        <is>
+          <t>Срвзв. потенциал: +32.3% · Покупать 13 / Держать 10 / без прогноза 2</t>
+        </is>
+      </c>
+      <c r="L29" s="28" t="n"/>
+      <c r="M29" s="28" t="n"/>
+      <c r="N29" s="28" t="n"/>
+      <c r="O29" s="28" t="n"/>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n"/>
+      <c r="R29" s="28" t="n"/>
+      <c r="S29" s="28" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2563,15 +2564,15 @@
         <v>341.3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>916.74</v>
+        <v>908.91</v>
       </c>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="9" t="n">
-        <v>312883.36</v>
+        <v>310210.98</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.4381690494560358</v>
+        <v>0.4359344121527129</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -2626,15 +2627,15 @@
         <v>146.3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1715.32</v>
+        <v>1716.65</v>
       </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="9" t="n">
-        <v>250951.32</v>
+        <v>251145.9</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3514379970355006</v>
+        <v>0.3529312221026607</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -2697,7 +2698,7 @@
         <v>123855.6</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.1734502292541444</v>
+        <v>0.1740522472087273</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -2752,15 +2753,15 @@
         <v>159</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>165.91</v>
+        <v>165.96</v>
       </c>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="9" t="n">
-        <v>26379.69</v>
+        <v>26387.64</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.03694272425431922</v>
+        <v>0.03708211853589907</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2793,33 +2794,33 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>ИТОГО ФОНДЫ (4 позиции)</t>
         </is>
       </c>
-      <c r="B34" s="23" t="n"/>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="23" t="n"/>
-      <c r="F34" s="23" t="n"/>
-      <c r="G34" s="23" t="n"/>
-      <c r="H34" s="23" t="n"/>
-      <c r="I34" s="24" t="n">
-        <v>714069.97</v>
-      </c>
-      <c r="J34" s="25" t="n">
-        <v>0.4965031835633611</v>
-      </c>
-      <c r="K34" s="27" t="n"/>
-      <c r="L34" s="27" t="n"/>
-      <c r="M34" s="27" t="n"/>
-      <c r="N34" s="27" t="n"/>
-      <c r="O34" s="27" t="n"/>
-      <c r="P34" s="27" t="n"/>
-      <c r="Q34" s="27" t="n"/>
-      <c r="R34" s="27" t="n"/>
-      <c r="S34" s="27" t="n"/>
+      <c r="B34" s="24" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="24" t="n"/>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="24" t="n"/>
+      <c r="I34" s="25" t="n">
+        <v>711600.12</v>
+      </c>
+      <c r="J34" s="26" t="n">
+        <v>0.4943534405170052</v>
+      </c>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="28" t="n"/>
+      <c r="M34" s="28" t="n"/>
+      <c r="N34" s="28" t="n"/>
+      <c r="O34" s="28" t="n"/>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n"/>
+      <c r="R34" s="28" t="n"/>
+      <c r="S34" s="28" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -2848,7 +2849,7 @@
         <v>180000</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.1251566048091968</v>
+        <v>0.1250472235629485</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2881,66 +2882,66 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>ИТОГО CASH</t>
         </is>
       </c>
-      <c r="B36" s="23" t="n"/>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="23" t="n"/>
-      <c r="G36" s="23" t="n"/>
-      <c r="H36" s="23" t="n"/>
-      <c r="I36" s="24" t="n">
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="25" t="n">
         <v>180000</v>
       </c>
-      <c r="J36" s="25" t="n">
-        <v>0.1251566048091968</v>
-      </c>
-      <c r="K36" s="27" t="n"/>
-      <c r="L36" s="27" t="n"/>
-      <c r="M36" s="27" t="n"/>
-      <c r="N36" s="27" t="n"/>
-      <c r="O36" s="27" t="n"/>
-      <c r="P36" s="27" t="n"/>
-      <c r="Q36" s="27" t="n"/>
-      <c r="R36" s="27" t="n"/>
-      <c r="S36" s="27" t="n"/>
+      <c r="J36" s="26" t="n">
+        <v>0.1250472235629485</v>
+      </c>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="28" t="n"/>
+      <c r="M36" s="28" t="n"/>
+      <c r="N36" s="28" t="n"/>
+      <c r="O36" s="28" t="n"/>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n"/>
+      <c r="R36" s="28" t="n"/>
+      <c r="S36" s="28" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="28" t="inlineStr">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>ИТОГО ПОРТФЕЛЬ (ликвидная часть)</t>
         </is>
       </c>
-      <c r="B37" s="23" t="n"/>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="23" t="n"/>
-      <c r="F37" s="23" t="n"/>
-      <c r="G37" s="23" t="n"/>
-      <c r="H37" s="23" t="n"/>
-      <c r="I37" s="29" t="n">
-        <v>1438198.17</v>
-      </c>
-      <c r="J37" s="30" t="n">
+      <c r="B37" s="24" t="n"/>
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="24" t="n"/>
+      <c r="E37" s="24" t="n"/>
+      <c r="F37" s="24" t="n"/>
+      <c r="G37" s="24" t="n"/>
+      <c r="H37" s="24" t="n"/>
+      <c r="I37" s="30" t="n">
+        <v>1439456.19</v>
+      </c>
+      <c r="J37" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="K37" s="31" t="n"/>
-      <c r="L37" s="31" t="n"/>
-      <c r="M37" s="31" t="n"/>
-      <c r="N37" s="31" t="n"/>
-      <c r="O37" s="32" t="inlineStr">
+      <c r="K37" s="32" t="n"/>
+      <c r="L37" s="32" t="n"/>
+      <c r="M37" s="32" t="n"/>
+      <c r="N37" s="32" t="n"/>
+      <c r="O37" s="33" t="inlineStr">
         <is>
           <t>Ближайших утверждённых отсечек нет</t>
         </is>
       </c>
-      <c r="P37" s="31" t="n"/>
-      <c r="Q37" s="31" t="n"/>
-      <c r="R37" s="31" t="n"/>
-      <c r="S37" s="31" t="n"/>
+      <c r="P37" s="32" t="n"/>
+      <c r="Q37" s="32" t="n"/>
+      <c r="R37" s="32" t="n"/>
+      <c r="S37" s="32" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3002,60 +3003,60 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="28" t="inlineStr">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>ВСЕГО СЕМЕЙНЫЙ ПОРТФЕЛЬ (ликвидный)</t>
         </is>
       </c>
-      <c r="B39" s="23" t="n"/>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="23" t="n"/>
-      <c r="F39" s="23" t="n"/>
-      <c r="G39" s="23" t="n"/>
-      <c r="H39" s="23" t="n"/>
-      <c r="I39" s="29" t="n">
-        <v>2031198.17</v>
-      </c>
-      <c r="J39" s="30" t="n"/>
-      <c r="K39" s="33" t="inlineStr">
-        <is>
-          <t>ваш 1 438 198 ₽ + жены 593 000 ₽</t>
-        </is>
-      </c>
-      <c r="L39" s="31" t="n"/>
-      <c r="M39" s="31" t="n"/>
-      <c r="N39" s="31" t="n"/>
-      <c r="O39" s="31" t="n"/>
-      <c r="P39" s="31" t="n"/>
-      <c r="Q39" s="31" t="n"/>
-      <c r="R39" s="31" t="n"/>
-      <c r="S39" s="31" t="n"/>
+      <c r="B39" s="24" t="n"/>
+      <c r="C39" s="24" t="n"/>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="24" t="n"/>
+      <c r="G39" s="24" t="n"/>
+      <c r="H39" s="24" t="n"/>
+      <c r="I39" s="30" t="n">
+        <v>2032456.19</v>
+      </c>
+      <c r="J39" s="31" t="n"/>
+      <c r="K39" s="34" t="inlineStr">
+        <is>
+          <t>ваш 1 439 456 ₽ + жены 593 000 ₽</t>
+        </is>
+      </c>
+      <c r="L39" s="32" t="n"/>
+      <c r="M39" s="32" t="n"/>
+      <c r="N39" s="32" t="n"/>
+      <c r="O39" s="32" t="n"/>
+      <c r="P39" s="32" t="n"/>
+      <c r="Q39" s="32" t="n"/>
+      <c r="R39" s="32" t="n"/>
+      <c r="S39" s="32" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="34" t="inlineStr">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>ЗАБЛОКИРОВАННЫЕ АКТИВЫ — справочно, вне ликвидного итога</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n"/>
-      <c r="C40" s="35" t="n"/>
-      <c r="D40" s="35" t="n"/>
-      <c r="E40" s="35" t="n"/>
-      <c r="F40" s="35" t="n"/>
-      <c r="G40" s="35" t="n"/>
-      <c r="H40" s="35" t="n"/>
-      <c r="I40" s="35" t="n"/>
-      <c r="J40" s="35" t="n"/>
-      <c r="K40" s="35" t="n"/>
-      <c r="L40" s="35" t="n"/>
-      <c r="M40" s="35" t="n"/>
-      <c r="N40" s="35" t="n"/>
-      <c r="O40" s="35" t="n"/>
-      <c r="P40" s="35" t="n"/>
-      <c r="Q40" s="35" t="n"/>
-      <c r="R40" s="35" t="n"/>
-      <c r="S40" s="35" t="n"/>
+      <c r="B40" s="36" t="n"/>
+      <c r="C40" s="36" t="n"/>
+      <c r="D40" s="36" t="n"/>
+      <c r="E40" s="36" t="n"/>
+      <c r="F40" s="36" t="n"/>
+      <c r="G40" s="36" t="n"/>
+      <c r="H40" s="36" t="n"/>
+      <c r="I40" s="36" t="n"/>
+      <c r="J40" s="36" t="n"/>
+      <c r="K40" s="36" t="n"/>
+      <c r="L40" s="36" t="n"/>
+      <c r="M40" s="36" t="n"/>
+      <c r="N40" s="36" t="n"/>
+      <c r="O40" s="36" t="n"/>
+      <c r="P40" s="36" t="n"/>
+      <c r="Q40" s="36" t="n"/>
+      <c r="R40" s="36" t="n"/>
+      <c r="S40" s="36" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -3119,35 +3120,35 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>ИТОГО С УЧЁТОМ ЗАБЛОКИРОВАННЫХ</t>
         </is>
       </c>
-      <c r="B42" s="31" t="n"/>
-      <c r="C42" s="31" t="n"/>
-      <c r="D42" s="31" t="n"/>
-      <c r="E42" s="31" t="n"/>
-      <c r="F42" s="31" t="n"/>
-      <c r="G42" s="31" t="n"/>
-      <c r="H42" s="31" t="n"/>
-      <c r="I42" s="29" t="n">
-        <v>1458583</v>
-      </c>
-      <c r="J42" s="33" t="inlineStr">
-        <is>
-          <t>ликвидная часть: 1 438 198 ₽ + заблокировано 20 385 ₽</t>
-        </is>
-      </c>
-      <c r="K42" s="31" t="n"/>
-      <c r="L42" s="31" t="n"/>
-      <c r="M42" s="31" t="n"/>
-      <c r="N42" s="31" t="n"/>
-      <c r="O42" s="31" t="n"/>
-      <c r="P42" s="31" t="n"/>
-      <c r="Q42" s="31" t="n"/>
-      <c r="R42" s="31" t="n"/>
-      <c r="S42" s="31" t="n"/>
+      <c r="B42" s="32" t="n"/>
+      <c r="C42" s="32" t="n"/>
+      <c r="D42" s="32" t="n"/>
+      <c r="E42" s="32" t="n"/>
+      <c r="F42" s="32" t="n"/>
+      <c r="G42" s="32" t="n"/>
+      <c r="H42" s="32" t="n"/>
+      <c r="I42" s="30" t="n">
+        <v>1459841.02</v>
+      </c>
+      <c r="J42" s="34" t="inlineStr">
+        <is>
+          <t>ликвидная часть: 1 439 456 ₽ + заблокировано 20 385 ₽</t>
+        </is>
+      </c>
+      <c r="K42" s="32" t="n"/>
+      <c r="L42" s="32" t="n"/>
+      <c r="M42" s="32" t="n"/>
+      <c r="N42" s="32" t="n"/>
+      <c r="O42" s="32" t="n"/>
+      <c r="P42" s="32" t="n"/>
+      <c r="Q42" s="32" t="n"/>
+      <c r="R42" s="32" t="n"/>
+      <c r="S42" s="32" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3179,154 +3180,154 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="36" t="inlineStr">
+      <c r="B1" s="37" t="inlineStr">
         <is>
           <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 16.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="38" t="inlineStr">
         <is>
           <t>• Рекомендации: ПОКУПАТЬ — 13; ДЕРЖАТЬ — 10; ПРОДАВАТЬ — 0; без прогноза — 2 (FEES, PMSB).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="B3" s="37" t="inlineStr">
-        <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +33.1% (без учёта дивидендов).</t>
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +32.3% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>ДИВИДЕНДЫ</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="38" t="inlineStr">
         <is>
           <t>• Ближайших утверждённых отсечек нет. Выплаты T, GMKN (12.10) и SIBN (13.10) зафиксированы и придут в конце октября — начале ноября.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>• Дивиденды за 12 месяцев (факт): ≈ 54 925 ₽ — 3.82% годовых на портфель.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>МАКРО И СТРАТЕГИЯ</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>• IMOEX: 2 300–2 500 п. к концу 2026; 2 600–2 900 п. за 12 мес (Т-Инвестиции, 01.08.2026). Ключевая ставка: 14,00% (11.09.2026).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>ФОНДЫ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
-      <c r="B13" s="37" t="inlineStr">
-        <is>
-          <t>• ОПИФ «Флагманский»: пай 916.74 ₽ (14.10.2026); 1 мес +2.85%  1 год +7.51%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>• ОПИФ «Флагманский»: пай 908.91 ₽ (15.10.2026); 1 мес +2.47%  1 год +6.19%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>• ОПИФ «Рублевые перспективы»: пай 1 715.32 ₽ (14.10.2026); 1 мес -0.03%  1 год +16.59%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>• ОПИФ «Рублевые перспективы»: пай 1 716.65 ₽ (15.10.2026); 1 мес +0.09%  1 год +16.64%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.52 ₽ (15.10.2026); 1 мес +1.12%  1 год +15.44%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="75" customHeight="1">
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 165.91 ₽ (14.10.2026); 1 мес +1.05%  1 год +14.67%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → позиция 159 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 165.96 ₽ (15.10.2026); 1 мес +1.05%  1 год +14.66%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → позиция 159 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>СЕМЕЙНЫЙ БЛОК (вне расчётов основного портфеля)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>• Сэйв — пенсионный счёт жены (Яндекс Банк): 593 000 ₽. Отдельный блок: не учитывается в долях  потенциале и дивидендных расчётах основного портфеля; входит только в семейный итог. Доходность — по тарифу «Сэйв» её аккаунта.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="37" t="inlineStr">
-        <is>
-          <t>• Семейный итог (ликвидный): 2 031 198 ₽ = ваш 1 438 198 ₽ + 593 000 ₽.</t>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>• Семейный итог (ликвидный): 2 032 456 ₽ = ваш 1 439 456 ₽ + 593 000 ₽.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>ЗАБЛОКИРОВАННЫЕ АКТИВЫ</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t>• Barrick Mining (Barrick Gold): 6 шт × 40.51 $ ≈ 20,385 ₽. Заморожен из-за санкционных/инфраструктурных ограничений: продажа и вывод недоступны, дивиденды не поступают. Оценка по цене 40,51 $ и курсу ЦБ 83.8675 ₽/$ (14.10.2026).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="37" t="inlineStr">
-        <is>
-          <t>• Итого с учётом заблокированных: 1 458 583 ₽ (ликвидная часть 1 438 198 ₽).</t>
+      <c r="B24" s="38" t="inlineStr">
+        <is>
+          <t>• Итого с учётом заблокированных: 1 459 841 ₽ (ликвидная часть 1 439 456 ₽).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>ИСТОЧНИКИ</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B27" s="38" t="inlineStr">
         <is>
           <t>• tbank.ru/invest (08.10.2026); MOEX ISS (16.10.2026, закрытие 15.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>⚠️ Материал информационный, не является индивидуальной инвестиционной рекомендацией.</t>
         </is>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -67,12 +67,12 @@
       <sz val="9"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
       <sz val="10"/>
     </font>
     <font>
@@ -202,15 +202,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -633,14 +633,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 16.10.2026 (автообновление)</t>
+          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 19.10.2026 (автообновление)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (16.10.2026, закрытие 15.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
+          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (19.10.2026, закрытие 16.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Текущая цена, ₽ (16.10.2026)</t>
+          <t>Текущая цена, ₽ (19.10.2026)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Цена за пред. торг. день, ₽ (15.10.2026)</t>
+          <t>Цена за пред. торг. день, ₽ (16.10.2026)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -764,19 +764,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>287.81</v>
+        <v>287.53</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>283.63</v>
+        <v>287.29</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>0.0147</v>
+        <v>0.0008</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>46049.6</v>
+        <v>46004.8</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.08405419328474358</v>
+        <v>0.08357167243511418</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.3182</v>
+        <v>0.3195</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -837,19 +837,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3474.5</v>
+        <v>3435.5</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>3427</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>0.0139</v>
+        <v>3478</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>41694</v>
+        <v>41226</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.07610392999752655</v>
+        <v>0.07489057158839985</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.6740999999999999</v>
+        <v>0.6931</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
       <c r="R5" s="15" t="inlineStr">
         <is>
@@ -910,19 +910,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>269.72</v>
+        <v>270.76</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>267.18</v>
+        <v>269.56</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.0095</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>43155.2</v>
+        <v>43321.6</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.07877105386456702</v>
+        <v>0.07869740906525063</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.5273</v>
+        <v>0.5214</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="R6" s="15" t="inlineStr">
         <is>
@@ -979,19 +979,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2139</v>
+        <v>2153.5</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>2119</v>
+        <v>2145.5</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0037</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>42780</v>
+        <v>43070</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.07808620245824785</v>
+        <v>0.07824035604502938</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.3377000000000001</v>
+        <v>0.3287</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.287</v>
+        <v>0.285</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1052,21 +1052,21 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>107.47</v>
+        <v>108.97</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>104.58</v>
+        <v>108.04</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0086</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>29016.9</v>
+        <v>29421.9</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.05296445834760945</v>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
+        <v>0.05344740960114349</v>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1075,7 +1075,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.3072</v>
+        <v>0.2893</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1119,19 +1119,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6042</v>
+        <v>6031</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>6006</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0.006</v>
+        <v>6051.5</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>24168</v>
+        <v>24124</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.04411377608721211</v>
+        <v>0.0438233189976849</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>6221.5</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0.0297</v>
+        <v>0.0316</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1192,21 +1192,21 @@
         <v>140</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>155.4</v>
+        <v>154.56</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>153.51</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>0.0123</v>
+        <v>155.5</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>-0.006</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>21756</v>
+        <v>21638.4</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.03971115990373165</v>
-      </c>
-      <c r="K10" s="18" t="inlineStr">
+        <v>0.03930801300777255</v>
+      </c>
+      <c r="K10" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1215,7 +1215,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.2714</v>
+        <v>0.2783</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
       <c r="R10" s="15" t="inlineStr">
         <is>
@@ -1265,19 +1265,19 @@
         <v>24</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1054.8</v>
+        <v>1068.6</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1053.4</v>
+        <v>1056</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0013</v>
+        <v>0.0119</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>25315.2</v>
+        <v>25646.4</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.04620775671975306</v>
+        <v>0.0465888894189283</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.4221</v>
+        <v>0.4036999999999999</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.194</v>
+        <v>0.191</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1338,19 +1338,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3527</v>
+        <v>3517.5</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>3481</v>
+        <v>3517.5</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0132</v>
+        <v>0</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>21162</v>
+        <v>21105</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03862693353018796</v>
+        <v>0.03833904607221605</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.5477000000000001</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1411,19 +1411,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>115.8</v>
+        <v>115.46</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>114.96</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>0.0073</v>
+        <v>115.94</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>20844</v>
+        <v>20782.8</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.0380464891079878</v>
+        <v>0.03775374208527134</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3472</v>
+        <v>0.3511</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1480,19 +1480,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1.724</v>
+        <v>1.743</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1.6975</v>
+        <v>1.732</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.0156</v>
+        <v>0.0064</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>20688</v>
+        <v>20916</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03776174278766319</v>
+        <v>0.03799571133127082</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1949</v>
+        <v>0.1819</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>0.108</v>
+        <v>0.107</v>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         <v>28</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>575.4</v>
+        <v>570.4</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>571.2</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>0.0074</v>
+        <v>577.6</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>16111.2</v>
+        <v>15971.2</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.02940772382060128</v>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
+        <v>0.0290130572200226</v>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1575,8 +1575,8 @@
       <c r="L15" s="7" t="n">
         <v>563.15</v>
       </c>
-      <c r="M15" s="19" t="n">
-        <v>-0.0213</v>
+      <c r="M15" s="20" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>0.123</v>
+        <v>0.124</v>
       </c>
       <c r="R15" s="15" t="inlineStr">
         <is>
@@ -1622,21 +1622,21 @@
         <v>3</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>5649</v>
+        <v>5791</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>5451</v>
+        <v>5667</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.0363</v>
+        <v>0.0219</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>16947</v>
+        <v>17373</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.03093330699064811</v>
-      </c>
-      <c r="K16" s="18" t="inlineStr">
+        <v>0.03155954737799618</v>
+      </c>
+      <c r="K16" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1645,7 +1645,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.0951</v>
+        <v>0.0683</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         <v>26</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>782</v>
+        <v>793</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>779</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>0.0039</v>
+        <v>798</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>20332</v>
+        <v>20618</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.03711193708230704</v>
-      </c>
-      <c r="K17" s="18" t="inlineStr">
+        <v>0.03745436872385455</v>
+      </c>
+      <c r="K17" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1716,7 +1716,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1931</v>
+        <v>0.1765</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="Q17" s="16" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
@@ -1766,19 +1766,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>174.05</v>
+        <v>176.25</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>172.15</v>
+        <v>174</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.011</v>
+        <v>0.0129</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>20886</v>
+        <v>21150</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03812315157884442</v>
+        <v>0.03842079243910777</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3936</v>
+        <v>0.3762</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>0.201</v>
+        <v>0.199</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -1839,19 +1839,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>67.55</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>62.96</v>
+        <v>67.37</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0459</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>21210.7</v>
+        <v>22124.44</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.03871582549044314</v>
+        <v>0.04019094643364034</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.1843</v>
+        <v>0.1354</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -1905,31 +1905,31 @@
       <c r="E20" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="F20" s="20" t="n">
-        <v>0.6796</v>
-      </c>
-      <c r="G20" s="20" t="n">
-        <v>0.6742</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>0.008</v>
+      <c r="F20" s="21" t="n">
+        <v>0.6784</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>0.6806</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>-0.0032</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>13592</v>
+        <v>13568</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.02480943580674392</v>
+        <v>0.02464743791081863</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
           <t>Покупать</t>
         </is>
       </c>
-      <c r="L20" s="20" t="n">
+      <c r="L20" s="21" t="n">
         <v>0.7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.03</v>
+        <v>0.0318</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
         <v>160</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>77.28</v>
+        <v>76.86</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>76.26000000000001</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>0.0134</v>
+        <v>77.59999999999999</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>12364.8</v>
+        <v>12297.6</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.02256943142019035</v>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
+        <v>0.02233964714416887</v>
+      </c>
+      <c r="K21" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2002,7 +2002,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1423</v>
+        <v>0.1486</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2045,22 +2045,22 @@
       <c r="E22" s="6" t="n">
         <v>370000</v>
       </c>
-      <c r="F22" s="20" t="n">
-        <v>0.05854</v>
-      </c>
-      <c r="G22" s="20" t="n">
-        <v>0.0567</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>0.0325</v>
+      <c r="F22" s="21" t="n">
+        <v>0.05786</v>
+      </c>
+      <c r="G22" s="21" t="n">
+        <v>0.05804</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>-0.0031</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>21659.8</v>
+        <v>21408.2</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.03953556633953148</v>
-      </c>
-      <c r="K22" s="21" t="inlineStr">
+        <v>0.03888983492647314</v>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>нет прогноза</t>
         </is>
@@ -2109,21 +2109,21 @@
         <v>11</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1158</v>
+        <v>1161.4</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1093.6</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>0.05889999999999999</v>
+        <v>1165</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>-0.0031</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>12738</v>
+        <v>12775.4</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.02325063223265921</v>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
+        <v>0.02320761190196583</v>
+      </c>
+      <c r="K23" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2132,7 +2132,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.1587</v>
+        <v>0.1553</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2182,21 +2182,21 @@
         <v>340</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>35.95</v>
+        <v>35.86</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>34.97</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>0.028</v>
+        <v>36.11</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>12223</v>
+        <v>12192.4</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02231060431620298</v>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
+        <v>0.02214854230423534</v>
+      </c>
+      <c r="K24" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2205,7 +2205,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.1939</v>
+        <v>0.1969</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.147</v>
+        <v>0.148</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2255,19 +2255,19 @@
         <v>363</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>55.225</v>
+        <v>56.08</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>54.6</v>
+        <v>55.445</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0114</v>
+        <v>0.0115</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>20046.67</v>
+        <v>20357.04</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03659112511065178</v>
+        <v>0.03698031245931983</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.6214999999999999</v>
+        <v>0.5968</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>0.176</v>
+        <v>0.173</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         <v>20</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>463.8</v>
+        <v>473.8</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>439.1</v>
+        <v>459.8</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0563</v>
+        <v>0.0304</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>9276</v>
+        <v>9476</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.01693145427776314</v>
-      </c>
-      <c r="K26" s="21" t="inlineStr">
+        <v>0.01721396828146502</v>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
         <is>
           <t>нет прогноза</t>
         </is>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.125</v>
+        <v>0.122</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2397,21 +2397,21 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>43.2</v>
+        <v>43.5</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="H27" s="22" t="n">
-        <v>-0.0023</v>
+        <v>43.35</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0.0035</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7344</v>
+        <v>7395</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.0134049806183584</v>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
+        <v>0.01343365295920576</v>
+      </c>
+      <c r="K27" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2419,8 +2419,8 @@
       <c r="L27" s="7" t="n">
         <v>42.5</v>
       </c>
-      <c r="M27" s="19" t="n">
-        <v>-0.0162</v>
+      <c r="M27" s="20" t="n">
+        <v>-0.023</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2464,21 +2464,21 @@
         <v>160</v>
       </c>
       <c r="F28" s="7" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G28" s="7" t="n">
         <v>40.6</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>39.7</v>
-      </c>
       <c r="H28" s="8" t="n">
-        <v>0.0227</v>
+        <v>0.0037</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>6496</v>
+        <v>6520</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.01185712882582464</v>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
+        <v>0.01184414026964457</v>
+      </c>
+      <c r="K28" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2487,7 +2487,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.2315</v>
+        <v>0.227</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2522,14 +2522,14 @@
       <c r="G29" s="24" t="n"/>
       <c r="H29" s="24" t="n"/>
       <c r="I29" s="25" t="n">
-        <v>547856.0699999999</v>
+        <v>550483.1800000001</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>0.3805993359200463</v>
+        <v>0.3808813343063437</v>
       </c>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>Срвзв. потенциал: +32.3% · Покупать 13 / Держать 10 / без прогноза 2</t>
+          <t>Срвзв. потенциал: +31.6% · Покупать 13 / Держать 10 / без прогноза 2</t>
         </is>
       </c>
       <c r="L29" s="28" t="n"/>
@@ -2564,15 +2564,15 @@
         <v>341.3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>908.91</v>
+        <v>917.61</v>
       </c>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="9" t="n">
-        <v>310210.98</v>
+        <v>313180.29</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.4359344121527129</v>
+        <v>0.4381340604205028</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -2627,15 +2627,15 @@
         <v>146.3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1716.65</v>
+        <v>1717.61</v>
       </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="9" t="n">
-        <v>251145.9</v>
+        <v>251286.34</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3529312221026607</v>
+        <v>0.3515454451887985</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -2690,15 +2690,15 @@
         <v>8530</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>14.52</v>
+        <v>14.53</v>
       </c>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="9" t="n">
-        <v>123855.6</v>
+        <v>123940.9</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.1740522472087273</v>
+        <v>0.1733912749399763</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -2753,15 +2753,15 @@
         <v>159</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>165.96</v>
+        <v>166.02</v>
       </c>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="9" t="n">
-        <v>26387.64</v>
+        <v>26397.18</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.03708211853589907</v>
+        <v>0.03692921945072242</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
       <c r="G34" s="24" t="n"/>
       <c r="H34" s="24" t="n"/>
       <c r="I34" s="25" t="n">
-        <v>711600.12</v>
+        <v>714804.71</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>0.4943534405170052</v>
+        <v>0.4945760045080015</v>
       </c>
       <c r="K34" s="28" t="n"/>
       <c r="L34" s="28" t="n"/>
@@ -2849,7 +2849,7 @@
         <v>180000</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.1250472235629485</v>
+        <v>0.1245426611856549</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>180000</v>
       </c>
       <c r="J36" s="26" t="n">
-        <v>0.1250472235629485</v>
+        <v>0.1245426611856549</v>
       </c>
       <c r="K36" s="28" t="n"/>
       <c r="L36" s="28" t="n"/>
@@ -2924,7 +2924,7 @@
       <c r="G37" s="24" t="n"/>
       <c r="H37" s="24" t="n"/>
       <c r="I37" s="30" t="n">
-        <v>1439456.19</v>
+        <v>1445287.89</v>
       </c>
       <c r="J37" s="31" t="n">
         <v>1</v>
@@ -2969,7 +2969,7 @@
       <c r="G38" s="5" t="n"/>
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="9" t="n">
-        <v>593000</v>
+        <v>605000</v>
       </c>
       <c r="J38" s="5" t="n"/>
       <c r="K38" s="5" t="inlineStr">
@@ -3016,12 +3016,12 @@
       <c r="G39" s="24" t="n"/>
       <c r="H39" s="24" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>2032456.19</v>
+        <v>2050287.89</v>
       </c>
       <c r="J39" s="31" t="n"/>
       <c r="K39" s="34" t="inlineStr">
         <is>
-          <t>ваш 1 439 456 ₽ + жены 593 000 ₽</t>
+          <t>ваш 1 445 288 ₽ + жены 605 000 ₽</t>
         </is>
       </c>
       <c r="L39" s="32" t="n"/>
@@ -3133,11 +3133,11 @@
       <c r="G42" s="32" t="n"/>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="30" t="n">
-        <v>1459841.02</v>
+        <v>1465672.72</v>
       </c>
       <c r="J42" s="34" t="inlineStr">
         <is>
-          <t>ликвидная часть: 1 439 456 ₽ + заблокировано 20 385 ₽</t>
+          <t>ликвидная часть: 1 445 288 ₽ + заблокировано 20 385 ₽</t>
         </is>
       </c>
       <c r="K42" s="32" t="n"/>
@@ -3182,7 +3182,7 @@
     <row r="1">
       <c r="B1" s="37" t="inlineStr">
         <is>
-          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 16.10.2026 (АВТООБНОВЛЕНИЕ)</t>
+          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 19.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +32.3% (без учёта дивидендов).</t>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +31.6% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="38" t="inlineStr">
         <is>
-          <t>• Дивиденды за 12 месяцев (факт): ≈ 54 925 ₽ — 3.82% годовых на портфель.</t>
+          <t>• Дивиденды за 12 месяцев (факт): ≈ 54 925 ₽ — 3.8% годовых на портфель.</t>
         </is>
       </c>
     </row>
@@ -3245,28 +3245,28 @@
     <row r="13" ht="45" customHeight="1">
       <c r="B13" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Флагманский»: пай 908.91 ₽ (15.10.2026); 1 мес +2.47%  1 год +6.19%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
+          <t>• ОПИФ «Флагманский»: пай 917.61 ₽ (16.10.2026); 1 мес +5.15%  1 год +5.7%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Рублевые перспективы»: пай 1 716.65 ₽ (15.10.2026); 1 мес +0.09%  1 год +16.64%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+          <t>• ОПИФ «Рублевые перспективы»: пай 1 717.61 ₽ (16.10.2026); 1 мес +0.15%  1 год +16.17%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="B15" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.52 ₽ (15.10.2026); 1 мес +1.12%  1 год +15.44%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.53 ₽ (16.10.2026); 1 мес +1.12%  1 год +15.48%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="75" customHeight="1">
       <c r="B16" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 165.96 ₽ (15.10.2026); 1 мес +1.05%  1 год +14.66%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → позиция 159 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.02 ₽ (16.10.2026); 1 мес +1.05%  1 год +14.66%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → позиция 159 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
     <row r="19" ht="45" customHeight="1">
       <c r="B19" s="38" t="inlineStr">
         <is>
-          <t>• Сэйв — пенсионный счёт жены (Яндекс Банк): 593 000 ₽. Отдельный блок: не учитывается в долях  потенциале и дивидендных расчётах основного портфеля; входит только в семейный итог. Доходность — по тарифу «Сэйв» её аккаунта.</t>
+          <t>• Сэйв — пенсионный счёт жены (Яндекс Банк): 605 000 ₽. Отдельный блок: не учитывается в долях  потенциале и дивидендных расчётах основного портфеля; входит только в семейный итог. Доходность — по тарифу «Сэйв» её аккаунта.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>• Семейный итог (ликвидный): 2 032 456 ₽ = ваш 1 439 456 ₽ + 593 000 ₽.</t>
+          <t>• Семейный итог (ликвидный): 2 050 288 ₽ = ваш 1 445 288 ₽ + 605 000 ₽.</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="38" t="inlineStr">
         <is>
-          <t>• Итого с учётом заблокированных: 1 459 841 ₽ (ликвидная часть 1 439 456 ₽).</t>
+          <t>• Итого с учётом заблокированных: 1 465 673 ₽ (ликвидная часть 1 445 288 ₽).</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="38" t="inlineStr">
         <is>
-          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (16.10.2026, закрытие 15.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
+          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (19.10.2026, закрытие 16.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -67,12 +67,12 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -202,11 +202,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -633,14 +633,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 19.10.2026 (автообновление)</t>
+          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 20.10.2026 (автообновление)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (19.10.2026, закрытие 16.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
+          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (20.10.2026, закрытие 19.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Текущая цена, ₽ (19.10.2026)</t>
+          <t>Текущая цена, ₽ (20.10.2026)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Цена за пред. торг. день, ₽ (16.10.2026)</t>
+          <t>Цена за пред. торг. день, ₽ (19.10.2026)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -764,19 +764,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>287.53</v>
+        <v>293.03</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>287.29</v>
+        <v>290.7</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>0.0008</v>
+        <v>0.008</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>46004.8</v>
+        <v>46884.8</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.08357167243511418</v>
+        <v>0.08382534260547905</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.3195</v>
+        <v>0.2947</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="Q4" s="16" t="n">
-        <v>0.131</v>
+        <v>0.128</v>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
@@ -837,19 +837,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3435.5</v>
+        <v>3483.5</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>3478</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>-0.0122</v>
+        <v>3472</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0.0033</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>41226</v>
+        <v>41802</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.07489057158839985</v>
+        <v>0.07473780354388278</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.6931</v>
+        <v>0.6697</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="R5" s="15" t="inlineStr">
         <is>
@@ -910,19 +910,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>270.76</v>
+        <v>273.16</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>269.56</v>
+        <v>272.2</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0035</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>43321.6</v>
+        <v>43705.6</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.07869740906525063</v>
+        <v>0.07814125033652751</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.5214</v>
+        <v>0.508</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -979,19 +979,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2153.5</v>
+        <v>2226.5</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>2145.5</v>
+        <v>2176</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0037</v>
+        <v>0.0232</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>43070</v>
+        <v>44530</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.07824035604502938</v>
+        <v>0.07961519524924884</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.3287</v>
+        <v>0.2851</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.285</v>
+        <v>0.275</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1052,21 +1052,21 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>108.97</v>
+        <v>111.65</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>108.04</v>
+        <v>111.04</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0086</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>29421.9</v>
+        <v>30145.5</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.05344740960114349</v>
-      </c>
-      <c r="K8" s="19" t="inlineStr">
+        <v>0.05389714503449879</v>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1075,7 +1075,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.2893</v>
+        <v>0.2583</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1119,19 +1119,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6031</v>
+        <v>6125</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>6051.5</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>-0.0034</v>
+        <v>6086</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>0.0064</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>24124</v>
+        <v>24500</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.0438233189976849</v>
+        <v>0.04380355453866151</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>6221.5</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0.0316</v>
+        <v>0.0158</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="R9" s="15" t="inlineStr">
         <is>
@@ -1192,21 +1192,21 @@
         <v>140</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>154.56</v>
+        <v>157.07</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>155.5</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>-0.006</v>
+        <v>156.5</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0.0036</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>21638.4</v>
+        <v>21989.8</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.03930801300777255</v>
-      </c>
-      <c r="K10" s="19" t="inlineStr">
+        <v>0.03931556749364321</v>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1215,7 +1215,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.2783</v>
+        <v>0.2578</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>0.127</v>
+        <v>0.125</v>
       </c>
       <c r="R10" s="15" t="inlineStr">
         <is>
@@ -1265,19 +1265,19 @@
         <v>24</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1068.6</v>
+        <v>1075.6</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1056</v>
+        <v>1071</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0119</v>
+        <v>0.0043</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>25646.4</v>
+        <v>25814.4</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.0465888894189283</v>
+        <v>0.04615357054215606</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.4036999999999999</v>
+        <v>0.3946</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.191</v>
+        <v>0.19</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1338,19 +1338,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3517.5</v>
+        <v>3538</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>3517.5</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>0</v>
+        <v>3541</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>-0.0008</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>21105</v>
+        <v>21228</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03833904607221605</v>
+        <v>0.03795354513251863</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5428999999999999</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="R12" s="15" t="inlineStr">
         <is>
@@ -1411,19 +1411,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>115.46</v>
+        <v>116.7</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>115.94</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>-0.004099999999999999</v>
+        <v>116.82</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>-0.001</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>20782.8</v>
+        <v>21006</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.03775374208527134</v>
+        <v>0.0375566312913928</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3511</v>
+        <v>0.3368</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1480,19 +1480,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1.743</v>
+        <v>1.7605</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1.732</v>
+        <v>1.752</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.0064</v>
+        <v>0.0049</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>20916</v>
+        <v>21126</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03799571133127082</v>
+        <v>0.03777117931362298</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1819</v>
+        <v>0.1701</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         <v>28</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>570.4</v>
+        <v>570.6</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>577.6</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>-0.0125</v>
+        <v>573.2</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>-0.004500000000000001</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>15971.2</v>
+        <v>15976.8</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.0290130572200226</v>
-      </c>
-      <c r="K15" s="19" t="inlineStr">
+        <v>0.028564923679726</v>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1576,7 +1576,7 @@
         <v>563.15</v>
       </c>
       <c r="M15" s="20" t="n">
-        <v>-0.0127</v>
+        <v>-0.0131</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1622,21 +1622,21 @@
         <v>3</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>5791</v>
+        <v>5604</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>5667</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>0.0219</v>
+        <v>5790</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>-0.0321</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>17373</v>
+        <v>16812</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.03155954737799618</v>
-      </c>
-      <c r="K16" s="19" t="inlineStr">
+        <v>0.03005817791444805</v>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1645,7 +1645,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.0683</v>
+        <v>0.1039</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         <v>26</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>793</v>
+        <v>823.5</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>798</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>-0.0063</v>
+        <v>799</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>0.0307</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>20618</v>
+        <v>21411</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.03745436872385455</v>
-      </c>
-      <c r="K17" s="19" t="inlineStr">
+        <v>0.03828073086641965</v>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1716,7 +1716,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1765</v>
+        <v>0.133</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="Q17" s="16" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
@@ -1766,19 +1766,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>176.25</v>
+        <v>176.85</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>174</v>
+        <v>175.5</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0129</v>
+        <v>0.0077</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>21150</v>
+        <v>21222</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03842079243910777</v>
+        <v>0.03794281773140712</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3762</v>
+        <v>0.3715</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>0.199</v>
+        <v>0.198</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -1839,19 +1839,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>70.45999999999999</v>
+        <v>73.38</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>67.37</v>
+        <v>71</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.0335</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>22124.44</v>
+        <v>23041.32</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.04019094643364034</v>
+        <v>0.04119558029643886</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.1354</v>
+        <v>0.0902</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -1906,19 +1906,19 @@
         <v>20000</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>0.6784</v>
+        <v>0.6796</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>0.6806</v>
-      </c>
-      <c r="H20" s="18" t="n">
-        <v>-0.0032</v>
+        <v>0.6842</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>-0.0067</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>13568</v>
+        <v>13592</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.02464743791081863</v>
+        <v>0.02430113931793825</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>0.7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.0318</v>
+        <v>0.03</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
         <v>160</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>76.86</v>
+        <v>78.02</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>-0.0095</v>
+        <v>77.86</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>0.0021</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>12297.6</v>
+        <v>12483.2</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.02233964714416887</v>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
+        <v>0.0223187155925314</v>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2002,7 +2002,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1486</v>
+        <v>0.1315</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2046,19 +2046,19 @@
         <v>370000</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>0.05786</v>
+        <v>0.05964</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>0.05804</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>-0.0031</v>
+        <v>0.0586</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>0.0177</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>21408.2</v>
+        <v>22066.8</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.03888983492647314</v>
+        <v>0.03945323580790758</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -2109,21 +2109,21 @@
         <v>11</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1161.4</v>
+        <v>1177</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1165</v>
-      </c>
-      <c r="H23" s="18" t="n">
-        <v>-0.0031</v>
+        <v>1180</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>-0.0025</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>12775.4</v>
+        <v>12947</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.02320761190196583</v>
-      </c>
-      <c r="K23" s="19" t="inlineStr">
+        <v>0.02314794369845104</v>
+      </c>
+      <c r="K23" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2132,7 +2132,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.1553</v>
+        <v>0.14</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -2182,21 +2182,21 @@
         <v>340</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>35.86</v>
+        <v>36.16</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>36.11</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>-0.0069</v>
+        <v>36.18</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>12192.4</v>
+        <v>12294.4</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02214854230423534</v>
-      </c>
-      <c r="K24" s="19" t="inlineStr">
+        <v>0.02198116003755592</v>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2205,7 +2205,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.1969</v>
+        <v>0.1869</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.148</v>
+        <v>0.146</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2255,19 +2255,19 @@
         <v>363</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>56.08</v>
+        <v>57.44</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>55.445</v>
+        <v>56.715</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0115</v>
+        <v>0.0128</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>20357.04</v>
+        <v>20850.72</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03698031245931983</v>
+        <v>0.03727900615062694</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5968</v>
+        <v>0.5589999999999999</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>0.173</v>
+        <v>0.169</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -2328,19 +2328,19 @@
         <v>20</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>473.8</v>
+        <v>494.2</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>459.8</v>
+        <v>483.2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0304</v>
+        <v>0.0228</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>9476</v>
+        <v>9884</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.01721396828146502</v>
+        <v>0.01767160543102573</v>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.122</v>
+        <v>0.117</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2397,21 +2397,21 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>43.35</v>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>0.0035</v>
+        <v>43.7</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7395</v>
+        <v>7378</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.01343365295920576</v>
-      </c>
-      <c r="K27" s="19" t="inlineStr">
+        <v>0.01319112756678549</v>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2420,7 +2420,7 @@
         <v>42.5</v>
       </c>
       <c r="M27" s="20" t="n">
-        <v>-0.023</v>
+        <v>-0.0207</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2464,21 +2464,21 @@
         <v>160</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>40.75</v>
+        <v>41.4</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0037</v>
+        <v>0.0049</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>6520</v>
+        <v>6624</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.01184414026964457</v>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
+        <v>0.01184305082710587</v>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2487,7 +2487,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.227</v>
+        <v>0.2077</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2522,14 +2522,14 @@
       <c r="G29" s="24" t="n"/>
       <c r="H29" s="24" t="n"/>
       <c r="I29" s="25" t="n">
-        <v>550483.1800000001</v>
+        <v>559315.34</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>0.3808813343063437</v>
+        <v>0.3840362863071357</v>
       </c>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>Срвзв. потенциал: +31.6% · Покупать 13 / Держать 10 / без прогноза 2</t>
+          <t>Срвзв. потенциал: +29.6% · Покупать 13 / Держать 10 / без прогноза 2</t>
         </is>
       </c>
       <c r="L29" s="28" t="n"/>
@@ -2564,15 +2564,15 @@
         <v>341.3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>917.61</v>
+        <v>921.87</v>
       </c>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="9" t="n">
-        <v>313180.29</v>
+        <v>314634.23</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.4381340604205028</v>
+        <v>0.4387608015312843</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -2627,15 +2627,15 @@
         <v>146.3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1717.61</v>
+        <v>1722.76</v>
       </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="9" t="n">
-        <v>251286.34</v>
+        <v>252039.79</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3515454451887985</v>
+        <v>0.35147218495005</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -2690,15 +2690,15 @@
         <v>8530</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>14.53</v>
+        <v>14.54</v>
       </c>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="9" t="n">
-        <v>123940.9</v>
+        <v>124026.2</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.1733912749399763</v>
+        <v>0.1729558634573211</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>26397.18</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.03692921945072242</v>
+        <v>0.03681115006134453</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
       <c r="G34" s="24" t="n"/>
       <c r="H34" s="24" t="n"/>
       <c r="I34" s="25" t="n">
-        <v>714804.71</v>
+        <v>717097.4</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>0.4945760045080015</v>
+        <v>0.4923723751551363</v>
       </c>
       <c r="K34" s="28" t="n"/>
       <c r="L34" s="28" t="n"/>
@@ -2849,7 +2849,7 @@
         <v>180000</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.1245426611856549</v>
+        <v>0.123591338537728</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>180000</v>
       </c>
       <c r="J36" s="26" t="n">
-        <v>0.1245426611856549</v>
+        <v>0.123591338537728</v>
       </c>
       <c r="K36" s="28" t="n"/>
       <c r="L36" s="28" t="n"/>
@@ -2924,7 +2924,7 @@
       <c r="G37" s="24" t="n"/>
       <c r="H37" s="24" t="n"/>
       <c r="I37" s="30" t="n">
-        <v>1445287.89</v>
+        <v>1456412.74</v>
       </c>
       <c r="J37" s="31" t="n">
         <v>1</v>
@@ -3016,12 +3016,12 @@
       <c r="G39" s="24" t="n"/>
       <c r="H39" s="24" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>2050287.89</v>
+        <v>2061412.74</v>
       </c>
       <c r="J39" s="31" t="n"/>
       <c r="K39" s="34" t="inlineStr">
         <is>
-          <t>ваш 1 445 288 ₽ + жены 605 000 ₽</t>
+          <t>ваш 1 456 413 ₽ + жены 605 000 ₽</t>
         </is>
       </c>
       <c r="L39" s="32" t="n"/>
@@ -3133,11 +3133,11 @@
       <c r="G42" s="32" t="n"/>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="30" t="n">
-        <v>1465672.72</v>
+        <v>1476797.57</v>
       </c>
       <c r="J42" s="34" t="inlineStr">
         <is>
-          <t>ликвидная часть: 1 445 288 ₽ + заблокировано 20 385 ₽</t>
+          <t>ликвидная часть: 1 456 413 ₽ + заблокировано 20 385 ₽</t>
         </is>
       </c>
       <c r="K42" s="32" t="n"/>
@@ -3182,7 +3182,7 @@
     <row r="1">
       <c r="B1" s="37" t="inlineStr">
         <is>
-          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 19.10.2026 (АВТООБНОВЛЕНИЕ)</t>
+          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 20.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +31.6% (без учёта дивидендов).</t>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +29.6% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="38" t="inlineStr">
         <is>
-          <t>• Дивиденды за 12 месяцев (факт): ≈ 54 925 ₽ — 3.8% годовых на портфель.</t>
+          <t>• Дивиденды за 12 месяцев (факт): ≈ 54 925 ₽ — 3.77% годовых на портфель.</t>
         </is>
       </c>
     </row>
@@ -3245,21 +3245,21 @@
     <row r="13" ht="45" customHeight="1">
       <c r="B13" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Флагманский»: пай 917.61 ₽ (16.10.2026); 1 мес +5.15%  1 год +5.7%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
+          <t>• ОПИФ «Флагманский»: пай 921.87 ₽ (19.10.2026); 1 мес +5.41%  1 год +3.97%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Рублевые перспективы»: пай 1 717.61 ₽ (16.10.2026); 1 мес +0.15%  1 год +16.17%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+          <t>• ОПИФ «Рублевые перспективы»: пай 1 722.76 ₽ (19.10.2026); 1 мес +0.62%  1 год +16.01%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="B15" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.53 ₽ (16.10.2026); 1 мес +1.12%  1 год +15.48%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.54 ₽ (19.10.2026); 1 мес +1.15%  1 год +15.52%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>• Семейный итог (ликвидный): 2 050 288 ₽ = ваш 1 445 288 ₽ + 605 000 ₽.</t>
+          <t>• Семейный итог (ликвидный): 2 061 413 ₽ = ваш 1 456 413 ₽ + 605 000 ₽.</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="38" t="inlineStr">
         <is>
-          <t>• Итого с учётом заблокированных: 1 465 673 ₽ (ликвидная часть 1 445 288 ₽).</t>
+          <t>• Итого с учётом заблокированных: 1 476 798 ₽ (ликвидная часть 1 456 413 ₽).</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="38" t="inlineStr">
         <is>
-          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (19.10.2026, закрытие 16.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
+          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (20.10.2026, закрытие 19.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -633,14 +633,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 20.10.2026 (автообновление)</t>
+          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 21.10.2026 (автообновление)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (20.10.2026, закрытие 19.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
+          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (21.10.2026, закрытие 20.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Текущая цена, ₽ (20.10.2026)</t>
+          <t>Текущая цена, ₽ (21.10.2026)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Цена за пред. торг. день, ₽ (19.10.2026)</t>
+          <t>Цена за пред. торг. день, ₽ (20.10.2026)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -764,19 +764,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>293.03</v>
+        <v>294.41</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>290.7</v>
+        <v>293.45</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>0.008</v>
+        <v>0.0033</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>46884.8</v>
+        <v>47105.6</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.08382534260547905</v>
+        <v>0.08380851500746661</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.2947</v>
+        <v>0.2887</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -837,19 +837,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3483.5</v>
+        <v>3489.5</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>3472</v>
+        <v>3484</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0033</v>
+        <v>0.0016</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>41802</v>
+        <v>41874</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.07473780354388278</v>
+        <v>0.07450064870042324</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.6697</v>
+        <v>0.6668999999999999</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -910,19 +910,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>273.16</v>
+        <v>273.64</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>272.2</v>
+        <v>273.12</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.0035</v>
+        <v>0.0019</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>43705.6</v>
+        <v>43782.4</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.07814125033652751</v>
+        <v>0.07789600233226848</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.508</v>
+        <v>0.5054</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -979,19 +979,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
+        <v>2250.5</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>2226.5</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>2176</v>
-      </c>
       <c r="H7" s="8" t="n">
-        <v>0.0232</v>
+        <v>0.0108</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>44530</v>
+        <v>45010</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.07961519524924884</v>
+        <v>0.08008010216377824</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.2851</v>
+        <v>0.2714</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.275</v>
+        <v>0.272</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1052,19 +1052,19 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>111.65</v>
+        <v>112.43</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>111.04</v>
+        <v>112.41</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0002</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>30145.5</v>
+        <v>30356.1</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.05389714503449879</v>
+        <v>0.05400843344354296</v>
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.2583</v>
+        <v>0.2496</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1119,19 +1119,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6125</v>
+        <v>6109</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>6086</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0.0064</v>
+        <v>6117</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>24500</v>
+        <v>24436</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.04380355453866151</v>
+        <v>0.04347561378524961</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>6221.5</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0.0158</v>
+        <v>0.0184</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1192,19 +1192,19 @@
         <v>140</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>157.07</v>
+        <v>157.01</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>156.5</v>
+        <v>156.76</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.0036</v>
+        <v>0.0016</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>21989.8</v>
+        <v>21981.4</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.03931556749364321</v>
+        <v>0.03910848161970396</v>
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.2578</v>
+        <v>0.2583</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1265,19 +1265,19 @@
         <v>24</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1075.6</v>
+        <v>1079.6</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1071</v>
+        <v>1075.2</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0043</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>25814.4</v>
+        <v>25910.4</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.04615357054215606</v>
+        <v>0.04609881091100555</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.3946</v>
+        <v>0.3894</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.19</v>
+        <v>0.189</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1338,19 +1338,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3538</v>
+        <v>3552.5</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>3541</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>-0.0008</v>
+        <v>3551</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0.0004</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>21228</v>
+        <v>21315</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03795354513251863</v>
+        <v>0.03792284775874102</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.5428999999999999</v>
+        <v>0.5366</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1411,19 +1411,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>116.7</v>
+        <v>117.06</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>116.82</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>-0.001</v>
+        <v>116.86</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>0.0017</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>21006</v>
+        <v>21070.8</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.0375566312913928</v>
+        <v>0.03748837628688155</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3368</v>
+        <v>0.3326</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1480,19 +1480,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1.7605</v>
+        <v>1.794</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1.752</v>
+        <v>1.7665</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.0049</v>
+        <v>0.0156</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>21126</v>
+        <v>21528</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03777117931362298</v>
+        <v>0.03830180936195996</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1701</v>
+        <v>0.1483</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
@@ -1553,19 +1553,19 @@
         <v>28</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>570.6</v>
+        <v>572.65</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>573.2</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>-0.004500000000000001</v>
+        <v>571.4</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>0.0022</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>15976.8</v>
+        <v>16034.2</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.028564923679726</v>
+        <v>0.02852744665884144</v>
       </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>563.15</v>
       </c>
       <c r="M15" s="20" t="n">
-        <v>-0.0131</v>
+        <v>-0.0166</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>0.124</v>
+        <v>0.123</v>
       </c>
       <c r="R15" s="15" t="inlineStr">
         <is>
@@ -1622,19 +1622,19 @@
         <v>3</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>5604</v>
+        <v>5661</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>5790</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>-0.0321</v>
+        <v>5600</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>0.0109</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>16812</v>
+        <v>16983</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.03005817791444805</v>
+        <v>0.03021551599749935</v>
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.1039</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -1693,19 +1693,19 @@
         <v>26</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>823.5</v>
+        <v>828</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>799</v>
+        <v>826</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0307</v>
+        <v>0.0024</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>21411</v>
+        <v>21528</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.03828073086641965</v>
+        <v>0.03830180936195996</v>
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.133</v>
+        <v>0.1268</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -1766,19 +1766,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>176.85</v>
+        <v>176.65</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>175.5</v>
+        <v>176.45</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0077</v>
+        <v>0.0011</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>21222</v>
+        <v>21198</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03794281773140712</v>
+        <v>0.03771468575133907</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3715</v>
+        <v>0.3731</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -1839,19 +1839,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>73.38</v>
+        <v>73.67</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>71</v>
+        <v>72.81</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0118</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>23041.32</v>
+        <v>23132.38</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.04119558029643886</v>
+        <v>0.04115626202380228</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.0902</v>
+        <v>0.0859</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -1906,19 +1906,19 @@
         <v>20000</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>0.6796</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>0.6842</v>
-      </c>
-      <c r="H20" s="19" t="n">
-        <v>-0.0067</v>
+        <v>0.6802</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>0.0026</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>13592</v>
+        <v>13640</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.02430113931793825</v>
+        <v>0.02426777590566397</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>0.7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.03</v>
+        <v>0.0264</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -1979,19 +1979,19 @@
         <v>160</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>78.02</v>
+        <v>78.3</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>77.86</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0021</v>
+        <v>0.0008</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>12483.2</v>
+        <v>12528</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.0223187155925314</v>
+        <v>0.02228934725411717</v>
       </c>
       <c r="K21" s="18" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1315</v>
+        <v>0.1275</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2046,19 +2046,19 @@
         <v>370000</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>0.05964</v>
+        <v>0.06016</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>0.0586</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>0.0177</v>
+        <v>0.06054</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>22066.8</v>
+        <v>22259.2</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.03945323580790758</v>
+        <v>0.03960273295009937</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -2109,19 +2109,19 @@
         <v>11</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1177</v>
+        <v>1172.8</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1180</v>
+        <v>1178.4</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>-0.0025</v>
+        <v>-0.0048</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>12947</v>
+        <v>12900.8</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.02314794369845104</v>
+        <v>0.02295261901787314</v>
       </c>
       <c r="K23" s="18" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.14</v>
+        <v>0.1441</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2182,19 +2182,19 @@
         <v>340</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>36.16</v>
+        <v>36.56</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>36.18</v>
+        <v>36.65</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0025</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>12294.4</v>
+        <v>12430.4</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02198116003755592</v>
+        <v>0.0221157009983699</v>
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.1869</v>
+        <v>0.174</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.146</v>
+        <v>0.145</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2255,19 +2255,19 @@
         <v>363</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>57.44</v>
+        <v>58.08</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>56.715</v>
+        <v>57.625</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0128</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>20850.72</v>
+        <v>21083.04</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03727900615062694</v>
+        <v>0.03751015323534822</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5589999999999999</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>0.169</v>
+        <v>0.167</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -2328,19 +2328,19 @@
         <v>20</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>494.2</v>
+        <v>497.9</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>483.2</v>
+        <v>497.5</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0228</v>
+        <v>0.0008</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>9884</v>
+        <v>9958</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.01767160543102573</v>
+        <v>0.01771689974109984</v>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.117</v>
+        <v>0.116</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2397,19 +2397,19 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>43.4</v>
+        <v>43.35</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>43.7</v>
+        <v>43.55</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>-0.0069</v>
+        <v>-0.0046</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7378</v>
+        <v>7369.5</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.01319112756678549</v>
+        <v>0.01311153772263861</v>
       </c>
       <c r="K27" s="18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>42.5</v>
       </c>
       <c r="M27" s="20" t="n">
-        <v>-0.0207</v>
+        <v>-0.0196</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2464,19 +2464,19 @@
         <v>160</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>41.4</v>
+        <v>41.55</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>0.0049</v>
+        <v>41.65</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>-0.0024</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>6624</v>
+        <v>6648</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.01184305082710587</v>
+        <v>0.01182787201032654</v>
       </c>
       <c r="K28" s="18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.2077</v>
+        <v>0.2034</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2522,14 +2522,14 @@
       <c r="G29" s="24" t="n"/>
       <c r="H29" s="24" t="n"/>
       <c r="I29" s="25" t="n">
-        <v>559315.34</v>
+        <v>562062.22</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>0.3840362863071357</v>
+        <v>0.3852843986195348</v>
       </c>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>Срвзв. потенциал: +29.6% · Покупать 13 / Держать 10 / без прогноза 2</t>
+          <t>Срвзв. потенциал: +29.0% · Покупать 13 / Держать 10 / без прогноза 2</t>
         </is>
       </c>
       <c r="L29" s="28" t="n"/>
@@ -2572,7 +2572,7 @@
         <v>314634.23</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.4387608015312843</v>
+        <v>0.3715733849281525</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>252039.79</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.35147218495005</v>
+        <v>0.2976512692432757</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>124026.2</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.1729558634573211</v>
+        <v>0.1464711419154109</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -2750,18 +2750,18 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>159</v>
+        <v>939</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>166.02</v>
+        <v>166.2</v>
       </c>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="9" t="n">
-        <v>26397.18</v>
+        <v>156061.8</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.03681115006134453</v>
+        <v>0.1843042039131609</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="S33" s="17" t="inlineStr">
         <is>
-          <t>Доходность ≈ ставка денежного рынка ON минус расходы (~13,5% годовых); за 1 год +14,7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161,06 ₽; 08.10.2026 докуплено 180 паев по ~165,57 ₽; 12.10.2026 докуплено 220 паев по ~165,84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → позиция 159 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>Доходность ≈ ставка денежного рынка ON минус расходы (~13,5% годовых); за 1 год +14,7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161,06 ₽; 08.10.2026 докуплено 180 паев по ~165,57 ₽; 12.10.2026 докуплено 220 паев по ~165,84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → позиция 939 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -2807,10 +2807,10 @@
       <c r="G34" s="24" t="n"/>
       <c r="H34" s="24" t="n"/>
       <c r="I34" s="25" t="n">
-        <v>717097.4</v>
+        <v>846762.02</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>0.4923723751551363</v>
+        <v>0.580441424526919</v>
       </c>
       <c r="K34" s="28" t="n"/>
       <c r="L34" s="28" t="n"/>
@@ -2846,10 +2846,10 @@
       <c r="G35" s="5" t="n"/>
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="9" t="n">
-        <v>180000</v>
+        <v>50000</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.123591338537728</v>
+        <v>0.03427417685354611</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S35" s="17" t="inlineStr">
         <is>
-          <t>«Сейв» (Плюс): 10% брутто = ≈10,5% эфф. (капитализация ежедневно) → ≈1 580 ₽/мес на 180 тыс.; НДФЛ 0% — проценты в пределах безналогового лимита (1 млн × макс. ставка ≈ 140 тыс. ₽/год). С тратами картой Яндекса от 1 ₽/день → 13% (≈13,9% эфф., ≈2 080 ₽/мес, НДФЛ 0%). BCSD: ~13,5–14,5% брутто, но НДФЛ 13% с прибыли при продаже → чистыми ~11,8–12,6% (≈1 760–1 890 ₽/мес); без налога при владении 3+ года (ЛДВ) или на ИИС-3. Вывод: «Сейв» 13% чистыми выгоднее налогооблагаемого BCSD; «Сейв» 10% — проигрывает (~−250 ₽/мес)</t>
+          <t>«Сейв» (Плюс): 10% брутто = ≈10,5% эфф. (капитализация ежедневно) → ≈440 ₽/мес на 50 тыс.; НДФЛ 0% — проценты в пределах безналогового лимита (1 млн × макс. ставка ≈ 140 тыс. ₽/год). С тратами картой Яндекса от 1 ₽/день → 13% (≈13,9% эфф., ≈2 080 ₽/мес, НДФЛ 0%). BCSD: ~13,5–14,5% брутто, но НДФЛ 13% с прибыли при продаже → чистыми ~11,8–12,6% (≈1 760–1 890 ₽/мес); без налога при владении 3+ года (ЛДВ) или на ИИС-3. Вывод: «Сейв» 13% чистыми выгоднее налогооблагаемого BCSD; «Сейв» 10% — проигрывает (~−250 ₽/мес)</t>
         </is>
       </c>
     </row>
@@ -2895,10 +2895,10 @@
       <c r="G36" s="24" t="n"/>
       <c r="H36" s="24" t="n"/>
       <c r="I36" s="25" t="n">
-        <v>180000</v>
+        <v>50000</v>
       </c>
       <c r="J36" s="26" t="n">
-        <v>0.123591338537728</v>
+        <v>0.03427417685354611</v>
       </c>
       <c r="K36" s="28" t="n"/>
       <c r="L36" s="28" t="n"/>
@@ -2924,7 +2924,7 @@
       <c r="G37" s="24" t="n"/>
       <c r="H37" s="24" t="n"/>
       <c r="I37" s="30" t="n">
-        <v>1456412.74</v>
+        <v>1458824.24</v>
       </c>
       <c r="J37" s="31" t="n">
         <v>1</v>
@@ -3016,12 +3016,12 @@
       <c r="G39" s="24" t="n"/>
       <c r="H39" s="24" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>2061412.74</v>
+        <v>2063824.24</v>
       </c>
       <c r="J39" s="31" t="n"/>
       <c r="K39" s="34" t="inlineStr">
         <is>
-          <t>ваш 1 456 413 ₽ + жены 605 000 ₽</t>
+          <t>ваш 1 458 824 ₽ + жены 605 000 ₽</t>
         </is>
       </c>
       <c r="L39" s="32" t="n"/>
@@ -3133,11 +3133,11 @@
       <c r="G42" s="32" t="n"/>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="30" t="n">
-        <v>1476797.57</v>
+        <v>1479209.07</v>
       </c>
       <c r="J42" s="34" t="inlineStr">
         <is>
-          <t>ликвидная часть: 1 456 413 ₽ + заблокировано 20 385 ₽</t>
+          <t>ликвидная часть: 1 458 824 ₽ + заблокировано 20 385 ₽</t>
         </is>
       </c>
       <c r="K42" s="32" t="n"/>
@@ -3182,7 +3182,7 @@
     <row r="1">
       <c r="B1" s="37" t="inlineStr">
         <is>
-          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 20.10.2026 (АВТООБНОВЛЕНИЕ)</t>
+          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 21.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +29.6% (без учёта дивидендов).</t>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +29.0% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="75" customHeight="1">
+    <row r="16" ht="90" customHeight="1">
       <c r="B16" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.02 ₽ (16.10.2026); 1 мес +1.05%  1 год +14.66%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → позиция 159 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.20 ₽ (19.10.2026); 1 мес +1.1%  1 год +14.74%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → позиция 939 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>• Семейный итог (ликвидный): 2 061 413 ₽ = ваш 1 456 413 ₽ + 605 000 ₽.</t>
+          <t>• Семейный итог (ликвидный): 2 063 824 ₽ = ваш 1 458 824 ₽ + 605 000 ₽.</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="38" t="inlineStr">
         <is>
-          <t>• Итого с учётом заблокированных: 1 476 798 ₽ (ликвидная часть 1 456 413 ₽).</t>
+          <t>• Итого с учётом заблокированных: 1 479 209 ₽ (ликвидная часть 1 458 824 ₽).</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="38" t="inlineStr">
         <is>
-          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (20.10.2026, закрытие 19.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
+          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (21.10.2026, закрытие 20.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -51,11 +51,15 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
@@ -69,10 +73,6 @@
     <font>
       <b val="1"/>
       <color rgb="009C6500"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -190,23 +190,23 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -764,19 +764,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>294.41</v>
+        <v>291.62</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>293.45</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>0.0033</v>
+        <v>-0.0062</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>47105.6</v>
+        <v>46659.2</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.08380851500746661</v>
+        <v>0.08005251644922125</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.2887</v>
+        <v>0.301</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="Q4" s="16" t="n">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
@@ -837,19 +837,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3489.5</v>
+        <v>3452.5</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>3484</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0016</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>41874</v>
+        <v>41430</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.07450064870042324</v>
+        <v>0.07108085343279003</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.6668999999999999</v>
+        <v>0.6847</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
       <c r="R5" s="15" t="inlineStr">
         <is>
@@ -910,19 +910,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>273.64</v>
+        <v>270.4</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>273.12</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.0019</v>
+        <v>-0.01</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>43782.4</v>
+        <v>43264</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.07789600233226848</v>
+        <v>0.07422742078001998</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.5054</v>
+        <v>0.5234000000000001</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -984,14 +984,14 @@
       <c r="G7" s="7" t="n">
         <v>2226.5</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="18" t="n">
         <v>0.0108</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>45010</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.08008010216377824</v>
+        <v>0.07722300779652133</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1052,21 +1052,21 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>112.43</v>
+        <v>111.6</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>112.41</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0002</v>
+        <v>-0.0072</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>30356.1</v>
+        <v>30132</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.05400843344354296</v>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
+        <v>0.05169703778993071</v>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1075,7 +1075,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.2496</v>
+        <v>0.2589</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1119,19 +1119,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6109</v>
+        <v>6058.5</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>6117</v>
       </c>
-      <c r="H9" s="19" t="n">
-        <v>-0.0013</v>
+      <c r="H9" s="8" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>24436</v>
+        <v>24234</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.04347561378524961</v>
+        <v>0.04157792425996219</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>6221.5</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0.0184</v>
+        <v>0.0269</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="R9" s="15" t="inlineStr">
         <is>
@@ -1189,24 +1189,24 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>157.01</v>
+        <v>155.28</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>156.76</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.0016</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>21981.4</v>
+        <v>26397.6</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.03910848161970396</v>
-      </c>
-      <c r="K10" s="18" t="inlineStr">
+        <v>0.04528998157319377</v>
+      </c>
+      <c r="K10" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1215,7 +1215,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.2583</v>
+        <v>0.2723</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="R10" s="15" t="inlineStr">
         <is>
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1079.6</v>
+        <v>1064.2</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1075.2</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.0102</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>25910.4</v>
+        <v>30861.8</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.04609881091100555</v>
+        <v>0.05294914512363213</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.3894</v>
+        <v>0.4095</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.189</v>
+        <v>0.192</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1338,19 +1338,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3552.5</v>
+        <v>3536</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>3551</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0004</v>
+        <v>-0.0042</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>21315</v>
+        <v>21216</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03792284775874102</v>
+        <v>0.03639998519020211</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.5366</v>
+        <v>0.5438000000000001</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1411,19 +1411,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>117.06</v>
+        <v>114.92</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>116.86</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0017</v>
+        <v>-0.0166</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>21070.8</v>
+        <v>20685.6</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.03748837628688155</v>
+        <v>0.03548998556044705</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3326</v>
+        <v>0.3575</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1480,19 +1480,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1.794</v>
+        <v>1.7925</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1.7665</v>
       </c>
-      <c r="H14" s="8" t="n">
-        <v>0.0156</v>
+      <c r="H14" s="18" t="n">
+        <v>0.0147</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>21528</v>
+        <v>21510</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03830180936195996</v>
+        <v>0.03690439674968171</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1483</v>
+        <v>0.1492</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1550,24 +1550,24 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>572.65</v>
+        <v>566.45</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>571.4</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0022</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>16034.2</v>
+        <v>19825.75</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.02852744665884144</v>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
+        <v>0.03401475331752683</v>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1576,7 +1576,7 @@
         <v>563.15</v>
       </c>
       <c r="M15" s="20" t="n">
-        <v>-0.0166</v>
+        <v>-0.0058</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>0.123</v>
+        <v>0.125</v>
       </c>
       <c r="R15" s="15" t="inlineStr">
         <is>
@@ -1622,21 +1622,21 @@
         <v>3</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>5661</v>
+        <v>5620</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>5600</v>
       </c>
-      <c r="H16" s="8" t="n">
-        <v>0.0109</v>
+      <c r="H16" s="18" t="n">
+        <v>0.0036</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>16983</v>
+        <v>16860</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.03021551599749935</v>
-      </c>
-      <c r="K16" s="18" t="inlineStr">
+        <v>0.02892645881913685</v>
+      </c>
+      <c r="K16" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1645,7 +1645,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.1008</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         <v>26</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>826</v>
       </c>
-      <c r="H17" s="8" t="n">
-        <v>0.0024</v>
+      <c r="H17" s="18" t="n">
+        <v>0.0036</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>21528</v>
+        <v>21554</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.03830180936195996</v>
-      </c>
-      <c r="K17" s="18" t="inlineStr">
+        <v>0.03697988691504601</v>
+      </c>
+      <c r="K17" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1716,7 +1716,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1268</v>
+        <v>0.1255</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -1766,19 +1766,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>176.65</v>
+        <v>175.3</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>176.45</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0011</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>21198</v>
+        <v>21036</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03771468575133907</v>
+        <v>0.03609116178643908</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3731</v>
+        <v>0.3836</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>0.198</v>
+        <v>0.2</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -1839,19 +1839,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>73.67</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>72.81</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0118</v>
+        <v>-0.0194</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>23132.38</v>
+        <v>22419.6</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.04115626202380228</v>
+        <v>0.03846498435003087</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.0859</v>
+        <v>0.1204</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -1903,22 +1903,22 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G20" s="21" t="n">
         <v>0.6802</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>0.0026</v>
+      <c r="H20" s="18" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>13640</v>
+        <v>20520</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.02426777590566397</v>
+        <v>0.03520586802898507</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>0.7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.0264</v>
+        <v>0.0234</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="Q20" s="16" t="n">
-        <v>0.09</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="R20" s="15" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
         <v>160</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>78.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>78.23999999999999</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0008</v>
+        <v>-0.0274</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>12528</v>
+        <v>12176</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.02228934725411717</v>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
+        <v>0.02089018757899231</v>
+      </c>
+      <c r="K21" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2002,7 +2002,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1275</v>
+        <v>0.1601</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2051,14 +2051,14 @@
       <c r="G22" s="21" t="n">
         <v>0.06054</v>
       </c>
-      <c r="H22" s="19" t="n">
+      <c r="H22" s="8" t="n">
         <v>-0.0063</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>22259.2</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.03960273295009937</v>
+        <v>0.03818978838356649</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -2106,24 +2106,24 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1172.8</v>
+        <v>1134</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1178.4</v>
       </c>
-      <c r="H23" s="19" t="n">
-        <v>-0.0048</v>
+      <c r="H23" s="8" t="n">
+        <v>-0.0377</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>12900.8</v>
+        <v>13608</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.02295261901787314</v>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
+        <v>0.02334704932448483</v>
+      </c>
+      <c r="K23" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2132,7 +2132,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.1441</v>
+        <v>0.1832</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>0.104</v>
+        <v>0.107</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -2182,21 +2182,21 @@
         <v>340</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>36.56</v>
+        <v>36.11</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>36.65</v>
       </c>
-      <c r="H24" s="19" t="n">
-        <v>-0.0025</v>
+      <c r="H24" s="8" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>12430.4</v>
+        <v>12277.4</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.0221157009983699</v>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
+        <v>0.02106415809644548</v>
+      </c>
+      <c r="K24" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2205,7 +2205,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.174</v>
+        <v>0.1886</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.145</v>
+        <v>0.146</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2255,19 +2255,19 @@
         <v>363</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>58.08</v>
+        <v>57.075</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>57.625</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0095</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>21083.04</v>
+        <v>20718.23</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03751015323534822</v>
+        <v>0.03554596838080698</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>0.167</v>
+        <v>0.17</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>497.9</v>
+        <v>476.6</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>497.5</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0008</v>
+        <v>-0.042</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>9958</v>
+        <v>14298</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.01771689974109984</v>
+        <v>0.0245308723722431</v>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.116</v>
+        <v>0.122</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2397,21 +2397,21 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>43.35</v>
+        <v>43.3</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>43.55</v>
       </c>
-      <c r="H27" s="19" t="n">
-        <v>-0.0046</v>
+      <c r="H27" s="8" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7369.5</v>
+        <v>7361</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.01311153772263861</v>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
+        <v>0.01262916152833134</v>
+      </c>
+      <c r="K27" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2420,7 +2420,7 @@
         <v>42.5</v>
       </c>
       <c r="M27" s="20" t="n">
-        <v>-0.0196</v>
+        <v>-0.0185</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2464,21 +2464,21 @@
         <v>160</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>41.55</v>
+        <v>40.9</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>41.65</v>
       </c>
-      <c r="H28" s="19" t="n">
-        <v>-0.0024</v>
+      <c r="H28" s="8" t="n">
+        <v>-0.018</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>6648</v>
+        <v>6544</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.01182787201032654</v>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
+        <v>0.01122744641236249</v>
+      </c>
+      <c r="K28" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2487,7 +2487,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.2034</v>
+        <v>0.2225</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2522,14 +2522,14 @@
       <c r="G29" s="24" t="n"/>
       <c r="H29" s="24" t="n"/>
       <c r="I29" s="25" t="n">
-        <v>562062.22</v>
+        <v>582857.38</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>0.3852843986195348</v>
+        <v>0.3998334447424348</v>
       </c>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>Срвзв. потенциал: +29.0% · Покупать 13 / Держать 10 / без прогноза 2</t>
+          <t>Срвзв. потенциал: +29.9% · Покупать 13 / Держать 10 / без прогноза 2</t>
         </is>
       </c>
       <c r="L29" s="28" t="n"/>
@@ -2564,15 +2564,15 @@
         <v>341.3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>921.87</v>
+        <v>929.8200000000001</v>
       </c>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="9" t="n">
-        <v>314634.23</v>
+        <v>317347.57</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.3715733849281525</v>
+        <v>0.3847135894197</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -2627,15 +2627,15 @@
         <v>146.3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1722.76</v>
+        <v>1724.23</v>
       </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="9" t="n">
-        <v>252039.79</v>
+        <v>252254.85</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.2976512692432757</v>
+        <v>0.3058030940398505</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -2690,15 +2690,15 @@
         <v>8530</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>14.54</v>
+        <v>14.55</v>
       </c>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="9" t="n">
-        <v>124026.2</v>
+        <v>124111.5</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.1464711419154109</v>
+        <v>0.1504576847815885</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -2750,18 +2750,18 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>939</v>
+        <v>789</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>166.2</v>
+        <v>166.26</v>
       </c>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="9" t="n">
-        <v>156061.8</v>
+        <v>131179.14</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.1843042039131609</v>
+        <v>0.159025631758861</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="S33" s="17" t="inlineStr">
         <is>
-          <t>Доходность ≈ ставка денежного рынка ON минус расходы (~13,5% годовых); за 1 год +14,7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161,06 ₽; 08.10.2026 докуплено 180 паев по ~165,57 ₽; 12.10.2026 докуплено 220 паев по ~165,84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → позиция 939 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>Доходность ≈ ставка денежного рынка ON минус расходы (~13,5% годовых); за 1 год +14,7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161,06 ₽; 08.10.2026 докуплено 180 паев по ~165,57 ₽; 12.10.2026 докуплено 220 паев по ~165,84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → позиция 789 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -2807,10 +2807,10 @@
       <c r="G34" s="24" t="n"/>
       <c r="H34" s="24" t="n"/>
       <c r="I34" s="25" t="n">
-        <v>846762.02</v>
+        <v>824893.0600000001</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>0.580441424526919</v>
+        <v>0.5658671315509944</v>
       </c>
       <c r="K34" s="28" t="n"/>
       <c r="L34" s="28" t="n"/>
@@ -2849,7 +2849,7 @@
         <v>50000</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.03427417685354611</v>
+        <v>0.03429942370657079</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>50000</v>
       </c>
       <c r="J36" s="26" t="n">
-        <v>0.03427417685354611</v>
+        <v>0.03429942370657079</v>
       </c>
       <c r="K36" s="28" t="n"/>
       <c r="L36" s="28" t="n"/>
@@ -2924,7 +2924,7 @@
       <c r="G37" s="24" t="n"/>
       <c r="H37" s="24" t="n"/>
       <c r="I37" s="30" t="n">
-        <v>1458824.24</v>
+        <v>1457750.44</v>
       </c>
       <c r="J37" s="31" t="n">
         <v>1</v>
@@ -3016,12 +3016,12 @@
       <c r="G39" s="24" t="n"/>
       <c r="H39" s="24" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>2063824.24</v>
+        <v>2062750.44</v>
       </c>
       <c r="J39" s="31" t="n"/>
       <c r="K39" s="34" t="inlineStr">
         <is>
-          <t>ваш 1 458 824 ₽ + жены 605 000 ₽</t>
+          <t>ваш 1 457 750 ₽ + жены 605 000 ₽</t>
         </is>
       </c>
       <c r="L39" s="32" t="n"/>
@@ -3133,11 +3133,11 @@
       <c r="G42" s="32" t="n"/>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="30" t="n">
-        <v>1479209.07</v>
+        <v>1478135.27</v>
       </c>
       <c r="J42" s="34" t="inlineStr">
         <is>
-          <t>ликвидная часть: 1 458 824 ₽ + заблокировано 20 385 ₽</t>
+          <t>ликвидная часть: 1 457 750 ₽ + заблокировано 20 385 ₽</t>
         </is>
       </c>
       <c r="K42" s="32" t="n"/>
@@ -3196,7 +3196,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +29.0% (без учёта дивидендов).</t>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +29.9% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="38" t="inlineStr">
         <is>
-          <t>• Дивиденды за 12 месяцев (факт): ≈ 54 925 ₽ — 3.77% годовых на портфель.</t>
+          <t>• Дивиденды за 12 месяцев (факт): ≈ 58 341 ₽ — 4.0% годовых на портфель.</t>
         </is>
       </c>
     </row>
@@ -3245,28 +3245,28 @@
     <row r="13" ht="45" customHeight="1">
       <c r="B13" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Флагманский»: пай 921.87 ₽ (19.10.2026); 1 мес +5.41%  1 год +3.97%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
+          <t>• ОПИФ «Флагманский»: пай 929.82 ₽ (20.10.2026); 1 мес +6.32%  1 год +4.37%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Рублевые перспективы»: пай 1 722.76 ₽ (19.10.2026); 1 мес +0.62%  1 год +16.01%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+          <t>• ОПИФ «Рублевые перспективы»: пай 1 724.23 ₽ (20.10.2026); 1 мес +0.7%  1 год +15.86%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="B15" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.54 ₽ (19.10.2026); 1 мес +1.15%  1 год +15.52%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.55 ₽ (20.10.2026); 1 мес +1.19%  1 год +15.47%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.20 ₽ (19.10.2026); 1 мес +1.1%  1 год +14.74%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → позиция 939 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.26 ₽ (20.10.2026); 1 мес +1.13%  1 год +14.63%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → позиция 789 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>• Семейный итог (ликвидный): 2 063 824 ₽ = ваш 1 458 824 ₽ + 605 000 ₽.</t>
+          <t>• Семейный итог (ликвидный): 2 062 750 ₽ = ваш 1 457 750 ₽ + 605 000 ₽.</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="38" t="inlineStr">
         <is>
-          <t>• Итого с учётом заблокированных: 1 479 209 ₽ (ликвидная часть 1 458 824 ₽).</t>
+          <t>• Итого с учётом заблокированных: 1 478 135 ₽ (ликвидная часть 1 457 750 ₽).</t>
         </is>
       </c>
     </row>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -202,10 +202,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -633,14 +633,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 21.10.2026 (автообновление)</t>
+          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 22.10.2026 (автообновление)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (21.10.2026, закрытие 20.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
+          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (22.10.2026, закрытие 21.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Текущая цена, ₽ (21.10.2026)</t>
+          <t>Текущая цена, ₽ (22.10.2026)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Цена за пред. торг. день, ₽ (20.10.2026)</t>
+          <t>Цена за пред. торг. день, ₽ (21.10.2026)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -764,19 +764,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>291.62</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>293.45</v>
-      </c>
       <c r="H4" s="8" t="n">
-        <v>-0.0062</v>
+        <v>-0.0014</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>46659.2</v>
+        <v>46592</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.08005251644922125</v>
+        <v>0.08072512340070107</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.301</v>
+        <v>0.3029</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -837,19 +837,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
+        <v>3395.5</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>3452.5</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>3484</v>
-      </c>
       <c r="H5" s="8" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.0165</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>41430</v>
+        <v>40746</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.07108085343279003</v>
+        <v>0.07059636585862306</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.6847</v>
+        <v>0.713</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="R5" s="15" t="inlineStr">
         <is>
@@ -910,19 +910,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
+        <v>268.88</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>270.4</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>273.12</v>
-      </c>
       <c r="H6" s="8" t="n">
-        <v>-0.01</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>43264</v>
+        <v>43020.8</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.07422742078001998</v>
+        <v>0.07453767575542755</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.5234000000000001</v>
+        <v>0.532</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="R6" s="15" t="inlineStr">
         <is>
@@ -979,19 +979,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
+        <v>2208</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>2250.5</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>2226.5</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>0.0108</v>
+      <c r="H7" s="8" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>45010</v>
+        <v>44160</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.07722300779652133</v>
+        <v>0.07651144937703809</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.2714</v>
+        <v>0.2959</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.272</v>
+        <v>0.278</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1052,21 +1052,21 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>110.28</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>111.6</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>112.41</v>
-      </c>
       <c r="H8" s="8" t="n">
-        <v>-0.0072</v>
+        <v>-0.0118</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>30132</v>
+        <v>29775.6</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.05169703778993071</v>
-      </c>
-      <c r="K8" s="19" t="inlineStr">
+        <v>0.05158909221175125</v>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1075,7 +1075,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.2589</v>
+        <v>0.2739</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1119,19 +1119,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
+        <v>6062.5</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <v>6058.5</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>6117</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>-0.009599999999999999</v>
+      <c r="H9" s="19" t="n">
+        <v>0.0007000000000000001</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>24234</v>
+        <v>24250</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.04157792425996219</v>
+        <v>0.04201545850075122</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>6221.5</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0.0269</v>
+        <v>0.0262</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1192,21 +1192,21 @@
         <v>170</v>
       </c>
       <c r="F10" s="7" t="n">
+        <v>154.09</v>
+      </c>
+      <c r="G10" s="7" t="n">
         <v>155.28</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>156.76</v>
-      </c>
       <c r="H10" s="8" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0077</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>26397.6</v>
+        <v>26195.3</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.04528998157319377</v>
-      </c>
-      <c r="K10" s="19" t="inlineStr">
+        <v>0.04538587794081354</v>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1215,7 +1215,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.2723</v>
+        <v>0.2822</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
       <c r="R10" s="15" t="inlineStr">
         <is>
@@ -1265,19 +1265,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="7" t="n">
+        <v>1050.8</v>
+      </c>
+      <c r="G11" s="7" t="n">
         <v>1064.2</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>1075.2</v>
-      </c>
       <c r="H11" s="8" t="n">
-        <v>-0.0102</v>
+        <v>-0.0126</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>30861.8</v>
+        <v>30473.2</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.05294914512363213</v>
+        <v>0.05279775133959142</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.4095</v>
+        <v>0.4275</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.192</v>
+        <v>0.194</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1338,19 +1338,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
+        <v>3485</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>3536</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>3551</v>
-      </c>
       <c r="H12" s="8" t="n">
-        <v>-0.0042</v>
+        <v>-0.0144</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>21216</v>
+        <v>20910</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03639998519020211</v>
+        <v>0.03622858710312198</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.5438000000000001</v>
+        <v>0.5664</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="R12" s="15" t="inlineStr">
         <is>
@@ -1411,19 +1411,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
+        <v>113.76</v>
+      </c>
+      <c r="G13" s="7" t="n">
         <v>114.92</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>116.86</v>
-      </c>
       <c r="H13" s="8" t="n">
-        <v>-0.0166</v>
+        <v>-0.0101</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>20685.6</v>
+        <v>20476.8</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.03548998556044705</v>
+        <v>0.03547802641765701</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3575</v>
+        <v>0.3713</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1480,19 +1480,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="G14" s="7" t="n">
         <v>1.7925</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>1.7665</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>0.0147</v>
+      <c r="H14" s="8" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>21510</v>
+        <v>21096</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03690439674968171</v>
+        <v>0.03655085000131331</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1492</v>
+        <v>0.1718</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         <v>35</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>569.65</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>566.45</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>571.4</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>-0.008699999999999999</v>
+      <c r="H15" s="19" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>19825.75</v>
+        <v>19937.75</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.03401475331752683</v>
-      </c>
-      <c r="K15" s="19" t="inlineStr">
+        <v>0.03454407042158155</v>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1576,7 +1576,7 @@
         <v>563.15</v>
       </c>
       <c r="M15" s="20" t="n">
-        <v>-0.0058</v>
+        <v>-0.0114</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>0.125</v>
+        <v>0.124</v>
       </c>
       <c r="R15" s="15" t="inlineStr">
         <is>
@@ -1622,21 +1622,21 @@
         <v>3</v>
       </c>
       <c r="F16" s="7" t="n">
+        <v>5662</v>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>5620</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>5600</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>0.0036</v>
+      <c r="H16" s="19" t="n">
+        <v>0.0075</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>16860</v>
+        <v>16986</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.02892645881913685</v>
-      </c>
-      <c r="K16" s="19" t="inlineStr">
+        <v>0.02942987950902104</v>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1645,7 +1645,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.1008</v>
+        <v>0.0926</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         <v>26</v>
       </c>
       <c r="F17" s="7" t="n">
+        <v>821.5</v>
+      </c>
+      <c r="G17" s="7" t="n">
         <v>829</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>826</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>0.0036</v>
+      <c r="H17" s="8" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>21554</v>
+        <v>21359</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.03697988691504601</v>
-      </c>
-      <c r="K17" s="19" t="inlineStr">
+        <v>0.03700652280897094</v>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1716,7 +1716,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1255</v>
+        <v>0.1357</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -1766,19 +1766,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>174.55</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>175.3</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>176.45</v>
-      </c>
       <c r="H18" s="8" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0043</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>21036</v>
+        <v>20946</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03609116178643908</v>
+        <v>0.03629096056728804</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3836</v>
+        <v>0.3896</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>0.2</v>
+        <v>0.201</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -1839,19 +1839,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="G19" s="7" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>72.81</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>-0.0194</v>
+      <c r="H19" s="19" t="n">
+        <v>0.0098</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>22419.6</v>
+        <v>22639.4</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.03846498435003087</v>
+        <v>0.03922493901781061</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.1204</v>
+        <v>0.1096</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -1906,19 +1906,19 @@
         <v>30000</v>
       </c>
       <c r="F20" s="21" t="n">
+        <v>0.6754</v>
+      </c>
+      <c r="G20" s="21" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="G20" s="21" t="n">
-        <v>0.6802</v>
-      </c>
-      <c r="H20" s="18" t="n">
-        <v>0.005600000000000001</v>
+      <c r="H20" s="8" t="n">
+        <v>-0.0126</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>20520</v>
+        <v>20262</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.03520586802898507</v>
+        <v>0.03510586474813283</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>0.7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.0234</v>
+        <v>0.0364</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="Q20" s="16" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="R20" s="15" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
         <v>160</v>
       </c>
       <c r="F21" s="7" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="G21" s="7" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>78.23999999999999</v>
-      </c>
       <c r="H21" s="8" t="n">
-        <v>-0.0274</v>
+        <v>-0.0213</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>12176</v>
+        <v>11916.8</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.02089018757899231</v>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
+        <v>0.02064700271594854</v>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2002,7 +2002,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1601</v>
+        <v>0.1853</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2046,19 +2046,19 @@
         <v>370000</v>
       </c>
       <c r="F22" s="21" t="n">
+        <v>0.05812</v>
+      </c>
+      <c r="G22" s="21" t="n">
         <v>0.06016</v>
       </c>
-      <c r="G22" s="21" t="n">
-        <v>0.06054</v>
-      </c>
       <c r="H22" s="8" t="n">
-        <v>-0.0063</v>
+        <v>-0.0339</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>22259.2</v>
+        <v>21504.4</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.03818978838356649</v>
+        <v>0.03725844230035277</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -2109,21 +2109,21 @@
         <v>12</v>
       </c>
       <c r="F23" s="7" t="n">
+        <v>1099</v>
+      </c>
+      <c r="G23" s="7" t="n">
         <v>1134</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>1178.4</v>
-      </c>
       <c r="H23" s="8" t="n">
-        <v>-0.0377</v>
+        <v>-0.0309</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>13608</v>
+        <v>13188</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.02334704932448483</v>
-      </c>
-      <c r="K23" s="19" t="inlineStr">
+        <v>0.02284947903950132</v>
+      </c>
+      <c r="K23" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2132,7 +2132,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.1832</v>
+        <v>0.2209</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>0.107</v>
+        <v>0.111</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -2182,21 +2182,21 @@
         <v>340</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>36.11</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>36.65</v>
-      </c>
       <c r="H24" s="8" t="n">
-        <v>-0.0147</v>
+        <v>-0.021</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>12277.4</v>
+        <v>12019</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02106415809644548</v>
-      </c>
-      <c r="K24" s="19" t="inlineStr">
+        <v>0.02082407405033109</v>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2205,7 +2205,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.1886</v>
+        <v>0.2141</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.146</v>
+        <v>0.15</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2255,19 +2255,19 @@
         <v>363</v>
       </c>
       <c r="F25" s="7" t="n">
+        <v>56.555</v>
+      </c>
+      <c r="G25" s="7" t="n">
         <v>57.075</v>
       </c>
-      <c r="G25" s="7" t="n">
-        <v>57.625</v>
-      </c>
       <c r="H25" s="8" t="n">
-        <v>-0.0095</v>
+        <v>-0.0091</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>20718.23</v>
+        <v>20529.47</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03554596838080698</v>
+        <v>0.03556928226092442</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.569</v>
+        <v>0.5834</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -2328,19 +2328,19 @@
         <v>30</v>
       </c>
       <c r="F26" s="7" t="n">
+        <v>482.6</v>
+      </c>
+      <c r="G26" s="7" t="n">
         <v>476.6</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>497.5</v>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>-0.042</v>
+      <c r="H26" s="19" t="n">
+        <v>0.0126</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>14298</v>
+        <v>14478</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.0245308723722431</v>
+        <v>0.0250845281721186</v>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.122</v>
+        <v>0.12</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2397,21 +2397,21 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="G27" s="7" t="n">
         <v>43.3</v>
       </c>
-      <c r="G27" s="7" t="n">
-        <v>43.55</v>
-      </c>
       <c r="H27" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0139</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7361</v>
+        <v>7259</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.01262916152833134</v>
-      </c>
-      <c r="K27" s="19" t="inlineStr">
+        <v>0.012576916010596</v>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2420,7 +2420,7 @@
         <v>42.5</v>
       </c>
       <c r="M27" s="20" t="n">
-        <v>-0.0185</v>
+        <v>-0.004699999999999999</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2464,21 +2464,21 @@
         <v>160</v>
       </c>
       <c r="F28" s="7" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="G28" s="7" t="n">
         <v>40.9</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>41.65</v>
-      </c>
       <c r="H28" s="8" t="n">
-        <v>-0.018</v>
+        <v>-0.0147</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>6544</v>
+        <v>6448</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.01122744641236249</v>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
+        <v>0.01117178047063274</v>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2487,7 +2487,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.2225</v>
+        <v>0.2407</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2522,14 +2522,14 @@
       <c r="G29" s="24" t="n"/>
       <c r="H29" s="24" t="n"/>
       <c r="I29" s="25" t="n">
-        <v>582857.38</v>
+        <v>577168.52</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>0.3998334447424348</v>
+        <v>0.3979221155278064</v>
       </c>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>Срвзв. потенциал: +29.9% · Покупать 13 / Держать 10 / без прогноза 2</t>
+          <t>Срвзв. потенциал: +31.1% · Покупать 13 / Держать 10 / без прогноза 2</t>
         </is>
       </c>
       <c r="L29" s="28" t="n"/>
@@ -2564,15 +2564,15 @@
         <v>341.3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>929.8200000000001</v>
+        <v>924.46</v>
       </c>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="9" t="n">
-        <v>317347.57</v>
+        <v>315518.2</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.3847135894197</v>
+        <v>0.3832418294518459</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -2627,15 +2627,15 @@
         <v>146.3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1724.23</v>
+        <v>1725.49</v>
       </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="9" t="n">
-        <v>252254.85</v>
+        <v>252439.19</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3058030940398505</v>
+        <v>0.3066233802073609</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>124111.5</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.1504576847815885</v>
+        <v>0.1507511082277117</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -2753,15 +2753,15 @@
         <v>789</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>166.26</v>
+        <v>166.31</v>
       </c>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="9" t="n">
-        <v>131179.14</v>
+        <v>131218.59</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.159025631758861</v>
+        <v>0.1593836821130816</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
       <c r="G34" s="24" t="n"/>
       <c r="H34" s="24" t="n"/>
       <c r="I34" s="25" t="n">
-        <v>824893.0600000001</v>
+        <v>823287.48</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>0.5658671315509944</v>
+        <v>0.5676059666753076</v>
       </c>
       <c r="K34" s="28" t="n"/>
       <c r="L34" s="28" t="n"/>
@@ -2849,7 +2849,7 @@
         <v>50000</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.03429942370657079</v>
+        <v>0.03447191779688594</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>50000</v>
       </c>
       <c r="J36" s="26" t="n">
-        <v>0.03429942370657079</v>
+        <v>0.03447191779688594</v>
       </c>
       <c r="K36" s="28" t="n"/>
       <c r="L36" s="28" t="n"/>
@@ -2924,7 +2924,7 @@
       <c r="G37" s="24" t="n"/>
       <c r="H37" s="24" t="n"/>
       <c r="I37" s="30" t="n">
-        <v>1457750.44</v>
+        <v>1450456</v>
       </c>
       <c r="J37" s="31" t="n">
         <v>1</v>
@@ -3016,12 +3016,12 @@
       <c r="G39" s="24" t="n"/>
       <c r="H39" s="24" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>2062750.44</v>
+        <v>2055456</v>
       </c>
       <c r="J39" s="31" t="n"/>
       <c r="K39" s="34" t="inlineStr">
         <is>
-          <t>ваш 1 457 750 ₽ + жены 605 000 ₽</t>
+          <t>ваш 1 450 456 ₽ + жены 605 000 ₽</t>
         </is>
       </c>
       <c r="L39" s="32" t="n"/>
@@ -3133,11 +3133,11 @@
       <c r="G42" s="32" t="n"/>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="30" t="n">
-        <v>1478135.27</v>
+        <v>1470840.83</v>
       </c>
       <c r="J42" s="34" t="inlineStr">
         <is>
-          <t>ликвидная часть: 1 457 750 ₽ + заблокировано 20 385 ₽</t>
+          <t>ликвидная часть: 1 450 456 ₽ + заблокировано 20 385 ₽</t>
         </is>
       </c>
       <c r="K42" s="32" t="n"/>
@@ -3182,7 +3182,7 @@
     <row r="1">
       <c r="B1" s="37" t="inlineStr">
         <is>
-          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 21.10.2026 (АВТООБНОВЛЕНИЕ)</t>
+          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 22.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +29.9% (без учёта дивидендов).</t>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +31.1% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="38" t="inlineStr">
         <is>
-          <t>• Дивиденды за 12 месяцев (факт): ≈ 58 341 ₽ — 4.0% годовых на портфель.</t>
+          <t>• Дивиденды за 12 месяцев (факт): ≈ 58 341 ₽ — 4.02% годовых на портфель.</t>
         </is>
       </c>
     </row>
@@ -3245,28 +3245,28 @@
     <row r="13" ht="45" customHeight="1">
       <c r="B13" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Флагманский»: пай 929.82 ₽ (20.10.2026); 1 мес +6.32%  1 год +4.37%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
+          <t>• ОПИФ «Флагманский»: пай 924.46 ₽ (21.10.2026); 1 мес +6.21%  1 год +6.3%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Рублевые перспективы»: пай 1 724.23 ₽ (20.10.2026); 1 мес +0.7%  1 год +15.86%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+          <t>• ОПИФ «Рублевые перспективы»: пай 1 725.49 ₽ (21.10.2026); 1 мес +0.81%  1 год +16.21%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="B15" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.55 ₽ (20.10.2026); 1 мес +1.19%  1 год +15.47%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.55 ₽ (21.10.2026); 1 мес +1.11%  1 год +15.41%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.26 ₽ (20.10.2026); 1 мес +1.13%  1 год +14.63%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → позиция 789 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.31 ₽ (21.10.2026); 1 мес +1.05%  1 год +14.62%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → позиция 789 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>• Семейный итог (ликвидный): 2 062 750 ₽ = ваш 1 457 750 ₽ + 605 000 ₽.</t>
+          <t>• Семейный итог (ликвидный): 2 055 456 ₽ = ваш 1 450 456 ₽ + 605 000 ₽.</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="38" t="inlineStr">
         <is>
-          <t>• Итого с учётом заблокированных: 1 478 135 ₽ (ликвидная часть 1 457 750 ₽).</t>
+          <t>• Итого с учётом заблокированных: 1 470 841 ₽ (ликвидная часть 1 450 456 ₽).</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="38" t="inlineStr">
         <is>
-          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (21.10.2026, закрытие 20.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
+          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (22.10.2026, закрытие 21.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -51,15 +51,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
@@ -73,6 +69,10 @@
     <font>
       <b val="1"/>
       <color rgb="009C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -190,23 +190,23 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -633,14 +633,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 22.10.2026 (автообновление)</t>
+          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 23.10.2026 (автообновление)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (22.10.2026, закрытие 21.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
+          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (23.10.2026, закрытие 22.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Текущая цена, ₽ (22.10.2026)</t>
+          <t>Текущая цена, ₽ (23.10.2026)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Цена за пред. торг. день, ₽ (21.10.2026)</t>
+          <t>Цена за пред. торг. день, ₽ (22.10.2026)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -764,19 +764,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
+        <v>292.32</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>291.2</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>291.62</v>
-      </c>
       <c r="H4" s="8" t="n">
-        <v>-0.0014</v>
+        <v>0.0038</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>46592</v>
+        <v>46771.2</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.08072512340070107</v>
+        <v>0.08000183912273844</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.3029</v>
+        <v>0.2979</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -837,19 +837,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>3395.5</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>3452.5</v>
-      </c>
       <c r="H5" s="8" t="n">
-        <v>-0.0165</v>
+        <v>0.0013</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>40746</v>
+        <v>40800</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.07059636585862306</v>
+        <v>0.06978813962882562</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.713</v>
+        <v>0.7106999999999999</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -910,19 +910,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
+        <v>269.66</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>268.88</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>270.4</v>
-      </c>
       <c r="H6" s="8" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>43020.8</v>
+        <v>43145.6</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.07453767575542755</v>
+        <v>0.07380027346003575</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.532</v>
+        <v>0.5276</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -979,19 +979,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
+        <v>2278.5</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>2208</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>2250.5</v>
-      </c>
       <c r="H7" s="8" t="n">
-        <v>-0.0189</v>
+        <v>0.0319</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>44160</v>
+        <v>45570</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.07651144937703809</v>
+        <v>0.07794719418837213</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.2959</v>
+        <v>0.2558</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.278</v>
+        <v>0.269</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1052,19 +1052,19 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>110.28</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>111.6</v>
-      </c>
       <c r="H8" s="8" t="n">
-        <v>-0.0118</v>
+        <v>0.0405</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>29775.6</v>
+        <v>30982.5</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.05158909221175125</v>
+        <v>0.05299536853063945</v>
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.2739</v>
+        <v>0.2243</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1119,19 +1119,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
+        <v>6144.5</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <v>6062.5</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>6058.5</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.0007000000000000001</v>
+      <c r="H9" s="8" t="n">
+        <v>0.0135</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>24250</v>
+        <v>24578</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.04201545850075122</v>
+        <v>0.04204051215189402</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>6221.5</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0.0262</v>
+        <v>0.0125</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
       <c r="R9" s="15" t="inlineStr">
         <is>
@@ -1192,19 +1192,19 @@
         <v>170</v>
       </c>
       <c r="F10" s="7" t="n">
+        <v>155.37</v>
+      </c>
+      <c r="G10" s="7" t="n">
         <v>154.09</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>155.28</v>
-      </c>
       <c r="H10" s="8" t="n">
-        <v>-0.0077</v>
+        <v>0.0083</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>26195.3</v>
+        <v>26412.9</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.04538587794081354</v>
+        <v>0.04517909689221099</v>
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.2822</v>
+        <v>0.2716</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>0.127</v>
+        <v>0.126</v>
       </c>
       <c r="R10" s="15" t="inlineStr">
         <is>
@@ -1265,19 +1265,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="7" t="n">
+        <v>1062.6</v>
+      </c>
+      <c r="G11" s="7" t="n">
         <v>1050.8</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>1064.2</v>
-      </c>
       <c r="H11" s="8" t="n">
-        <v>-0.0126</v>
+        <v>0.0112</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>30473.2</v>
+        <v>30815.4</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.05279775133959142</v>
+        <v>0.05270954504701257</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.4275</v>
+        <v>0.4116</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.194</v>
+        <v>0.192</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1338,19 +1338,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
+        <v>3520.5</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>3485</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>3536</v>
-      </c>
       <c r="H12" s="8" t="n">
-        <v>-0.0144</v>
+        <v>0.0102</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>20910</v>
+        <v>21123</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03622858710312198</v>
+        <v>0.03613075670048244</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.5664</v>
+        <v>0.5506</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1411,19 +1411,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="G13" s="7" t="n">
         <v>113.76</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>114.92</v>
-      </c>
       <c r="H13" s="8" t="n">
-        <v>-0.0101</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>20476.8</v>
+        <v>20574</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.03547802641765701</v>
+        <v>0.03519169570400633</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3713</v>
+        <v>0.3648</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1480,19 +1480,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
+        <v>1.789</v>
+      </c>
+      <c r="G14" s="7" t="n">
         <v>1.758</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>1.7925</v>
-      </c>
       <c r="H14" s="8" t="n">
-        <v>-0.0192</v>
+        <v>0.0176</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>21096</v>
+        <v>21468</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03655085000131331</v>
+        <v>0.03672087699881442</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1718</v>
+        <v>0.1515</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
@@ -1553,19 +1553,19 @@
         <v>35</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>574.3</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>569.65</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>566.45</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>0.005600000000000001</v>
+      <c r="H15" s="8" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>19937.75</v>
+        <v>20100.5</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.03454407042158155</v>
+        <v>0.03438177697571591</v>
       </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
@@ -1575,8 +1575,8 @@
       <c r="L15" s="7" t="n">
         <v>563.15</v>
       </c>
-      <c r="M15" s="20" t="n">
-        <v>-0.0114</v>
+      <c r="M15" s="19" t="n">
+        <v>-0.0194</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>0.124</v>
+        <v>0.123</v>
       </c>
       <c r="R15" s="15" t="inlineStr">
         <is>
@@ -1622,19 +1622,19 @@
         <v>3</v>
       </c>
       <c r="F16" s="7" t="n">
+        <v>5770</v>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>5662</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>5620</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>0.0075</v>
+      <c r="H16" s="8" t="n">
+        <v>0.0191</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>16986</v>
+        <v>17310</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.02942987950902104</v>
+        <v>0.02960864453370028</v>
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.0926</v>
+        <v>0.0722</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -1693,19 +1693,19 @@
         <v>26</v>
       </c>
       <c r="F17" s="7" t="n">
+        <v>800.5</v>
+      </c>
+      <c r="G17" s="7" t="n">
         <v>821.5</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>829</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>-0.009000000000000001</v>
+      <c r="H17" s="20" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>21359</v>
+        <v>20813</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.03700652280897094</v>
+        <v>0.03560050367879283</v>
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1357</v>
+        <v>0.1655</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="Q17" s="16" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
@@ -1766,19 +1766,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>176.45</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>174.55</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>175.3</v>
-      </c>
       <c r="H18" s="8" t="n">
-        <v>-0.0043</v>
+        <v>0.0109</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>20946</v>
+        <v>21174</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03629096056728804</v>
+        <v>0.03621799187501847</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3896</v>
+        <v>0.3746</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>0.201</v>
+        <v>0.198</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -1839,19 +1839,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="G19" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>0.0098</v>
+      <c r="H19" s="8" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>22639.4</v>
+        <v>22768.14</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.03922493901781061</v>
+        <v>0.03894475817178063</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.1096</v>
+        <v>0.1033</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -1906,19 +1906,19 @@
         <v>30000</v>
       </c>
       <c r="F20" s="21" t="n">
+        <v>0.6942</v>
+      </c>
+      <c r="G20" s="21" t="n">
         <v>0.6754</v>
       </c>
-      <c r="G20" s="21" t="n">
-        <v>0.6840000000000001</v>
-      </c>
       <c r="H20" s="8" t="n">
-        <v>-0.0126</v>
+        <v>0.0278</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>20262</v>
+        <v>20826</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.03510586474813283</v>
+        <v>0.03562274009583143</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>0.7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.0364</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="Q20" s="16" t="n">
-        <v>0.091</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="R20" s="15" t="inlineStr">
         <is>
@@ -1979,19 +1979,19 @@
         <v>160</v>
       </c>
       <c r="F21" s="7" t="n">
+        <v>76.44</v>
+      </c>
+      <c r="G21" s="7" t="n">
         <v>74.48</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>76.09999999999999</v>
-      </c>
       <c r="H21" s="8" t="n">
-        <v>-0.0213</v>
+        <v>0.0263</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>11916.8</v>
+        <v>12230.4</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.02064700271594854</v>
+        <v>0.02092002114991149</v>
       </c>
       <c r="K21" s="18" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1853</v>
+        <v>0.1549</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2046,19 +2046,19 @@
         <v>370000</v>
       </c>
       <c r="F22" s="21" t="n">
+        <v>0.06144</v>
+      </c>
+      <c r="G22" s="21" t="n">
         <v>0.05812</v>
       </c>
-      <c r="G22" s="21" t="n">
-        <v>0.06016</v>
-      </c>
       <c r="H22" s="8" t="n">
-        <v>-0.0339</v>
+        <v>0.0571</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>21504.4</v>
+        <v>22732.8</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.03725844230035277</v>
+        <v>0.03888430932730801</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -2109,19 +2109,19 @@
         <v>12</v>
       </c>
       <c r="F23" s="7" t="n">
+        <v>1098.2</v>
+      </c>
+      <c r="G23" s="7" t="n">
         <v>1099</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>1134</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>-0.0309</v>
+      <c r="H23" s="20" t="n">
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>13188</v>
+        <v>13178.4</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.02284947903950132</v>
+        <v>0.02254156910011067</v>
       </c>
       <c r="K23" s="18" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.2209</v>
+        <v>0.2218</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2182,19 +2182,19 @@
         <v>340</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>35.35</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>36.11</v>
-      </c>
       <c r="H24" s="8" t="n">
-        <v>-0.021</v>
+        <v>0.017</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>12019</v>
+        <v>12223</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02082407405033109</v>
+        <v>0.02090736349713567</v>
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.2141</v>
+        <v>0.1939</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.15</v>
+        <v>0.147</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2255,19 +2255,19 @@
         <v>363</v>
       </c>
       <c r="F25" s="7" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="G25" s="7" t="n">
         <v>56.555</v>
       </c>
-      <c r="G25" s="7" t="n">
-        <v>57.075</v>
-      </c>
       <c r="H25" s="8" t="n">
-        <v>-0.0091</v>
+        <v>0.0068</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>20529.47</v>
+        <v>20669.22</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03556928226092442</v>
+        <v>0.03535456890634596</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5834</v>
+        <v>0.5727</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>0.172</v>
+        <v>0.171</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -2328,19 +2328,19 @@
         <v>30</v>
       </c>
       <c r="F26" s="7" t="n">
+        <v>479</v>
+      </c>
+      <c r="G26" s="7" t="n">
         <v>482.6</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>476.6</v>
-      </c>
-      <c r="H26" s="19" t="n">
-        <v>0.0126</v>
+      <c r="H26" s="20" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>14478</v>
+        <v>14370</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.0250845281721186</v>
+        <v>0.02457979329574079</v>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2397,19 +2397,19 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="G27" s="7" t="n">
         <v>42.7</v>
       </c>
-      <c r="G27" s="7" t="n">
-        <v>43.3</v>
-      </c>
       <c r="H27" s="8" t="n">
-        <v>-0.0139</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7259</v>
+        <v>7318.5</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.012576916010596</v>
+        <v>0.01251824754592059</v>
       </c>
       <c r="K27" s="18" t="inlineStr">
         <is>
@@ -2419,8 +2419,8 @@
       <c r="L27" s="7" t="n">
         <v>42.5</v>
       </c>
-      <c r="M27" s="20" t="n">
-        <v>-0.004699999999999999</v>
+      <c r="M27" s="19" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2464,19 +2464,19 @@
         <v>160</v>
       </c>
       <c r="F28" s="7" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="G28" s="7" t="n">
         <v>40.3</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>40.9</v>
-      </c>
       <c r="H28" s="8" t="n">
-        <v>-0.0147</v>
+        <v>0.0347</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>6448</v>
+        <v>6672</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.01117178047063274</v>
+        <v>0.01141241342165501</v>
       </c>
       <c r="K28" s="18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.2407</v>
+        <v>0.199</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2522,14 +2522,14 @@
       <c r="G29" s="24" t="n"/>
       <c r="H29" s="24" t="n"/>
       <c r="I29" s="25" t="n">
-        <v>577168.52</v>
+        <v>584626.5600000001</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>0.3979221155278064</v>
+        <v>0.4012489875632261</v>
       </c>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>Срвзв. потенциал: +31.1% · Покупать 13 / Держать 10 / без прогноза 2</t>
+          <t>Срвзв. потенциал: +29.6% · Покупать 13 / Держать 10 / без прогноза 2</t>
         </is>
       </c>
       <c r="L29" s="28" t="n"/>
@@ -2564,15 +2564,15 @@
         <v>341.3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>924.46</v>
+        <v>921.61</v>
       </c>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="9" t="n">
-        <v>315518.2</v>
+        <v>314545.49</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.3832418294518459</v>
+        <v>0.3824771168581927</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -2627,15 +2627,15 @@
         <v>146.3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1725.49</v>
+        <v>1725.1</v>
       </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="9" t="n">
-        <v>252439.19</v>
+        <v>252382.13</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3066233802073609</v>
+        <v>0.3068884867143687</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -2690,15 +2690,15 @@
         <v>8530</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>14.55</v>
+        <v>14.56</v>
       </c>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="9" t="n">
-        <v>124111.5</v>
+        <v>124196.8</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.1507511082277117</v>
+        <v>0.1510192817802398</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -2753,15 +2753,15 @@
         <v>789</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>166.31</v>
+        <v>166.37</v>
       </c>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="9" t="n">
-        <v>131218.59</v>
+        <v>131265.93</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.1593836821130816</v>
+        <v>0.1596151146471989</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
       <c r="G34" s="24" t="n"/>
       <c r="H34" s="24" t="n"/>
       <c r="I34" s="25" t="n">
-        <v>823287.48</v>
+        <v>822390.35</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>0.5676059666753076</v>
+        <v>0.5644343208068876</v>
       </c>
       <c r="K34" s="28" t="n"/>
       <c r="L34" s="28" t="n"/>
@@ -2849,7 +2849,7 @@
         <v>50000</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.03447191779688594</v>
+        <v>0.03431669162988644</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>50000</v>
       </c>
       <c r="J36" s="26" t="n">
-        <v>0.03447191779688594</v>
+        <v>0.03431669162988644</v>
       </c>
       <c r="K36" s="28" t="n"/>
       <c r="L36" s="28" t="n"/>
@@ -2924,7 +2924,7 @@
       <c r="G37" s="24" t="n"/>
       <c r="H37" s="24" t="n"/>
       <c r="I37" s="30" t="n">
-        <v>1450456</v>
+        <v>1457016.91</v>
       </c>
       <c r="J37" s="31" t="n">
         <v>1</v>
@@ -3016,12 +3016,12 @@
       <c r="G39" s="24" t="n"/>
       <c r="H39" s="24" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>2055456</v>
+        <v>2062016.91</v>
       </c>
       <c r="J39" s="31" t="n"/>
       <c r="K39" s="34" t="inlineStr">
         <is>
-          <t>ваш 1 450 456 ₽ + жены 605 000 ₽</t>
+          <t>ваш 1 457 017 ₽ + жены 605 000 ₽</t>
         </is>
       </c>
       <c r="L39" s="32" t="n"/>
@@ -3133,11 +3133,11 @@
       <c r="G42" s="32" t="n"/>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="30" t="n">
-        <v>1470840.83</v>
+        <v>1477401.74</v>
       </c>
       <c r="J42" s="34" t="inlineStr">
         <is>
-          <t>ликвидная часть: 1 450 456 ₽ + заблокировано 20 385 ₽</t>
+          <t>ликвидная часть: 1 457 017 ₽ + заблокировано 20 385 ₽</t>
         </is>
       </c>
       <c r="K42" s="32" t="n"/>
@@ -3182,7 +3182,7 @@
     <row r="1">
       <c r="B1" s="37" t="inlineStr">
         <is>
-          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 22.10.2026 (АВТООБНОВЛЕНИЕ)</t>
+          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 23.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +31.1% (без учёта дивидендов).</t>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +29.6% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="38" t="inlineStr">
         <is>
-          <t>• Дивиденды за 12 месяцев (факт): ≈ 58 341 ₽ — 4.02% годовых на портфель.</t>
+          <t>• Дивиденды за 12 месяцев (факт): ≈ 58 341 ₽ — 4.0% годовых на портфель.</t>
         </is>
       </c>
     </row>
@@ -3245,28 +3245,28 @@
     <row r="13" ht="45" customHeight="1">
       <c r="B13" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Флагманский»: пай 924.46 ₽ (21.10.2026); 1 мес +6.21%  1 год +6.3%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
+          <t>• ОПИФ «Флагманский»: пай 921.61 ₽ (22.10.2026); 1 мес +4.68%  1 год +5.69%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Рублевые перспективы»: пай 1 725.49 ₽ (21.10.2026); 1 мес +0.81%  1 год +16.21%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+          <t>• ОПИФ «Рублевые перспективы»: пай 1 725.10 ₽ (22.10.2026); 1 мес +0.62%  1 год +16.08%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="B15" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.55 ₽ (21.10.2026); 1 мес +1.11%  1 год +15.41%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.56 ₽ (22.10.2026); 1 мес +1.11%  1 год +15.37%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.31 ₽ (21.10.2026); 1 мес +1.05%  1 год +14.62%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → позиция 789 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.37 ₽ (22.10.2026); 1 мес +1.05%  1 год +14.61%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → позиция 789 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>• Семейный итог (ликвидный): 2 055 456 ₽ = ваш 1 450 456 ₽ + 605 000 ₽.</t>
+          <t>• Семейный итог (ликвидный): 2 062 017 ₽ = ваш 1 457 017 ₽ + 605 000 ₽.</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="38" t="inlineStr">
         <is>
-          <t>• Итого с учётом заблокированных: 1 470 841 ₽ (ликвидная часть 1 450 456 ₽).</t>
+          <t>• Итого с учётом заблокированных: 1 477 402 ₽ (ликвидная часть 1 457 017 ₽).</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="38" t="inlineStr">
         <is>
-          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (22.10.2026, закрытие 21.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
+          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (23.10.2026, закрытие 22.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -67,12 +67,12 @@
       <sz val="9"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
       <sz val="10"/>
     </font>
     <font>
@@ -202,11 +202,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -633,14 +633,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 23.10.2026 (автообновление)</t>
+          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 26.10.2026 (автообновление)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (23.10.2026, закрытие 22.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
+          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (26.10.2026, закрытие 23.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Текущая цена, ₽ (23.10.2026)</t>
+          <t>Текущая цена, ₽ (26.10.2026)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Цена за пред. торг. день, ₽ (22.10.2026)</t>
+          <t>Цена за пред. торг. день, ₽ (23.10.2026)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -764,19 +764,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
+        <v>296</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>292.32</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>291.2</v>
-      </c>
       <c r="H4" s="8" t="n">
-        <v>0.0038</v>
+        <v>0.0126</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>46771.2</v>
+        <v>47360</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.08000183912273844</v>
+        <v>0.08021470305358711</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.2979</v>
+        <v>0.2818</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="Q4" s="16" t="n">
-        <v>0.129</v>
+        <v>0.127</v>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
@@ -837,19 +837,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
+        <v>3471.5</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>3400</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>3395.5</v>
-      </c>
       <c r="H5" s="8" t="n">
-        <v>0.0013</v>
+        <v>0.021</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>40800</v>
+        <v>41658</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.06978813962882562</v>
+        <v>0.0705570967019918</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.7106999999999999</v>
+        <v>0.6755</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="R5" s="15" t="inlineStr">
         <is>
@@ -910,19 +910,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
+        <v>273.82</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>269.66</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>268.88</v>
-      </c>
       <c r="H6" s="8" t="n">
-        <v>0.0029</v>
+        <v>0.0154</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>43145.6</v>
+        <v>43811.2</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.07380027346003575</v>
+        <v>0.07420402023693655</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.5276</v>
+        <v>0.5044</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="R6" s="15" t="inlineStr">
         <is>
@@ -979,19 +979,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
+        <v>2288</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>2278.5</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>2208</v>
-      </c>
       <c r="H7" s="8" t="n">
-        <v>0.0319</v>
+        <v>0.0042</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>45570</v>
+        <v>45760</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.07794719418837213</v>
+        <v>0.07750474686934429</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.2558</v>
+        <v>0.2506</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.269</v>
+        <v>0.268</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1052,21 +1052,21 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>114.36</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>114.75</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>110.28</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>0.0405</v>
+      <c r="H8" s="18" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>30982.5</v>
+        <v>30877.2</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.05299536853063945</v>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
+        <v>0.05229741193256376</v>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1075,7 +1075,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.2243</v>
+        <v>0.2285</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1119,19 +1119,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
+        <v>6165.5</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <v>6144.5</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>6062.5</v>
-      </c>
       <c r="H9" s="8" t="n">
-        <v>0.0135</v>
+        <v>0.0034</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>24578</v>
+        <v>24662</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.04204051215189402</v>
+        <v>0.04177058713487258</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>6221.5</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0.0125</v>
+        <v>0.0091</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="R9" s="15" t="inlineStr">
         <is>
@@ -1192,21 +1192,21 @@
         <v>170</v>
       </c>
       <c r="F10" s="7" t="n">
+        <v>157.62</v>
+      </c>
+      <c r="G10" s="7" t="n">
         <v>155.37</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>154.09</v>
-      </c>
       <c r="H10" s="8" t="n">
-        <v>0.0083</v>
+        <v>0.0145</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>26412.9</v>
+        <v>26795.4</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.04517909689221099</v>
-      </c>
-      <c r="K10" s="18" t="inlineStr">
+        <v>0.04538397496203733</v>
+      </c>
+      <c r="K10" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1215,7 +1215,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.2716</v>
+        <v>0.2535</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>0.126</v>
+        <v>0.124</v>
       </c>
       <c r="R10" s="15" t="inlineStr">
         <is>
@@ -1265,19 +1265,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="7" t="n">
+        <v>1066.8</v>
+      </c>
+      <c r="G11" s="7" t="n">
         <v>1062.6</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>1050.8</v>
-      </c>
       <c r="H11" s="8" t="n">
-        <v>0.0112</v>
+        <v>0.004</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>30815.4</v>
+        <v>30937.2</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.05270954504701257</v>
+        <v>0.05239903528947287</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.4116</v>
+        <v>0.4061</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.192</v>
+        <v>0.191</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1338,19 +1338,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
+        <v>3534.5</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>3520.5</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>3485</v>
-      </c>
       <c r="H12" s="8" t="n">
-        <v>0.0102</v>
+        <v>0.004</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>21123</v>
+        <v>21207</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03613075670048244</v>
+        <v>0.03591877549952326</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.5506</v>
+        <v>0.5444</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="R12" s="15" t="inlineStr">
         <is>
@@ -1411,19 +1411,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="G13" s="7" t="n">
         <v>114.3</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>113.76</v>
-      </c>
       <c r="H13" s="8" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0105</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>20574</v>
+        <v>20790</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.03519169570400633</v>
+        <v>0.03521249316900498</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3648</v>
+        <v>0.3506</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1480,19 +1480,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
+        <v>1.823</v>
+      </c>
+      <c r="G14" s="7" t="n">
         <v>1.789</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>1.758</v>
-      </c>
       <c r="H14" s="8" t="n">
-        <v>0.0176</v>
+        <v>0.019</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>21468</v>
+        <v>21876</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03672087699881442</v>
+        <v>0.03705187592905979</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1515</v>
+        <v>0.13</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>0.104</v>
+        <v>0.102</v>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         <v>35</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>573.75</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>574.3</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>569.65</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>0.008199999999999999</v>
+      <c r="H15" s="18" t="n">
+        <v>-0.001</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>20100.5</v>
+        <v>20081.25</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.03438177697571591</v>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
+        <v>0.03401206726551617</v>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1575,8 +1575,8 @@
       <c r="L15" s="7" t="n">
         <v>563.15</v>
       </c>
-      <c r="M15" s="19" t="n">
-        <v>-0.0194</v>
+      <c r="M15" s="20" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1622,21 +1622,21 @@
         <v>3</v>
       </c>
       <c r="F16" s="7" t="n">
+        <v>5662</v>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>5770</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>5662</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>0.0191</v>
+      <c r="H16" s="18" t="n">
+        <v>-0.0187</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>17310</v>
+        <v>16986</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.02960864453370028</v>
-      </c>
-      <c r="K16" s="18" t="inlineStr">
+        <v>0.02876957234096771</v>
+      </c>
+      <c r="K16" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1645,7 +1645,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.0722</v>
+        <v>0.0926</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         <v>26</v>
       </c>
       <c r="F17" s="7" t="n">
+        <v>798</v>
+      </c>
+      <c r="G17" s="7" t="n">
         <v>800.5</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>821.5</v>
-      </c>
-      <c r="H17" s="20" t="n">
-        <v>-0.0256</v>
+      <c r="H17" s="18" t="n">
+        <v>-0.0031</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>20813</v>
+        <v>20748</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.03560050367879283</v>
-      </c>
-      <c r="K17" s="18" t="inlineStr">
+        <v>0.03514135681916861</v>
+      </c>
+      <c r="K17" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1716,7 +1716,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1655</v>
+        <v>0.1692</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -1766,19 +1766,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>176.45</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>174.55</v>
-      </c>
       <c r="H18" s="8" t="n">
-        <v>0.0109</v>
+        <v>0.0017</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>21174</v>
+        <v>21210</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03621799187501847</v>
+        <v>0.03592385666736872</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3746</v>
+        <v>0.3723</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -1839,19 +1839,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="G19" s="7" t="n">
         <v>72.51000000000001</v>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>0.005699999999999999</v>
+      <c r="H19" s="18" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>22768.14</v>
+        <v>22466.7</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.03894475817178063</v>
+        <v>0.03805235787782993</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.1033</v>
+        <v>0.1181</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -1906,19 +1906,19 @@
         <v>30000</v>
       </c>
       <c r="F20" s="21" t="n">
+        <v>0.7104</v>
+      </c>
+      <c r="G20" s="21" t="n">
         <v>0.6942</v>
       </c>
-      <c r="G20" s="21" t="n">
-        <v>0.6754</v>
-      </c>
       <c r="H20" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.0233</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>20826</v>
+        <v>21312</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.03562274009583143</v>
+        <v>0.0360966163741142</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -1928,8 +1928,8 @@
       <c r="L20" s="21" t="n">
         <v>0.7</v>
       </c>
-      <c r="M20" s="12" t="n">
-        <v>0.008399999999999999</v>
+      <c r="M20" s="20" t="n">
+        <v>-0.0146</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="Q20" s="16" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="R20" s="15" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
         <v>160</v>
       </c>
       <c r="F21" s="7" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="G21" s="7" t="n">
         <v>76.44</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>74.48</v>
-      </c>
       <c r="H21" s="8" t="n">
-        <v>0.0263</v>
+        <v>0.0152</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>12230.4</v>
+        <v>12416</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.02092002114991149</v>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
+        <v>0.02102925998972419</v>
+      </c>
+      <c r="K21" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2002,7 +2002,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1549</v>
+        <v>0.1376</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2046,19 +2046,19 @@
         <v>370000</v>
       </c>
       <c r="F22" s="21" t="n">
+        <v>0.0644</v>
+      </c>
+      <c r="G22" s="21" t="n">
         <v>0.06144</v>
       </c>
-      <c r="G22" s="21" t="n">
-        <v>0.05812</v>
-      </c>
       <c r="H22" s="8" t="n">
-        <v>0.0571</v>
+        <v>0.0482</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>22732.8</v>
+        <v>23828</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.03888430932730801</v>
+        <v>0.04035802247383601</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -2109,21 +2109,21 @@
         <v>12</v>
       </c>
       <c r="F23" s="7" t="n">
+        <v>1130.8</v>
+      </c>
+      <c r="G23" s="7" t="n">
         <v>1098.2</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>1099</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>-0.0007000000000000001</v>
+      <c r="H23" s="8" t="n">
+        <v>0.0297</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>13178.4</v>
+        <v>13569.6</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.02254156910011067</v>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
+        <v>0.02298313839856325</v>
+      </c>
+      <c r="K23" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2132,7 +2132,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.2218</v>
+        <v>0.1866</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>0.111</v>
+        <v>0.108</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -2182,21 +2182,21 @@
         <v>340</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>35.95</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>35.35</v>
-      </c>
       <c r="H24" s="8" t="n">
-        <v>0.017</v>
+        <v>0.0011</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>12223</v>
+        <v>12236.6</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02090736349713567</v>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
+        <v>0.02072540615256596</v>
+      </c>
+      <c r="K24" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2205,7 +2205,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.1939</v>
+        <v>0.1926</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2255,19 +2255,19 @@
         <v>363</v>
       </c>
       <c r="F25" s="7" t="n">
+        <v>57.465</v>
+      </c>
+      <c r="G25" s="7" t="n">
         <v>56.94</v>
       </c>
-      <c r="G25" s="7" t="n">
-        <v>56.555</v>
-      </c>
       <c r="H25" s="8" t="n">
-        <v>0.0068</v>
+        <v>0.0092</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>20669.22</v>
+        <v>20859.8</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03535456890634596</v>
+        <v>0.03533071500754257</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5727</v>
+        <v>0.5583</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>0.171</v>
+        <v>0.169</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -2328,19 +2328,19 @@
         <v>30</v>
       </c>
       <c r="F26" s="7" t="n">
+        <v>490.1</v>
+      </c>
+      <c r="G26" s="7" t="n">
         <v>479</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>482.6</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <v>-0.0075</v>
+      <c r="H26" s="8" t="n">
+        <v>0.0232</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>14370</v>
+        <v>14703</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.02457979329574079</v>
+        <v>0.02490280361057625</v>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.121</v>
+        <v>0.118</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2397,21 +2397,21 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="G27" s="7" t="n">
         <v>43.05</v>
       </c>
-      <c r="G27" s="7" t="n">
-        <v>42.7</v>
-      </c>
       <c r="H27" s="8" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0046</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7318.5</v>
+        <v>7352.5</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.01251824754592059</v>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
+        <v>0.01245309552790328</v>
+      </c>
+      <c r="K27" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2419,8 +2419,8 @@
       <c r="L27" s="7" t="n">
         <v>42.5</v>
       </c>
-      <c r="M27" s="19" t="n">
-        <v>-0.0128</v>
+      <c r="M27" s="20" t="n">
+        <v>-0.0173</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2464,21 +2464,21 @@
         <v>160</v>
       </c>
       <c r="F28" s="7" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="G28" s="7" t="n">
         <v>41.7</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>40.3</v>
-      </c>
       <c r="H28" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.036</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>6672</v>
+        <v>6912</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.01141241342165501</v>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
+        <v>0.01170701071592893</v>
+      </c>
+      <c r="K28" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2487,7 +2487,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.199</v>
+        <v>0.1574</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2522,14 +2522,14 @@
       <c r="G29" s="24" t="n"/>
       <c r="H29" s="24" t="n"/>
       <c r="I29" s="25" t="n">
-        <v>584626.5600000001</v>
+        <v>590415.45</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>0.4012489875632261</v>
+        <v>0.4027117438100599</v>
       </c>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>Срвзв. потенциал: +29.6% · Покупать 13 / Держать 10 / без прогноза 2</t>
+          <t>Срвзв. потенциал: +28.5% · Покупать 13 / Держать 10 / без прогноза 2</t>
         </is>
       </c>
       <c r="L29" s="28" t="n"/>
@@ -2564,15 +2564,15 @@
         <v>341.3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>921.61</v>
+        <v>930.83</v>
       </c>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="9" t="n">
-        <v>314545.49</v>
+        <v>317692.28</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.3824771168581927</v>
+        <v>0.3847625670238284</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -2627,15 +2627,15 @@
         <v>146.3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1725.1</v>
+        <v>1725.78</v>
       </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="9" t="n">
-        <v>252382.13</v>
+        <v>252481.61</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3068884867143687</v>
+        <v>0.3057848065741764</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>124196.8</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.1510192817802398</v>
+        <v>0.1504168737878837</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -2753,15 +2753,15 @@
         <v>789</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>166.37</v>
+        <v>166.43</v>
       </c>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="9" t="n">
-        <v>131265.93</v>
+        <v>131313.27</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.1596151146471989</v>
+        <v>0.1590357526141116</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
       <c r="G34" s="24" t="n"/>
       <c r="H34" s="24" t="n"/>
       <c r="I34" s="25" t="n">
-        <v>822390.35</v>
+        <v>825683.96</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>0.5644343208068876</v>
+        <v>0.5631841567960252</v>
       </c>
       <c r="K34" s="28" t="n"/>
       <c r="L34" s="28" t="n"/>
@@ -2849,7 +2849,7 @@
         <v>50000</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.03431669162988644</v>
+        <v>0.03410409939391491</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>50000</v>
       </c>
       <c r="J36" s="26" t="n">
-        <v>0.03431669162988644</v>
+        <v>0.03410409939391491</v>
       </c>
       <c r="K36" s="28" t="n"/>
       <c r="L36" s="28" t="n"/>
@@ -2924,7 +2924,7 @@
       <c r="G37" s="24" t="n"/>
       <c r="H37" s="24" t="n"/>
       <c r="I37" s="30" t="n">
-        <v>1457016.91</v>
+        <v>1466099.41</v>
       </c>
       <c r="J37" s="31" t="n">
         <v>1</v>
@@ -3016,12 +3016,12 @@
       <c r="G39" s="24" t="n"/>
       <c r="H39" s="24" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>2062016.91</v>
+        <v>2071099.41</v>
       </c>
       <c r="J39" s="31" t="n"/>
       <c r="K39" s="34" t="inlineStr">
         <is>
-          <t>ваш 1 457 017 ₽ + жены 605 000 ₽</t>
+          <t>ваш 1 466 099 ₽ + жены 605 000 ₽</t>
         </is>
       </c>
       <c r="L39" s="32" t="n"/>
@@ -3133,11 +3133,11 @@
       <c r="G42" s="32" t="n"/>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="30" t="n">
-        <v>1477401.74</v>
+        <v>1486484.24</v>
       </c>
       <c r="J42" s="34" t="inlineStr">
         <is>
-          <t>ликвидная часть: 1 457 017 ₽ + заблокировано 20 385 ₽</t>
+          <t>ликвидная часть: 1 466 099 ₽ + заблокировано 20 385 ₽</t>
         </is>
       </c>
       <c r="K42" s="32" t="n"/>
@@ -3182,7 +3182,7 @@
     <row r="1">
       <c r="B1" s="37" t="inlineStr">
         <is>
-          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 23.10.2026 (АВТООБНОВЛЕНИЕ)</t>
+          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 26.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +29.6% (без учёта дивидендов).</t>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +28.5% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="38" t="inlineStr">
         <is>
-          <t>• Дивиденды за 12 месяцев (факт): ≈ 58 341 ₽ — 4.0% годовых на портфель.</t>
+          <t>• Дивиденды за 12 месяцев (факт): ≈ 58 341 ₽ — 3.98% годовых на портфель.</t>
         </is>
       </c>
     </row>
@@ -3245,28 +3245,28 @@
     <row r="13" ht="45" customHeight="1">
       <c r="B13" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Флагманский»: пай 921.61 ₽ (22.10.2026); 1 мес +4.68%  1 год +5.69%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
+          <t>• ОПИФ «Флагманский»: пай 930.83 ₽ (23.10.2026); 1 мес +5.13%  1 год +8.19%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>• ОПИФ «Рублевые перспективы»: пай 1 725.10 ₽ (22.10.2026); 1 мес +0.62%  1 год +16.08%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+          <t>• ОПИФ «Рублевые перспективы»: пай 1 725.78 ₽ (23.10.2026); 1 мес +0.7%  1 год +16.49%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="B15" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.56 ₽ (22.10.2026); 1 мес +1.11%  1 год +15.37%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.56 ₽ (23.10.2026); 1 мес +1.11%  1 год +15.41%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="38" t="inlineStr">
         <is>
-          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.37 ₽ (22.10.2026); 1 мес +1.05%  1 год +14.61%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → позиция 789 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.43 ₽ (23.10.2026); 1 мес +1.05%  1 год +14.6%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → позиция 789 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>• Семейный итог (ликвидный): 2 062 017 ₽ = ваш 1 457 017 ₽ + 605 000 ₽.</t>
+          <t>• Семейный итог (ликвидный): 2 071 099 ₽ = ваш 1 466 099 ₽ + 605 000 ₽.</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="38" t="inlineStr">
         <is>
-          <t>• Итого с учётом заблокированных: 1 477 402 ₽ (ликвидная часть 1 457 017 ₽).</t>
+          <t>• Итого с учётом заблокированных: 1 486 484 ₽ (ликвидная часть 1 466 099 ₽).</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="38" t="inlineStr">
         <is>
-          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (23.10.2026, закрытие 22.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
+          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (26.10.2026, закрытие 23.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Портфель и прогнозы" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Сводка и макропрогнозы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Остатки по дням" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Сводка и макропрогнозы" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,12 +68,12 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -102,8 +103,12 @@
       <color rgb="001F3864"/>
       <sz val="12"/>
     </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -140,6 +145,11 @@
         <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFBFD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -167,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -202,11 +212,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -237,6 +247,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -315,6 +340,363 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Динамика остатков: помесячно с 03.2023 (на 1-е число) + ежедневно, ₽</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Остатки по дням'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="A855F7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A855F7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Остатки по дням'!$A$5:$A$57</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Остатки по дням'!$B$5:$B$57</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Остатки по дням'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="2563EB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2563EB"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Остатки по дням'!$A$5:$A$57</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Остатки по дням'!$C$5:$C$57</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Остатки по дням'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="16A34A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="16A34A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Остатки по дням'!$A$5:$A$57</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Остатки по дням'!$D$5:$D$57</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Остатки по дням'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="F59E0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="F59E0B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Остатки по дням'!$A$5:$A$57</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Остатки по дням'!$E$5:$E$57</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Остатки по дням'!F4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="111827"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="111827"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Остатки по дням'!$A$5:$A$57</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Остатки по дням'!$F$5:$F$57</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Остатки по дням'!I4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="DC2626"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="DC2626"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Остатки по дням'!$A$5:$A$57</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Остатки по дням'!$I$5:$I$57</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Дата</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>₽</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10800000" cy="5040000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -633,14 +1015,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 26.10.2026 (автообновление)</t>
+          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 27.10.2026 (автообновление)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (26.10.2026, закрытие 23.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
+          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (27.10.2026, закрытие 26.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
         </is>
       </c>
     </row>
@@ -672,12 +1054,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Текущая цена, ₽ (26.10.2026)</t>
+          <t>Текущая цена, ₽ (27.10.2026)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Цена за пред. торг. день, ₽ (23.10.2026)</t>
+          <t>Цена за пред. торг. день, ₽ (26.10.2026)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -764,19 +1146,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
+        <v>298.18</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>296</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>292.32</v>
-      </c>
       <c r="H4" s="8" t="n">
-        <v>0.0126</v>
+        <v>0.0074</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>47360</v>
+        <v>47708.8</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.08021470305358711</v>
+        <v>0.07611602767534147</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -787,7 +1169,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.2818</v>
+        <v>0.2724</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -805,7 +1187,7 @@
         </is>
       </c>
       <c r="Q4" s="16" t="n">
-        <v>0.127</v>
+        <v>0.126</v>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
@@ -837,19 +1219,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
+        <v>3529.5</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>3471.5</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>3400</v>
-      </c>
       <c r="H5" s="8" t="n">
-        <v>0.021</v>
+        <v>0.0167</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>41658</v>
+        <v>42354</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.0705570967019918</v>
+        <v>0.06757282170503999</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -860,7 +1242,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.6755</v>
+        <v>0.648</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -878,7 +1260,7 @@
         </is>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="R5" s="15" t="inlineStr">
         <is>
@@ -910,19 +1292,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
+        <v>276.98</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>273.82</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>269.66</v>
-      </c>
       <c r="H6" s="8" t="n">
-        <v>0.0154</v>
+        <v>0.0115</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>43811.2</v>
+        <v>44316.8</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.07420402023693655</v>
+        <v>0.07070433075832074</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -933,7 +1315,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.5044</v>
+        <v>0.4872</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -947,7 +1329,7 @@
         </is>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="R6" s="15" t="inlineStr">
         <is>
@@ -979,19 +1361,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
+        <v>2353.5</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>2288</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>2278.5</v>
-      </c>
       <c r="H7" s="8" t="n">
-        <v>0.0042</v>
+        <v>0.0286</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>45760</v>
+        <v>47070</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.07750474686934429</v>
+        <v>0.07509686730075631</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1002,7 +1384,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.2506</v>
+        <v>0.2158</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1020,7 +1402,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.268</v>
+        <v>0.26</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1052,21 +1434,21 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>114.36</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>114.75</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>-0.0034</v>
+      <c r="H8" s="8" t="n">
+        <v>0.0253</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>30877.2</v>
+        <v>31657.5</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.05229741193256376</v>
-      </c>
-      <c r="K8" s="19" t="inlineStr">
+        <v>0.05050730989109184</v>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1075,7 +1457,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.2285</v>
+        <v>0.1982</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1119,19 +1501,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
+        <v>6341.5</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <v>6165.5</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>6144.5</v>
-      </c>
       <c r="H9" s="8" t="n">
-        <v>0.0034</v>
+        <v>0.0285</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>24662</v>
+        <v>25366</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.04177058713487258</v>
+        <v>0.04046966509349871</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1141,8 +1523,8 @@
       <c r="L9" s="7" t="n">
         <v>6221.5</v>
       </c>
-      <c r="M9" s="12" t="n">
-        <v>0.0091</v>
+      <c r="M9" s="19" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1160,7 +1542,7 @@
         </is>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>0.109</v>
+        <v>0.106</v>
       </c>
       <c r="R9" s="15" t="inlineStr">
         <is>
@@ -1192,21 +1574,21 @@
         <v>170</v>
       </c>
       <c r="F10" s="7" t="n">
+        <v>163.14</v>
+      </c>
+      <c r="G10" s="7" t="n">
         <v>157.62</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>155.37</v>
-      </c>
       <c r="H10" s="8" t="n">
-        <v>0.0145</v>
+        <v>0.035</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>26795.4</v>
+        <v>27733.8</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.04538397496203733</v>
-      </c>
-      <c r="K10" s="19" t="inlineStr">
+        <v>0.04424732310061005</v>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1215,7 +1597,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.2535</v>
+        <v>0.211</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1233,7 +1615,7 @@
         </is>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>0.124</v>
+        <v>0.12</v>
       </c>
       <c r="R10" s="15" t="inlineStr">
         <is>
@@ -1265,19 +1647,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="7" t="n">
+        <v>1073</v>
+      </c>
+      <c r="G11" s="7" t="n">
         <v>1066.8</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>1062.6</v>
-      </c>
       <c r="H11" s="8" t="n">
-        <v>0.004</v>
+        <v>0.0058</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>30937.2</v>
+        <v>31117</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.05239903528947287</v>
+        <v>0.04964498023789322</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1670,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.4061</v>
+        <v>0.3979</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1306,7 +1688,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.191</v>
+        <v>0.19</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1338,19 +1720,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
+        <v>3635</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>3534.5</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>3520.5</v>
-      </c>
       <c r="H12" s="8" t="n">
-        <v>0.004</v>
+        <v>0.0284</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>21207</v>
+        <v>21810</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03591877549952326</v>
+        <v>0.03479631773591449</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1361,7 +1743,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.5444</v>
+        <v>0.5017</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1379,7 +1761,7 @@
         </is>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="R12" s="15" t="inlineStr">
         <is>
@@ -1411,19 +1793,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
+        <v>115.86</v>
+      </c>
+      <c r="G13" s="7" t="n">
         <v>115.5</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>114.3</v>
-      </c>
       <c r="H13" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.0031</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>20790</v>
+        <v>20854.8</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.03521249316900498</v>
+        <v>0.03327236346258365</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1434,7 +1816,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3506</v>
+        <v>0.3465</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1483,16 +1865,16 @@
         <v>1.823</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1.789</v>
+        <v>1.823</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>21876</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03705187592905979</v>
+        <v>0.03490161608394615</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1553,21 +1935,21 @@
         <v>35</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>573.35</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>573.75</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>574.3</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>-0.001</v>
+      <c r="H15" s="20" t="n">
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>20081.25</v>
+        <v>20067.25</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.03401206726551617</v>
-      </c>
-      <c r="K15" s="19" t="inlineStr">
+        <v>0.03201588294754838</v>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1575,8 +1957,8 @@
       <c r="L15" s="7" t="n">
         <v>563.15</v>
       </c>
-      <c r="M15" s="20" t="n">
-        <v>-0.0185</v>
+      <c r="M15" s="19" t="n">
+        <v>-0.0178</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1619,24 +2001,24 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="7" t="n">
+        <v>5683</v>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>5662</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>5770</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>-0.0187</v>
+      <c r="H16" s="8" t="n">
+        <v>0.0037</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>16986</v>
+        <v>22732</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.02876957234096771</v>
-      </c>
-      <c r="K16" s="19" t="inlineStr">
+        <v>0.03626730374932637</v>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1645,7 +2027,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.0926</v>
+        <v>0.0886</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -1693,21 +2075,21 @@
         <v>26</v>
       </c>
       <c r="F17" s="7" t="n">
+        <v>801</v>
+      </c>
+      <c r="G17" s="7" t="n">
         <v>798</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>800.5</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>-0.0031</v>
+      <c r="H17" s="8" t="n">
+        <v>0.0038</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>20748</v>
+        <v>20826</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.03514135681916861</v>
-      </c>
-      <c r="K17" s="19" t="inlineStr">
+        <v>0.03322641509253348</v>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1716,7 +2098,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1692</v>
+        <v>0.1648</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -1766,19 +2148,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>176.75</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>176.45</v>
-      </c>
       <c r="H18" s="8" t="n">
-        <v>0.0017</v>
+        <v>0.0008</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>21210</v>
+        <v>21228</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03592385666736872</v>
+        <v>0.03386777775781719</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -1789,7 +2171,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3723</v>
+        <v>0.3711</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -1839,19 +2221,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="G19" s="7" t="n">
         <v>71.55</v>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>72.51000000000001</v>
-      </c>
-      <c r="H19" s="18" t="n">
-        <v>-0.0132</v>
+      <c r="H19" s="20" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>22466.7</v>
+        <v>22435.3</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.03805235787782993</v>
+        <v>0.03579393981203862</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -1862,7 +2244,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.1181</v>
+        <v>0.1197</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -1906,19 +2288,19 @@
         <v>30000</v>
       </c>
       <c r="F20" s="21" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="G20" s="21" t="n">
         <v>0.7104</v>
       </c>
-      <c r="G20" s="21" t="n">
-        <v>0.6942</v>
-      </c>
       <c r="H20" s="8" t="n">
-        <v>0.0233</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>21312</v>
+        <v>21450</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.0360966163741142</v>
+        <v>0.03422196311028729</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -1928,8 +2310,8 @@
       <c r="L20" s="21" t="n">
         <v>0.7</v>
       </c>
-      <c r="M20" s="20" t="n">
-        <v>-0.0146</v>
+      <c r="M20" s="19" t="n">
+        <v>-0.021</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -1976,24 +2358,24 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="F21" s="7" t="n">
+        <v>76.22</v>
+      </c>
+      <c r="G21" s="7" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>76.44</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>0.0152</v>
+      <c r="H21" s="20" t="n">
+        <v>-0.0178</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>12416</v>
+        <v>20579.4</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.02102925998972419</v>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
+        <v>0.03283298217397885</v>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2002,7 +2384,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1376</v>
+        <v>0.1582</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2046,19 +2428,19 @@
         <v>370000</v>
       </c>
       <c r="F22" s="21" t="n">
+        <v>0.06551999999999999</v>
+      </c>
+      <c r="G22" s="21" t="n">
         <v>0.0644</v>
       </c>
-      <c r="G22" s="21" t="n">
-        <v>0.06144</v>
-      </c>
       <c r="H22" s="8" t="n">
-        <v>0.0482</v>
+        <v>0.0174</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>23828</v>
+        <v>24242.4</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.04035802247383601</v>
+        <v>0.0386770404897356</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -2106,24 +2488,24 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F23" s="7" t="n">
+        <v>1112.4</v>
+      </c>
+      <c r="G23" s="7" t="n">
         <v>1130.8</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>1098.2</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>0.0297</v>
+      <c r="H23" s="20" t="n">
+        <v>-0.0163</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>13569.6</v>
+        <v>15573.6</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.02298313839856325</v>
-      </c>
-      <c r="K23" s="19" t="inlineStr">
+        <v>0.02484658110463264</v>
+      </c>
+      <c r="K23" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2132,7 +2514,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.1866</v>
+        <v>0.2062</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2150,7 +2532,7 @@
         </is>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>0.108</v>
+        <v>0.11</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -2182,21 +2564,21 @@
         <v>340</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>35.99</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>35.95</v>
-      </c>
       <c r="H24" s="8" t="n">
-        <v>0.0011</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>12236.6</v>
+        <v>12753.4</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02072540615256596</v>
-      </c>
-      <c r="K24" s="19" t="inlineStr">
+        <v>0.02034715078464979</v>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2205,7 +2587,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.1926</v>
+        <v>0.1442</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2223,7 +2605,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.147</v>
+        <v>0.141</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2255,19 +2637,19 @@
         <v>363</v>
       </c>
       <c r="F25" s="7" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="G25" s="7" t="n">
         <v>57.465</v>
       </c>
-      <c r="G25" s="7" t="n">
-        <v>56.94</v>
-      </c>
       <c r="H25" s="8" t="n">
-        <v>0.0092</v>
+        <v>0.0105</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>20859.8</v>
+        <v>21079.41</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03533071500754257</v>
+        <v>0.03363071288608956</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2278,7 +2660,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5583</v>
+        <v>0.5421</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2296,7 +2678,7 @@
         </is>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>0.169</v>
+        <v>0.167</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -2325,22 +2707,22 @@
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>490.1</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>479</v>
+        <v>490.1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0232</v>
+        <v>0</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>14703</v>
+        <v>19604</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.02490280361057625</v>
+        <v>0.03127680022443226</v>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
@@ -2397,21 +2779,21 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G27" s="7" t="n">
         <v>43.25</v>
       </c>
-      <c r="G27" s="7" t="n">
-        <v>43.05</v>
-      </c>
       <c r="H27" s="8" t="n">
-        <v>0.0046</v>
+        <v>0.0104</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7352.5</v>
+        <v>7429</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.01245309552790328</v>
-      </c>
-      <c r="K27" s="19" t="inlineStr">
+        <v>0.01185244587162351</v>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2419,8 +2801,8 @@
       <c r="L27" s="7" t="n">
         <v>42.5</v>
       </c>
-      <c r="M27" s="20" t="n">
-        <v>-0.0173</v>
+      <c r="M27" s="19" t="n">
+        <v>-0.0275</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2461,24 +2843,24 @@
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>160</v>
+        <v>340</v>
       </c>
       <c r="F28" s="7" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G28" s="7" t="n">
         <v>43.2</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>41.7</v>
-      </c>
       <c r="H28" s="8" t="n">
-        <v>0.036</v>
+        <v>0.0162</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>6912</v>
+        <v>14926</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.01170701071592893</v>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
+        <v>0.02381338095030993</v>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2487,7 +2869,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.1574</v>
+        <v>0.139</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2522,14 +2904,14 @@
       <c r="G29" s="24" t="n"/>
       <c r="H29" s="24" t="n"/>
       <c r="I29" s="25" t="n">
-        <v>590415.45</v>
+        <v>626790.46</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>0.4027117438100599</v>
+        <v>0.4248175838876356</v>
       </c>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>Срвзв. потенциал: +28.5% · Покупать 13 / Держать 10 / без прогноза 2</t>
+          <t>Срвзв. потенциал: +26.4% · Покупать 13 / Держать 10 / без прогноза 2</t>
         </is>
       </c>
       <c r="L29" s="28" t="n"/>
@@ -2564,15 +2946,15 @@
         <v>341.3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>930.83</v>
+        <v>935.34</v>
       </c>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="9" t="n">
-        <v>317692.28</v>
+        <v>319231.54</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.3847625670238284</v>
+        <v>0.3997169952716098</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -2627,15 +3009,15 @@
         <v>146.3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1725.78</v>
+        <v>1727.59</v>
       </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="9" t="n">
-        <v>252481.61</v>
+        <v>252746.42</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3057848065741764</v>
+        <v>0.3164694803278407</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -2690,15 +3072,15 @@
         <v>8530</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>14.56</v>
+        <v>14.58</v>
       </c>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="9" t="n">
-        <v>124196.8</v>
+        <v>124367.4</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.1504168737878837</v>
+        <v>0.1557232203238515</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -2750,18 +3132,18 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>789</v>
+        <v>614</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>166.43</v>
+        <v>166.61</v>
       </c>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="9" t="n">
-        <v>131313.27</v>
+        <v>102298.54</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.1590357526141116</v>
+        <v>0.128090304076698</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2789,7 +3171,7 @@
       </c>
       <c r="S33" s="17" t="inlineStr">
         <is>
-          <t>Доходность ≈ ставка денежного рынка ON минус расходы (~13,5% годовых); за 1 год +14,7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161,06 ₽; 08.10.2026 докуплено 180 паев по ~165,57 ₽; 12.10.2026 докуплено 220 паев по ~165,84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → позиция 789 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>Доходность ≈ ставка денежного рынка ON минус расходы (~13,5% годовых); за 1 год +14,7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161,06 ₽; 08.10.2026 докуплено 180 паев по ~165,57 ₽; 12.10.2026 докуплено 220 паев по ~165,84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → 27.10.2026 продано ещё 175 паев → позиция 614 паев (средняя цена покупки 166,67 ₽ по данным приложения). Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -2807,10 +3189,10 @@
       <c r="G34" s="24" t="n"/>
       <c r="H34" s="24" t="n"/>
       <c r="I34" s="25" t="n">
-        <v>825683.96</v>
+        <v>798643.9</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>0.5631841567960252</v>
+        <v>0.5412940905076929</v>
       </c>
       <c r="K34" s="28" t="n"/>
       <c r="L34" s="28" t="n"/>
@@ -2849,7 +3231,7 @@
         <v>50000</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.03410409939391491</v>
+        <v>0.03388832560467143</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2898,7 +3280,7 @@
         <v>50000</v>
       </c>
       <c r="J36" s="26" t="n">
-        <v>0.03410409939391491</v>
+        <v>0.03388832560467143</v>
       </c>
       <c r="K36" s="28" t="n"/>
       <c r="L36" s="28" t="n"/>
@@ -2924,7 +3306,7 @@
       <c r="G37" s="24" t="n"/>
       <c r="H37" s="24" t="n"/>
       <c r="I37" s="30" t="n">
-        <v>1466099.41</v>
+        <v>1475434.36</v>
       </c>
       <c r="J37" s="31" t="n">
         <v>1</v>
@@ -3016,12 +3398,12 @@
       <c r="G39" s="24" t="n"/>
       <c r="H39" s="24" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>2071099.41</v>
+        <v>2080434.36</v>
       </c>
       <c r="J39" s="31" t="n"/>
       <c r="K39" s="34" t="inlineStr">
         <is>
-          <t>ваш 1 466 099 ₽ + жены 605 000 ₽</t>
+          <t>ваш 1 475 434 ₽ + жены 605 000 ₽</t>
         </is>
       </c>
       <c r="L39" s="32" t="n"/>
@@ -3133,11 +3515,11 @@
       <c r="G42" s="32" t="n"/>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="30" t="n">
-        <v>1486484.24</v>
+        <v>1495819.19</v>
       </c>
       <c r="J42" s="34" t="inlineStr">
         <is>
-          <t>ликвидная часть: 1 466 099 ₽ + заблокировано 20 385 ₽</t>
+          <t>ликвидная часть: 1 475 434 ₽ + заблокировано 20 385 ₽</t>
         </is>
       </c>
       <c r="K42" s="32" t="n"/>
@@ -3172,6 +3554,1753 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="66" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Учёт ежедневных остатков — Акции, Фонды, Счета, Сэйв жены (обновлено: 2026-10-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>Помесячные остатки на 1-е число за 03.2023–09.2026 — данные пользователя: «Сэйв жены», «Тинькоф — акции», «IH+БКС — фонды» (IH и БКС суммируются); кэш и заблокированные в эти месяцы не указаны, «Итого» = акции + фонды. Записи добавляются ежедневно в 18:40 МСК (GitHub Actions) и при ручных обновлениях. Категории: Акции (25 бумаг), Фонды (4 пифа), Счета — денежный остаток «Сэйв» Яндекс Банка, Сэйв жены — пенсионный счёт (семейный блок, входит только в «Семейный итог»). Заблокированные активы (Barrick, 6 шт) — справочно, вне ликвидного итога. Не учитываются: PINS-RM, FIVE, остатки на брокерском счёте Т-Банка (−4 091,15 ₽ и 2,82 $). История до 21.10 восстановлена из git-истории portfolio_data.json; 17–20.10 пересчитаны по фактическим остаткам (регрессия публикации 16.10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Сэйв жены, ₽</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Тинькоф — акции, ₽</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>IH+БКС — фонды, ₽</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Счета (кэш), ₽</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО портфель, ₽</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Заблокировано, ₽</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Итого с заблокир., ₽</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Семейный итог, ₽</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Примечание / источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>01.03.2023</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>187000</v>
+      </c>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="38" t="n">
+        <v>377000</v>
+      </c>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="38" t="n">
+        <v>427000</v>
+      </c>
+      <c r="J5" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>01.04.2023</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C6" s="41" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D6" s="41" t="n">
+        <v>187000</v>
+      </c>
+      <c r="E6" s="41" t="n"/>
+      <c r="F6" s="42" t="n">
+        <v>377000</v>
+      </c>
+      <c r="G6" s="41" t="n"/>
+      <c r="H6" s="41" t="n"/>
+      <c r="I6" s="42" t="n">
+        <v>437000</v>
+      </c>
+      <c r="J6" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>01.05.2023</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>187000</v>
+      </c>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="38" t="n">
+        <v>377000</v>
+      </c>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="38" t="n">
+        <v>447000</v>
+      </c>
+      <c r="J7" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>01.06.2023</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="n">
+        <v>75000</v>
+      </c>
+      <c r="C8" s="41" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D8" s="41" t="n">
+        <v>187000</v>
+      </c>
+      <c r="E8" s="41" t="n"/>
+      <c r="F8" s="42" t="n">
+        <v>377000</v>
+      </c>
+      <c r="G8" s="41" t="n"/>
+      <c r="H8" s="41" t="n"/>
+      <c r="I8" s="42" t="n">
+        <v>452000</v>
+      </c>
+      <c r="J8" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>01.07.2023</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>187000</v>
+      </c>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="38" t="n">
+        <v>377000</v>
+      </c>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="38" t="n">
+        <v>457000</v>
+      </c>
+      <c r="J9" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>01.08.2023</t>
+        </is>
+      </c>
+      <c r="B10" s="41" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C10" s="41" t="n">
+        <v>195000</v>
+      </c>
+      <c r="D10" s="41" t="n">
+        <v>190000</v>
+      </c>
+      <c r="E10" s="41" t="n"/>
+      <c r="F10" s="42" t="n">
+        <v>385000</v>
+      </c>
+      <c r="G10" s="41" t="n"/>
+      <c r="H10" s="41" t="n"/>
+      <c r="I10" s="42" t="n">
+        <v>485000</v>
+      </c>
+      <c r="J10" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>01.09.2023</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>195000</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>190000</v>
+      </c>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="38" t="n">
+        <v>385000</v>
+      </c>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="38" t="n">
+        <v>505000</v>
+      </c>
+      <c r="J11" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>01.10.2023</t>
+        </is>
+      </c>
+      <c r="B12" s="41" t="n">
+        <v>140000</v>
+      </c>
+      <c r="C12" s="41" t="n">
+        <v>198000</v>
+      </c>
+      <c r="D12" s="41" t="n">
+        <v>190000</v>
+      </c>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="42" t="n">
+        <v>388000</v>
+      </c>
+      <c r="G12" s="41" t="n"/>
+      <c r="H12" s="41" t="n"/>
+      <c r="I12" s="42" t="n">
+        <v>528000</v>
+      </c>
+      <c r="J12" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>01.11.2023</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>194232</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>188409</v>
+      </c>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="38" t="n">
+        <v>382641</v>
+      </c>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="38" t="n">
+        <v>532641</v>
+      </c>
+      <c r="J13" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>01.12.2023</t>
+        </is>
+      </c>
+      <c r="B14" s="41" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C14" s="41" t="n">
+        <v>195822</v>
+      </c>
+      <c r="D14" s="41" t="n">
+        <v>188409</v>
+      </c>
+      <c r="E14" s="41" t="n"/>
+      <c r="F14" s="42" t="n">
+        <v>384231</v>
+      </c>
+      <c r="G14" s="41" t="n"/>
+      <c r="H14" s="41" t="n"/>
+      <c r="I14" s="42" t="n">
+        <v>534231</v>
+      </c>
+      <c r="J14" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>01.01.2024</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>220000</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>199407</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>188409</v>
+      </c>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="38" t="n">
+        <v>387816</v>
+      </c>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="38" t="n">
+        <v>607816</v>
+      </c>
+      <c r="J15" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>01.02.2024</t>
+        </is>
+      </c>
+      <c r="B16" s="41" t="n">
+        <v>110000</v>
+      </c>
+      <c r="C16" s="41" t="n">
+        <v>200786</v>
+      </c>
+      <c r="D16" s="41" t="n">
+        <v>188409</v>
+      </c>
+      <c r="E16" s="41" t="n"/>
+      <c r="F16" s="42" t="n">
+        <v>389195</v>
+      </c>
+      <c r="G16" s="41" t="n"/>
+      <c r="H16" s="41" t="n"/>
+      <c r="I16" s="42" t="n">
+        <v>499195</v>
+      </c>
+      <c r="J16" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>01.03.2024</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>110000</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>313059</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>190747</v>
+      </c>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="38" t="n">
+        <v>503806</v>
+      </c>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="38" t="n">
+        <v>613806</v>
+      </c>
+      <c r="J17" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>01.04.2024</t>
+        </is>
+      </c>
+      <c r="B18" s="41" t="n">
+        <v>110000</v>
+      </c>
+      <c r="C18" s="41" t="n">
+        <v>384361</v>
+      </c>
+      <c r="D18" s="41" t="n">
+        <v>344588</v>
+      </c>
+      <c r="E18" s="41" t="n"/>
+      <c r="F18" s="42" t="n">
+        <v>728949</v>
+      </c>
+      <c r="G18" s="41" t="n"/>
+      <c r="H18" s="41" t="n"/>
+      <c r="I18" s="42" t="n">
+        <v>838949</v>
+      </c>
+      <c r="J18" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>01.05.2024</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>256990</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>567974</v>
+      </c>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="38" t="n">
+        <v>824964</v>
+      </c>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="38" t="n">
+        <v>974964</v>
+      </c>
+      <c r="J19" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t>01.06.2024</t>
+        </is>
+      </c>
+      <c r="B20" s="41" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C20" s="41" t="n">
+        <v>118601</v>
+      </c>
+      <c r="D20" s="41" t="n">
+        <v>608474</v>
+      </c>
+      <c r="E20" s="41" t="n"/>
+      <c r="F20" s="42" t="n">
+        <v>727075</v>
+      </c>
+      <c r="G20" s="41" t="n"/>
+      <c r="H20" s="41" t="n"/>
+      <c r="I20" s="42" t="n">
+        <v>877075</v>
+      </c>
+      <c r="J20" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>01.07.2024</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>110212</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>581385</v>
+      </c>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="38" t="n">
+        <v>691597</v>
+      </c>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="38" t="n">
+        <v>841597</v>
+      </c>
+      <c r="J21" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>01.08.2024</t>
+        </is>
+      </c>
+      <c r="B22" s="41" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C22" s="41" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D22" s="41" t="n">
+        <v>642877</v>
+      </c>
+      <c r="E22" s="41" t="n"/>
+      <c r="F22" s="42" t="n">
+        <v>707877</v>
+      </c>
+      <c r="G22" s="41" t="n"/>
+      <c r="H22" s="41" t="n"/>
+      <c r="I22" s="42" t="n">
+        <v>807877</v>
+      </c>
+      <c r="J22" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>01.09.2024</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>671000</v>
+      </c>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="38" t="n">
+        <v>736000</v>
+      </c>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="38" t="n">
+        <v>856000</v>
+      </c>
+      <c r="J23" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>01.10.2024</t>
+        </is>
+      </c>
+      <c r="B24" s="41" t="n">
+        <v>130000</v>
+      </c>
+      <c r="C24" s="41" t="n">
+        <v>59000</v>
+      </c>
+      <c r="D24" s="41" t="n">
+        <v>826800</v>
+      </c>
+      <c r="E24" s="41" t="n"/>
+      <c r="F24" s="42" t="n">
+        <v>885800</v>
+      </c>
+      <c r="G24" s="41" t="n"/>
+      <c r="H24" s="41" t="n"/>
+      <c r="I24" s="42" t="n">
+        <v>1015800</v>
+      </c>
+      <c r="J24" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>01.11.2024</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>140000</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>58000</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>886800</v>
+      </c>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="38" t="n">
+        <v>944800</v>
+      </c>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="38" t="n">
+        <v>1084800</v>
+      </c>
+      <c r="J25" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>01.12.2024</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="C26" s="41" t="n">
+        <v>82000</v>
+      </c>
+      <c r="D26" s="41" t="n">
+        <v>805000</v>
+      </c>
+      <c r="E26" s="41" t="n"/>
+      <c r="F26" s="42" t="n">
+        <v>887000</v>
+      </c>
+      <c r="G26" s="41" t="n"/>
+      <c r="H26" s="41" t="n"/>
+      <c r="I26" s="42" t="n">
+        <v>1127000</v>
+      </c>
+      <c r="J26" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>01.01.2025</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>240000</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>820000</v>
+      </c>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="38" t="n">
+        <v>905000</v>
+      </c>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="38" t="n">
+        <v>1145000</v>
+      </c>
+      <c r="J27" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>01.02.2025</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C28" s="41" t="n">
+        <v>47000</v>
+      </c>
+      <c r="D28" s="41" t="n">
+        <v>627000</v>
+      </c>
+      <c r="E28" s="41" t="n"/>
+      <c r="F28" s="42" t="n">
+        <v>674000</v>
+      </c>
+      <c r="G28" s="41" t="n"/>
+      <c r="H28" s="41" t="n"/>
+      <c r="I28" s="42" t="n">
+        <v>924000</v>
+      </c>
+      <c r="J28" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>01.03.2025</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>47596</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>647647</v>
+      </c>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="38" t="n">
+        <v>695243</v>
+      </c>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="38" t="n">
+        <v>945243</v>
+      </c>
+      <c r="J29" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>01.04.2025</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C30" s="41" t="n">
+        <v>55254</v>
+      </c>
+      <c r="D30" s="41" t="n">
+        <v>557125</v>
+      </c>
+      <c r="E30" s="41" t="n"/>
+      <c r="F30" s="42" t="n">
+        <v>612379</v>
+      </c>
+      <c r="G30" s="41" t="n"/>
+      <c r="H30" s="41" t="n"/>
+      <c r="I30" s="42" t="n">
+        <v>862379</v>
+      </c>
+      <c r="J30" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>01.05.2025</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>158000</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>402000</v>
+      </c>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="38" t="n">
+        <v>560000</v>
+      </c>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="38" t="n">
+        <v>810000</v>
+      </c>
+      <c r="J31" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>01.06.2025</t>
+        </is>
+      </c>
+      <c r="B32" s="41" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C32" s="41" t="n">
+        <v>260270</v>
+      </c>
+      <c r="D32" s="41" t="n">
+        <v>413000</v>
+      </c>
+      <c r="E32" s="41" t="n"/>
+      <c r="F32" s="42" t="n">
+        <v>673270</v>
+      </c>
+      <c r="G32" s="41" t="n"/>
+      <c r="H32" s="41" t="n"/>
+      <c r="I32" s="42" t="n">
+        <v>923270</v>
+      </c>
+      <c r="J32" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>01.07.2025</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>393000</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>422882</v>
+      </c>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="38" t="n">
+        <v>815882</v>
+      </c>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="38" t="n">
+        <v>1215882</v>
+      </c>
+      <c r="J33" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="40" t="inlineStr">
+        <is>
+          <t>01.08.2025</t>
+        </is>
+      </c>
+      <c r="B34" s="41" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C34" s="41" t="n">
+        <v>237000</v>
+      </c>
+      <c r="D34" s="41" t="n">
+        <v>641720</v>
+      </c>
+      <c r="E34" s="41" t="n"/>
+      <c r="F34" s="42" t="n">
+        <v>878720</v>
+      </c>
+      <c r="G34" s="41" t="n"/>
+      <c r="H34" s="41" t="n"/>
+      <c r="I34" s="42" t="n">
+        <v>1278720</v>
+      </c>
+      <c r="J34" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>01.09.2025</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>226800</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>641720</v>
+      </c>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="38" t="n">
+        <v>868520</v>
+      </c>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="38" t="n">
+        <v>1168520</v>
+      </c>
+      <c r="J35" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="40" t="inlineStr">
+        <is>
+          <t>01.10.2025</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C36" s="41" t="n">
+        <v>271000</v>
+      </c>
+      <c r="D36" s="41" t="n">
+        <v>616949</v>
+      </c>
+      <c r="E36" s="41" t="n"/>
+      <c r="F36" s="42" t="n">
+        <v>887949</v>
+      </c>
+      <c r="G36" s="41" t="n"/>
+      <c r="H36" s="41" t="n"/>
+      <c r="I36" s="42" t="n">
+        <v>1187949</v>
+      </c>
+      <c r="J36" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>01.11.2025</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>333000</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>632516</v>
+      </c>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="38" t="n">
+        <v>965516</v>
+      </c>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="38" t="n">
+        <v>1265516</v>
+      </c>
+      <c r="J37" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="40" t="inlineStr">
+        <is>
+          <t>01.12.2025</t>
+        </is>
+      </c>
+      <c r="B38" s="41" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C38" s="41" t="n">
+        <v>371636</v>
+      </c>
+      <c r="D38" s="41" t="n">
+        <v>641500</v>
+      </c>
+      <c r="E38" s="41" t="n"/>
+      <c r="F38" s="42" t="n">
+        <v>1013136</v>
+      </c>
+      <c r="G38" s="41" t="n"/>
+      <c r="H38" s="41" t="n"/>
+      <c r="I38" s="42" t="n">
+        <v>1313136</v>
+      </c>
+      <c r="J38" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>01.01.2026</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>436147</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>660148</v>
+      </c>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="38" t="n">
+        <v>1096295</v>
+      </c>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="9" t="n"/>
+      <c r="I39" s="38" t="n">
+        <v>1496295</v>
+      </c>
+      <c r="J39" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="40" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="B40" s="41" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C40" s="41" t="n">
+        <v>458213</v>
+      </c>
+      <c r="D40" s="41" t="n">
+        <v>666230</v>
+      </c>
+      <c r="E40" s="41" t="n"/>
+      <c r="F40" s="42" t="n">
+        <v>1124443</v>
+      </c>
+      <c r="G40" s="41" t="n"/>
+      <c r="H40" s="41" t="n"/>
+      <c r="I40" s="42" t="n">
+        <v>1524443</v>
+      </c>
+      <c r="J40" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>01.03.2026</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>528000</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>674900</v>
+      </c>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="38" t="n">
+        <v>1202900</v>
+      </c>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
+      <c r="I41" s="38" t="n">
+        <v>1602900</v>
+      </c>
+      <c r="J41" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="40" t="inlineStr">
+        <is>
+          <t>01.04.2026</t>
+        </is>
+      </c>
+      <c r="B42" s="41" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C42" s="41" t="n">
+        <v>537000</v>
+      </c>
+      <c r="D42" s="41" t="n">
+        <v>672500</v>
+      </c>
+      <c r="E42" s="41" t="n"/>
+      <c r="F42" s="42" t="n">
+        <v>1209500</v>
+      </c>
+      <c r="G42" s="41" t="n"/>
+      <c r="H42" s="41" t="n"/>
+      <c r="I42" s="42" t="n">
+        <v>1709500</v>
+      </c>
+      <c r="J42" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>01.05.2026</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>434000</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>675300</v>
+      </c>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="38" t="n">
+        <v>1109300</v>
+      </c>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="38" t="n">
+        <v>1509300</v>
+      </c>
+      <c r="J43" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="40" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+      <c r="B44" s="41" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C44" s="41" t="n">
+        <v>434693</v>
+      </c>
+      <c r="D44" s="41" t="n">
+        <v>659831</v>
+      </c>
+      <c r="E44" s="41" t="n"/>
+      <c r="F44" s="42" t="n">
+        <v>1094524</v>
+      </c>
+      <c r="G44" s="41" t="n"/>
+      <c r="H44" s="41" t="n"/>
+      <c r="I44" s="42" t="n">
+        <v>1494524</v>
+      </c>
+      <c r="J44" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>530000</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>439528</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>666833</v>
+      </c>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="38" t="n">
+        <v>1106361</v>
+      </c>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="38" t="n">
+        <v>1636361</v>
+      </c>
+      <c r="J45" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="40" t="inlineStr">
+        <is>
+          <t>01.08.2026</t>
+        </is>
+      </c>
+      <c r="B46" s="41" t="n">
+        <v>545000</v>
+      </c>
+      <c r="C46" s="41" t="n">
+        <v>451035</v>
+      </c>
+      <c r="D46" s="41" t="n">
+        <v>663167</v>
+      </c>
+      <c r="E46" s="41" t="n"/>
+      <c r="F46" s="42" t="n">
+        <v>1114202</v>
+      </c>
+      <c r="G46" s="41" t="n"/>
+      <c r="H46" s="41" t="n"/>
+      <c r="I46" s="42" t="n">
+        <v>1659202</v>
+      </c>
+      <c r="J46" s="43" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>593000</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>491400</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>670946</v>
+      </c>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="38" t="n">
+        <v>1162346</v>
+      </c>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="38" t="n">
+        <v>1755346</v>
+      </c>
+      <c r="J47" s="39" t="inlineStr">
+        <is>
+          <t>помесячные данные пользователя: остатки на 1-е число (Сэйв жены; Тинькоф — акции; IH+БКС — фонды; кэш не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="40" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="B48" s="41" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C48" s="41" t="n">
+        <v>547352.6800000001</v>
+      </c>
+      <c r="D48" s="41" t="n">
+        <v>710434.17</v>
+      </c>
+      <c r="E48" s="41" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F48" s="42" t="n">
+        <v>1437786.85</v>
+      </c>
+      <c r="G48" s="41" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H48" s="41" t="n">
+        <v>1458171.68</v>
+      </c>
+      <c r="I48" s="42" t="n">
+        <v>2042786.85</v>
+      </c>
+      <c r="J48" s="43" t="inlineStr">
+        <is>
+          <t>данные приложения Т-Банк от 14.10 (TMON 159 паев, кэш 180 тыс.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>547856.0699999999</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>711600.12</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F49" s="38" t="n">
+        <v>1439456.19</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>1459841.02</v>
+      </c>
+      <c r="I49" s="38" t="n">
+        <v>2044456.19</v>
+      </c>
+      <c r="J49" s="39" t="inlineStr">
+        <is>
+          <t>автообновление: закрытие MOEX 16.10; СЧА фондов на 15.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="40" t="inlineStr">
+        <is>
+          <t>17.10.2026</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C50" s="41" t="n">
+        <v>547856.0699999999</v>
+      </c>
+      <c r="D50" s="41" t="n">
+        <v>841048.92</v>
+      </c>
+      <c r="E50" s="41" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F50" s="42" t="n">
+        <v>1438904.99</v>
+      </c>
+      <c r="G50" s="41" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H50" s="41" t="n">
+        <v>1459289.82</v>
+      </c>
+      <c r="I50" s="42" t="n">
+        <v>2043904.99</v>
+      </c>
+      <c r="J50" s="43" t="inlineStr">
+        <is>
+          <t>перевод 130 000 ₽ с «Сэйва» → покупка 780 паев TMON (~165,96 ₽) → 939 паев; акции по закрытию 16.10, СЧА на 15.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>19.10.2026</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>550483.1800000001</v>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>844300.3199999999</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F51" s="38" t="n">
+        <v>1444783.5</v>
+      </c>
+      <c r="G51" s="9" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>1465168.33</v>
+      </c>
+      <c r="I51" s="38" t="n">
+        <v>2049783.5</v>
+      </c>
+      <c r="J51" s="39" t="inlineStr">
+        <is>
+          <t>пересчёт по фактическим остаткам (в публикации 16–20.10 были устаревшие кэш/TMON); СЧА на 16.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="40" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="B52" s="41" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C52" s="41" t="n">
+        <v>559315.34</v>
+      </c>
+      <c r="D52" s="41" t="n">
+        <v>846593</v>
+      </c>
+      <c r="E52" s="41" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F52" s="42" t="n">
+        <v>1455908.34</v>
+      </c>
+      <c r="G52" s="41" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H52" s="41" t="n">
+        <v>1476293.17</v>
+      </c>
+      <c r="I52" s="42" t="n">
+        <v>2060908.34</v>
+      </c>
+      <c r="J52" s="43" t="inlineStr">
+        <is>
+          <t>пересчёт по фактическим остаткам; СЧА на 19.10 (TMON — 16.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>582857.38</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>824893.0600000001</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F53" s="38" t="n">
+        <v>1457750.44</v>
+      </c>
+      <c r="G53" s="9" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>1478135.27</v>
+      </c>
+      <c r="I53" s="38" t="n">
+        <v>2062750.44</v>
+      </c>
+      <c r="J53" s="39" t="inlineStr">
+        <is>
+          <t>автообновление + данные приложения от 21.10: продано 150 паев TMON (→789), докупки SIBN 35, MOEX 170, PMSB 40, PLZL 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="40" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="B54" s="41" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C54" s="41" t="n">
+        <v>577168.52</v>
+      </c>
+      <c r="D54" s="41" t="n">
+        <v>823287.48</v>
+      </c>
+      <c r="E54" s="41" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F54" s="42" t="n">
+        <v>1450456</v>
+      </c>
+      <c r="G54" s="41" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H54" s="41" t="n">
+        <v>1470840.83</v>
+      </c>
+      <c r="I54" s="42" t="n">
+        <v>2055456</v>
+      </c>
+      <c r="J54" s="43" t="inlineStr">
+        <is>
+          <t>автообновление GitHub Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>584626.5600000001</v>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>822390.35</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F55" s="38" t="n">
+        <v>1457016.91</v>
+      </c>
+      <c r="G55" s="9" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>1477401.74</v>
+      </c>
+      <c r="I55" s="38" t="n">
+        <v>2062016.91</v>
+      </c>
+      <c r="J55" s="39" t="inlineStr">
+        <is>
+          <t>автообновление GitHub Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="40" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C56" s="41" t="n">
+        <v>590415.45</v>
+      </c>
+      <c r="D56" s="41" t="n">
+        <v>825683.96</v>
+      </c>
+      <c r="E56" s="41" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F56" s="42" t="n">
+        <v>1466099.41</v>
+      </c>
+      <c r="G56" s="41" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H56" s="41" t="n">
+        <v>1486484.24</v>
+      </c>
+      <c r="I56" s="42" t="n">
+        <v>2071099.41</v>
+      </c>
+      <c r="J56" s="43" t="inlineStr">
+        <is>
+          <t>автообновление GitHub Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>27.10.2026</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>626790.46</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>798643.9</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F57" s="38" t="n">
+        <v>1475434.36</v>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>1495819.19</v>
+      </c>
+      <c r="I57" s="38" t="n">
+        <v>2080434.36</v>
+      </c>
+      <c r="J57" s="39" t="inlineStr">
+        <is>
+          <t>автообновление GitHub Actions</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3180,154 +5309,154 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="37" t="inlineStr">
-        <is>
-          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 26.10.2026 (АВТООБНОВЛЕНИЕ)</t>
+      <c r="B1" s="44" t="inlineStr">
+        <is>
+          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 27.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="38" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>• Рекомендации: ПОКУПАТЬ — 13; ДЕРЖАТЬ — 10; ПРОДАВАТЬ — 0; без прогноза — 2 (FEES, PMSB).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="B3" s="38" t="inlineStr">
-        <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +28.5% (без учёта дивидендов).</t>
+      <c r="B3" s="45" t="inlineStr">
+        <is>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +26.4% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>ДИВИДЕНДЫ</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>• Ближайших утверждённых отсечек нет. Выплаты T, GMKN (12.10) и SIBN (13.10) зафиксированы и придут в конце октября — начале ноября.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="38" t="inlineStr">
-        <is>
-          <t>• Дивиденды за 12 месяцев (факт): ≈ 58 341 ₽ — 3.98% годовых на портфель.</t>
+      <c r="B7" s="45" t="inlineStr">
+        <is>
+          <t>• Дивиденды за 12 месяцев (факт): ≈ 59 165 ₽ — 4.01% годовых на портфель.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>МАКРО И СТРАТЕГИЯ</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="45" t="inlineStr">
         <is>
           <t>• IMOEX: 2 300–2 500 п. к концу 2026; 2 600–2 900 п. за 12 мес (Т-Инвестиции, 01.08.2026). Ключевая ставка: 14,00% (11.09.2026).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>ФОНДЫ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
-      <c r="B13" s="38" t="inlineStr">
-        <is>
-          <t>• ОПИФ «Флагманский»: пай 930.83 ₽ (23.10.2026); 1 мес +5.13%  1 год +8.19%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
+      <c r="B13" s="45" t="inlineStr">
+        <is>
+          <t>• ОПИФ «Флагманский»: пай 935.34 ₽ (26.10.2026); 1 мес +6.66%  1 год +9.01%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
-      <c r="B14" s="38" t="inlineStr">
-        <is>
-          <t>• ОПИФ «Рублевые перспективы»: пай 1 725.78 ₽ (23.10.2026); 1 мес +0.7%  1 год +16.49%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>• ОПИФ «Рублевые перспективы»: пай 1 727.59 ₽ (26.10.2026); 1 мес +0.93%  1 год +16.57%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
-      <c r="B15" s="38" t="inlineStr">
-        <is>
-          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.56 ₽ (23.10.2026); 1 мес +1.11%  1 год +15.41%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="B16" s="38" t="inlineStr">
-        <is>
-          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.43 ₽ (23.10.2026); 1 мес +1.05%  1 год +14.6%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → позиция 789 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+      <c r="B15" s="45" t="inlineStr">
+        <is>
+          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.58 ₽ (26.10.2026); 1 мес +1.15%  1 год +15.45%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="105" customHeight="1">
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.61 ₽ (26.10.2026); 1 мес +1.1%  1 год +14.69%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → 27.10.2026 продано ещё 175 паев → позиция 614 паев (средняя цена покупки 166 67 ₽ по данным приложения). Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>СЕМЕЙНЫЙ БЛОК (вне расчётов основного портфеля)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="45" t="inlineStr">
         <is>
           <t>• Сэйв — пенсионный счёт жены (Яндекс Банк): 605 000 ₽. Отдельный блок: не учитывается в долях  потенциале и дивидендных расчётах основного портфеля; входит только в семейный итог. Доходность — по тарифу «Сэйв» её аккаунта.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="38" t="inlineStr">
-        <is>
-          <t>• Семейный итог (ликвидный): 2 071 099 ₽ = ваш 1 466 099 ₽ + 605 000 ₽.</t>
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>• Семейный итог (ликвидный): 2 080 434 ₽ = ваш 1 475 434 ₽ + 605 000 ₽.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B22" s="44" t="inlineStr">
         <is>
           <t>ЗАБЛОКИРОВАННЫЕ АКТИВЫ</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="45" t="inlineStr">
         <is>
           <t>• Barrick Mining (Barrick Gold): 6 шт × 40.51 $ ≈ 20,385 ₽. Заморожен из-за санкционных/инфраструктурных ограничений: продажа и вывод недоступны, дивиденды не поступают. Оценка по цене 40,51 $ и курсу ЦБ 83.8675 ₽/$ (14.10.2026).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="38" t="inlineStr">
-        <is>
-          <t>• Итого с учётом заблокированных: 1 486 484 ₽ (ликвидная часть 1 466 099 ₽).</t>
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>• Итого с учётом заблокированных: 1 495 819 ₽ (ликвидная часть 1 475 434 ₽).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B26" s="44" t="inlineStr">
         <is>
           <t>ИСТОЧНИКИ</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="38" t="inlineStr">
-        <is>
-          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (26.10.2026, закрытие 23.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
+      <c r="B27" s="45" t="inlineStr">
+        <is>
+          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (27.10.2026, закрытие 26.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="38" t="inlineStr">
+      <c r="B28" s="45" t="inlineStr">
         <is>
           <t>⚠️ Материал информационный, не является индивидуальной инвестиционной рекомендацией.</t>
         </is>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -52,11 +52,15 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
@@ -70,10 +74,6 @@
     <font>
       <b val="1"/>
       <color rgb="009C6500"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -200,23 +200,23 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -394,12 +394,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$57</f>
+              <f>'Остатки по дням'!$A$5:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$B$5:$B$57</f>
+              <f>'Остатки по дням'!$B$5:$B$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -434,12 +434,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$57</f>
+              <f>'Остатки по дням'!$A$5:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$C$5:$C$57</f>
+              <f>'Остатки по дням'!$C$5:$C$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -474,12 +474,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$57</f>
+              <f>'Остатки по дням'!$A$5:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$D$5:$D$57</f>
+              <f>'Остатки по дням'!$D$5:$D$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -514,12 +514,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$57</f>
+              <f>'Остатки по дням'!$A$5:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$E$5:$E$57</f>
+              <f>'Остатки по дням'!$E$5:$E$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -554,12 +554,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$57</f>
+              <f>'Остатки по дням'!$A$5:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$F$5:$F$57</f>
+              <f>'Остатки по дням'!$F$5:$F$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -594,12 +594,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$57</f>
+              <f>'Остатки по дням'!$A$5:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$I$5:$I$57</f>
+              <f>'Остатки по дням'!$I$5:$I$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -678,7 +678,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10800000" cy="5040000"/>
@@ -988,7 +988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1015,14 +1015,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 27.10.2026 (автообновление)</t>
+          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 28.10.2026 (автообновление)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (27.10.2026, закрытие 26.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
+          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (28.10.2026, закрытие 27.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Текущая цена, ₽ (27.10.2026)</t>
+          <t>Текущая цена, ₽ (28.10.2026)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Цена за пред. торг. день, ₽ (26.10.2026)</t>
+          <t>Цена за пред. торг. день, ₽ (27.10.2026)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1146,19 +1146,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
+        <v>297.98</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>298.18</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>296</v>
-      </c>
       <c r="H4" s="8" t="n">
-        <v>0.0074</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>47708.8</v>
+        <v>47676.8</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.07611602767534147</v>
+        <v>0.069265167107838</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.2724</v>
+        <v>0.2732</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -1219,19 +1219,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
+        <v>3553.5</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>3529.5</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>3471.5</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>0.0167</v>
+      <c r="H5" s="18" t="n">
+        <v>0.0068</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>42354</v>
+        <v>42642</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.06757282170503999</v>
+        <v>0.06195057671262393</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.648</v>
+        <v>0.6368</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -1292,19 +1292,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
+        <v>277.58</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>276.98</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>273.82</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>0.0115</v>
+      <c r="H6" s="18" t="n">
+        <v>0.0022</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>44316.8</v>
+        <v>44412.8</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.07070433075832074</v>
+        <v>0.06452320654337095</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.4872</v>
+        <v>0.484</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -1361,19 +1361,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
+        <v>2347.5</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>2353.5</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>2288</v>
-      </c>
       <c r="H7" s="8" t="n">
-        <v>0.0286</v>
+        <v>-0.0025</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>47070</v>
+        <v>46950</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.07509686730075631</v>
+        <v>0.06820926731057861</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.2158</v>
+        <v>0.2189</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.26</v>
+        <v>0.261</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>117.25</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>114.36</v>
-      </c>
       <c r="H8" s="8" t="n">
-        <v>0.0253</v>
+        <v>-0.0038</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>31657.5</v>
+        <v>31536</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.05050730989109184</v>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
+        <v>0.04581570721845383</v>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1457,7 +1457,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.1982</v>
+        <v>0.2028</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1501,19 +1501,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
+        <v>6291.5</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <v>6341.5</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>6165.5</v>
-      </c>
       <c r="H9" s="8" t="n">
-        <v>0.0285</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>25366</v>
+        <v>25166</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.04046966509349871</v>
+        <v>0.03656132952370653</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1523,8 +1523,8 @@
       <c r="L9" s="7" t="n">
         <v>6221.5</v>
       </c>
-      <c r="M9" s="19" t="n">
-        <v>-0.0189</v>
+      <c r="M9" s="20" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="R9" s="15" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         <v>170</v>
       </c>
       <c r="F10" s="7" t="n">
+        <v>161.86</v>
+      </c>
+      <c r="G10" s="7" t="n">
         <v>163.14</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>157.62</v>
-      </c>
       <c r="H10" s="8" t="n">
-        <v>0.035</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>27733.8</v>
+        <v>27516.2</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.04424732310061005</v>
-      </c>
-      <c r="K10" s="18" t="inlineStr">
+        <v>0.03997571546690827</v>
+      </c>
+      <c r="K10" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1597,7 +1597,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.211</v>
+        <v>0.2206</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="R10" s="15" t="inlineStr">
         <is>
@@ -1647,19 +1647,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="7" t="n">
+        <v>1077.8</v>
+      </c>
+      <c r="G11" s="7" t="n">
         <v>1073</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>1066.8</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>0.0058</v>
+      <c r="H11" s="18" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>31117</v>
+        <v>31256.2</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.04964498023789322</v>
+        <v>0.04540921194702678</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.3979</v>
+        <v>0.3917</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.19</v>
+        <v>0.189</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1720,19 +1720,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
+        <v>3774</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>3635</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>3534.5</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>0.0284</v>
+      <c r="H12" s="18" t="n">
+        <v>0.0382</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>21810</v>
+        <v>22644</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03479631773591449</v>
+        <v>0.03289735141599025</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.5017</v>
+        <v>0.4464</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="R12" s="15" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="G13" s="7" t="n">
         <v>115.86</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>115.5</v>
-      </c>
       <c r="H13" s="8" t="n">
-        <v>0.0031</v>
+        <v>-0.0066</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>20854.8</v>
+        <v>20718</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.03327236346258365</v>
+        <v>0.03009924600938376</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3465</v>
+        <v>0.3553</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1862,19 +1862,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1.823</v>
+        <v>1.798</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1.823</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0</v>
+        <v>-0.0137</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>21876</v>
+        <v>21576</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03490161608394615</v>
+        <v>0.03134575402541095</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.13</v>
+        <v>0.1457</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>0.102</v>
+        <v>0.104</v>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         <v>35</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>577.3</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>573.35</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>573.75</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>-0.0007000000000000001</v>
+      <c r="H15" s="18" t="n">
+        <v>0.0069</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>20067.25</v>
+        <v>20205.5</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.03201588294754838</v>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
+        <v>0.02935468265482207</v>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1957,8 +1957,8 @@
       <c r="L15" s="7" t="n">
         <v>563.15</v>
       </c>
-      <c r="M15" s="19" t="n">
-        <v>-0.0178</v>
+      <c r="M15" s="20" t="n">
+        <v>-0.0245</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>0.123</v>
+        <v>0.122</v>
       </c>
       <c r="R15" s="15" t="inlineStr">
         <is>
@@ -2004,21 +2004,21 @@
         <v>4</v>
       </c>
       <c r="F16" s="7" t="n">
+        <v>5590</v>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>5683</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>5662</v>
-      </c>
       <c r="H16" s="8" t="n">
-        <v>0.0037</v>
+        <v>-0.0164</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>22732</v>
+        <v>22360</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.03626730374932637</v>
-      </c>
-      <c r="K16" s="18" t="inlineStr">
+        <v>0.03248475435707216</v>
+      </c>
+      <c r="K16" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2027,7 +2027,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.0886</v>
+        <v>0.1067</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -2072,24 +2072,24 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F17" s="7" t="n">
+        <v>808</v>
+      </c>
+      <c r="G17" s="7" t="n">
         <v>801</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>798</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>0.0038</v>
+      <c r="H17" s="18" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>20826</v>
+        <v>31512</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.03322641509253348</v>
-      </c>
-      <c r="K17" s="18" t="inlineStr">
+        <v>0.04578083986136216</v>
+      </c>
+      <c r="K17" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2098,7 +2098,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1648</v>
+        <v>0.1547</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="Q17" s="16" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
@@ -2148,19 +2148,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>179.1</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>176.9</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>176.75</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>0.0008</v>
+      <c r="H18" s="18" t="n">
+        <v>0.0124</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>21228</v>
+        <v>21492</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03386777775781719</v>
+        <v>0.03122371827559011</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3711</v>
+        <v>0.3543</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>0.198</v>
+        <v>0.195</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -2221,19 +2221,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
+        <v>71.36</v>
+      </c>
+      <c r="G19" s="7" t="n">
         <v>71.45</v>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>71.55</v>
-      </c>
-      <c r="H19" s="20" t="n">
-        <v>-0.0014</v>
+      <c r="H19" s="8" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>22435.3</v>
+        <v>22407.04</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.03579393981203862</v>
+        <v>0.03255309437697183</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.1197</v>
+        <v>0.1211</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -2288,19 +2288,19 @@
         <v>30000</v>
       </c>
       <c r="F20" s="21" t="n">
+        <v>0.6982</v>
+      </c>
+      <c r="G20" s="21" t="n">
         <v>0.715</v>
       </c>
-      <c r="G20" s="21" t="n">
-        <v>0.7104</v>
-      </c>
       <c r="H20" s="8" t="n">
-        <v>0.006500000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>21450</v>
+        <v>20946</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.03422196311028729</v>
+        <v>0.03043048590175463</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -2310,8 +2310,8 @@
       <c r="L20" s="21" t="n">
         <v>0.7</v>
       </c>
-      <c r="M20" s="19" t="n">
-        <v>-0.021</v>
+      <c r="M20" s="12" t="n">
+        <v>0.0026</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="Q20" s="16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="R20" s="15" t="inlineStr">
         <is>
@@ -2358,24 +2358,24 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>270</v>
+        <v>400</v>
       </c>
       <c r="F21" s="7" t="n">
+        <v>75.56</v>
+      </c>
+      <c r="G21" s="7" t="n">
         <v>76.22</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="H21" s="20" t="n">
-        <v>-0.0178</v>
+      <c r="H21" s="8" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>20579.4</v>
+        <v>30224</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.03283298217397885</v>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
+        <v>0.04390962503077589</v>
+      </c>
+      <c r="K21" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2384,7 +2384,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1582</v>
+        <v>0.1683</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2425,22 +2425,22 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>370000</v>
+        <v>470000</v>
       </c>
       <c r="F22" s="21" t="n">
+        <v>0.06451999999999999</v>
+      </c>
+      <c r="G22" s="21" t="n">
         <v>0.06551999999999999</v>
       </c>
-      <c r="G22" s="21" t="n">
-        <v>0.0644</v>
-      </c>
       <c r="H22" s="8" t="n">
-        <v>0.0174</v>
+        <v>-0.0153</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>24242.4</v>
+        <v>30324.4</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.0386770404897356</v>
+        <v>0.04405548680794271</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -2488,24 +2488,24 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F23" s="7" t="n">
+        <v>1098.4</v>
+      </c>
+      <c r="G23" s="7" t="n">
         <v>1112.4</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>1130.8</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>-0.0163</v>
+      <c r="H23" s="8" t="n">
+        <v>-0.0126</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>15573.6</v>
+        <v>20869.6</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.02484658110463264</v>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
+        <v>0.03031949148167947</v>
+      </c>
+      <c r="K23" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2514,7 +2514,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.2062</v>
+        <v>0.2216</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -2561,24 +2561,24 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>340</v>
+        <v>540</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>37.51</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>0.04219999999999999</v>
+      <c r="H24" s="18" t="n">
+        <v>0.0144</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>12753.4</v>
+        <v>20547</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02034715078464979</v>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
+        <v>0.02985081609010562</v>
+      </c>
+      <c r="K24" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2587,7 +2587,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.1442</v>
+        <v>0.128</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.141</v>
+        <v>0.139</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2634,22 +2634,22 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>363</v>
+        <v>463</v>
       </c>
       <c r="F25" s="7" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="G25" s="7" t="n">
         <v>58.07</v>
       </c>
-      <c r="G25" s="7" t="n">
-        <v>57.465</v>
-      </c>
       <c r="H25" s="8" t="n">
-        <v>0.0105</v>
+        <v>-0.0021</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>21079.41</v>
+        <v>26830.85</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03363071288608956</v>
+        <v>0.03898003450095928</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5421</v>
+        <v>0.5453</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>0.167</v>
+        <v>0.168</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -2707,22 +2707,22 @@
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>490.1</v>
+        <v>487.8</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>490.1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0</v>
+        <v>-0.004699999999999999</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>19604</v>
+        <v>24390</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.03127680022443226</v>
+        <v>0.03543395164440921</v>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.118</v>
+        <v>0.119</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="G27" s="7" t="n">
         <v>43.7</v>
       </c>
-      <c r="G27" s="7" t="n">
-        <v>43.25</v>
-      </c>
       <c r="H27" s="8" t="n">
-        <v>0.0104</v>
+        <v>-0.0103</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7429</v>
+        <v>7352.5</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.01185244587162351</v>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
+        <v>0.01068176012568752</v>
+      </c>
+      <c r="K27" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2801,8 +2801,8 @@
       <c r="L27" s="7" t="n">
         <v>42.5</v>
       </c>
-      <c r="M27" s="19" t="n">
-        <v>-0.0275</v>
+      <c r="M27" s="20" t="n">
+        <v>-0.0173</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         <v>340</v>
       </c>
       <c r="F28" s="7" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="G28" s="7" t="n">
         <v>43.9</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>43.2</v>
-      </c>
       <c r="H28" s="8" t="n">
-        <v>0.0162</v>
+        <v>-0.0091</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>14926</v>
+        <v>14790</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.02381338095030993</v>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
+        <v>0.02148700880774138</v>
+      </c>
+      <c r="K28" s="19" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2869,7 +2869,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.139</v>
+        <v>0.1494</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2891,104 +2891,116 @@
       <c r="S28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>ИТОГО АКЦИИ (25 позиций)</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
-      <c r="G29" s="24" t="n"/>
-      <c r="H29" s="24" t="n"/>
-      <c r="I29" s="25" t="n">
-        <v>626790.46</v>
-      </c>
-      <c r="J29" s="26" t="n">
-        <v>0.4248175838876356</v>
-      </c>
-      <c r="K29" s="27" t="inlineStr">
-        <is>
-          <t>Срвзв. потенциал: +26.4% · Покупать 13 / Держать 10 / без прогноза 2</t>
-        </is>
-      </c>
-      <c r="L29" s="28" t="n"/>
-      <c r="M29" s="28" t="n"/>
-      <c r="N29" s="28" t="n"/>
-      <c r="O29" s="28" t="n"/>
-      <c r="P29" s="28" t="n"/>
-      <c r="Q29" s="28" t="n"/>
-      <c r="R29" s="28" t="n"/>
-      <c r="S29" s="28" t="n"/>
+      <c r="A29" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Акции</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>NVTK</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>НОВАТЭК</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>1197.8</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>1198</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>11978</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>0.01740171680183409</v>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>Покупать</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>1437.8</v>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>0.2004</v>
+      </c>
+      <c r="N29" s="13" t="inlineStr">
+        <is>
+          <t>1100 — 1650</t>
+        </is>
+      </c>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
+          <t>≈45–50 (оценка)</t>
+        </is>
+      </c>
+      <c r="P29" s="15" t="inlineStr">
+        <is>
+          <t>ожидается апрель 2027</t>
+        </is>
+      </c>
+      <c r="Q29" s="5" t="n"/>
+      <c r="R29" s="15" t="inlineStr">
+        <is>
+          <t>прогноз по истории</t>
+        </is>
+      </c>
+      <c r="S29" s="17" t="inlineStr">
+        <is>
+          <t>Куплено 28.10.2026 (10 шт). Сводный прогноз Т-Банка от 28.10.2026: Покупать, цель 1 437,8 ₽, диапазон 1 100–1 650. Дивиденды 2 раза в год (апрель/октябрь): последние отсечки 12.10.2026 (35,5 ₽) и 13.04.2026 (47,23 ₽) — обе до покупки. Доходность за 12 мес ≈ 6,8% (82,73 ₽/акция).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Фонды</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>ОПИФ «Флагманский»</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>341.3</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>935.34</v>
-      </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="9" t="n">
-        <v>319231.54</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>0.3997169952716098</v>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="13" t="n"/>
-      <c r="O30" s="14" t="inlineStr">
-        <is>
-          <t>— (выплат нет)</t>
-        </is>
-      </c>
-      <c r="P30" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S30" s="17" t="inlineStr">
-        <is>
-          <t>Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
-        </is>
-      </c>
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>ИТОГО АКЦИИ (26 позиций)</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="25" t="n">
+        <v>688322.89</v>
+      </c>
+      <c r="J30" s="26" t="n">
+        <v>0.4662015079014227</v>
+      </c>
+      <c r="K30" s="27" t="inlineStr">
+        <is>
+          <t>Срвзв. потенциал: +26.1% · Покупать 14 / Держать 10 / без прогноза 2</t>
+        </is>
+      </c>
+      <c r="L30" s="28" t="n"/>
+      <c r="M30" s="28" t="n"/>
+      <c r="N30" s="28" t="n"/>
+      <c r="O30" s="28" t="n"/>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n"/>
+      <c r="R30" s="28" t="n"/>
+      <c r="S30" s="28" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3002,22 +3014,22 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>ОПИФ «Рублевые перспективы»</t>
+          <t>ОПИФ «Флагманский»</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>146.3</v>
+        <v>341.3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1727.59</v>
+        <v>939.65</v>
       </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="9" t="n">
-        <v>252746.42</v>
+        <v>320702.54</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3164694803278407</v>
+        <v>0.4344818660532686</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -3045,13 +3057,13 @@
       </c>
       <c r="S31" s="17" t="inlineStr">
         <is>
-          <t>Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+          <t>Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -3065,22 +3077,22 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>БПИФ «БКС Денежный рынок» (BCSD)</t>
+          <t>ОПИФ «Рублевые перспективы»</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>8530</v>
+        <v>146.3</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>14.58</v>
+        <v>1730.26</v>
       </c>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="9" t="n">
-        <v>124367.4</v>
+        <v>253137.04</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.1557232203238515</v>
+        <v>0.3429453770662399</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -3108,13 +3120,13 @@
       </c>
       <c r="S32" s="17" t="inlineStr">
         <is>
-          <t>Доходность ≈ ключевая ставка минус комиссии (~13,5–14,5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+          <t>Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3128,22 +3140,22 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>БПИФ «Т-Капитал Денежный рынок» (TMON)</t>
+          <t>БПИФ «БКС Денежный рынок» (BCSD)</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>614</v>
+        <v>8530</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>166.61</v>
+        <v>14.59</v>
       </c>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="9" t="n">
-        <v>102298.54</v>
+        <v>124452.7</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.128090304076698</v>
+        <v>0.16860621475392</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -3171,131 +3183,165 @@
       </c>
       <c r="S33" s="17" t="inlineStr">
         <is>
-          <t>Доходность ≈ ставка денежного рынка ON минус расходы (~13,5% годовых); за 1 год +14,7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161,06 ₽; 08.10.2026 докуплено 180 паев по ~165,57 ₽; 12.10.2026 докуплено 220 паев по ~165,84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → 27.10.2026 продано ещё 175 паев → позиция 614 паев (средняя цена покупки 166,67 ₽ по данным приложения). Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>Доходность ≈ ключевая ставка минус комиссии (~13,5–14,5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Фонды</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>БПИФ «Т-Капитал Денежный рынок» (TMON)</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>239</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="9" t="n">
+        <v>39834.13</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>0.05396654212657151</v>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="13" t="n"/>
+      <c r="O34" s="14" t="inlineStr">
+        <is>
+          <t>— (выплат нет)</t>
+        </is>
+      </c>
+      <c r="P34" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S34" s="17" t="inlineStr">
+        <is>
+          <t>Доходность ≈ ставка денежного рынка ON минус расходы (~13,5% годовых); за 1 год +14,7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161,06 ₽; 08.10.2026 докуплено 180 паев по ~165,57 ₽; 12.10.2026 докуплено 220 паев по ~165,84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → 27.10.2026 продано ещё 175 паев → 28.10.2026 продано 375 паев → позиция 239 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>ИТОГО ФОНДЫ (4 позиции)</t>
         </is>
       </c>
-      <c r="B34" s="24" t="n"/>
-      <c r="C34" s="24" t="n"/>
-      <c r="D34" s="24" t="n"/>
-      <c r="E34" s="24" t="n"/>
-      <c r="F34" s="24" t="n"/>
-      <c r="G34" s="24" t="n"/>
-      <c r="H34" s="24" t="n"/>
-      <c r="I34" s="25" t="n">
-        <v>798643.9</v>
-      </c>
-      <c r="J34" s="26" t="n">
-        <v>0.5412940905076929</v>
-      </c>
-      <c r="K34" s="28" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="28" t="n"/>
-      <c r="N34" s="28" t="n"/>
-      <c r="O34" s="28" t="n"/>
-      <c r="P34" s="28" t="n"/>
-      <c r="Q34" s="28" t="n"/>
-      <c r="R34" s="28" t="n"/>
-      <c r="S34" s="28" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="B35" s="24" t="n"/>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="24" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="24" t="n"/>
+      <c r="H35" s="24" t="n"/>
+      <c r="I35" s="25" t="n">
+        <v>738126.41</v>
+      </c>
+      <c r="J35" s="26" t="n">
+        <v>0.4999334619888404</v>
+      </c>
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="28" t="n"/>
+      <c r="M35" s="28" t="n"/>
+      <c r="N35" s="28" t="n"/>
+      <c r="O35" s="28" t="n"/>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n"/>
+      <c r="R35" s="28" t="n"/>
+      <c r="S35" s="28" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Яндекс Банк — денежный остаток</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="9" t="n">
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="J35" s="10" t="n">
-        <v>0.03388832560467143</v>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="J36" s="10" t="n">
+        <v>0.03386503010973692</v>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P35" s="5" t="inlineStr">
+      <c r="P36" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="5" t="inlineStr">
+      <c r="Q36" s="5" t="n"/>
+      <c r="R36" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S35" s="17" t="inlineStr">
+      <c r="S36" s="17" t="inlineStr">
         <is>
           <t>«Сейв» (Плюс): 10% брутто = ≈10,5% эфф. (капитализация ежедневно) → ≈440 ₽/мес на 50 тыс.; НДФЛ 0% — проценты в пределах безналогового лимита (1 млн × макс. ставка ≈ 140 тыс. ₽/год). С тратами картой Яндекса от 1 ₽/день → 13% (≈13,9% эфф., ≈2 080 ₽/мес, НДФЛ 0%). BCSD: ~13,5–14,5% брутто, но НДФЛ 13% с прибыли при продаже → чистыми ~11,8–12,6% (≈1 760–1 890 ₽/мес); без налога при владении 3+ года (ЛДВ) или на ИИС-3. Вывод: «Сейв» 13% чистыми выгоднее налогооблагаемого BCSD; «Сейв» 10% — проигрывает (~−250 ₽/мес)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>ИТОГО CASH</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="n"/>
-      <c r="C36" s="24" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="24" t="n"/>
-      <c r="F36" s="24" t="n"/>
-      <c r="G36" s="24" t="n"/>
-      <c r="H36" s="24" t="n"/>
-      <c r="I36" s="25" t="n">
-        <v>50000</v>
-      </c>
-      <c r="J36" s="26" t="n">
-        <v>0.03388832560467143</v>
-      </c>
-      <c r="K36" s="28" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="28" t="n"/>
-      <c r="N36" s="28" t="n"/>
-      <c r="O36" s="28" t="n"/>
-      <c r="P36" s="28" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="28" t="n"/>
-      <c r="S36" s="28" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="29" t="inlineStr">
-        <is>
-          <t>ИТОГО ПОРТФЕЛЬ (ликвидная часть)</t>
         </is>
       </c>
       <c r="B37" s="24" t="n"/>
@@ -3305,244 +3351,273 @@
       <c r="F37" s="24" t="n"/>
       <c r="G37" s="24" t="n"/>
       <c r="H37" s="24" t="n"/>
-      <c r="I37" s="30" t="n">
-        <v>1475434.36</v>
-      </c>
-      <c r="J37" s="31" t="n">
+      <c r="I37" s="25" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J37" s="26" t="n">
+        <v>0.03386503010973692</v>
+      </c>
+      <c r="K37" s="28" t="n"/>
+      <c r="L37" s="28" t="n"/>
+      <c r="M37" s="28" t="n"/>
+      <c r="N37" s="28" t="n"/>
+      <c r="O37" s="28" t="n"/>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n"/>
+      <c r="R37" s="28" t="n"/>
+      <c r="S37" s="28" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>ИТОГО ПОРТФЕЛЬ (ликвидная часть)</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="n"/>
+      <c r="C38" s="24" t="n"/>
+      <c r="D38" s="24" t="n"/>
+      <c r="E38" s="24" t="n"/>
+      <c r="F38" s="24" t="n"/>
+      <c r="G38" s="24" t="n"/>
+      <c r="H38" s="24" t="n"/>
+      <c r="I38" s="30" t="n">
+        <v>1476449.3</v>
+      </c>
+      <c r="J38" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="K37" s="32" t="n"/>
-      <c r="L37" s="32" t="n"/>
-      <c r="M37" s="32" t="n"/>
-      <c r="N37" s="32" t="n"/>
-      <c r="O37" s="33" t="inlineStr">
+      <c r="K38" s="32" t="n"/>
+      <c r="L38" s="32" t="n"/>
+      <c r="M38" s="32" t="n"/>
+      <c r="N38" s="32" t="n"/>
+      <c r="O38" s="33" t="inlineStr">
         <is>
           <t>Ближайших утверждённых отсечек нет</t>
         </is>
       </c>
-      <c r="P37" s="32" t="n"/>
-      <c r="Q37" s="32" t="n"/>
-      <c r="R37" s="32" t="n"/>
-      <c r="S37" s="32" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="P38" s="32" t="n"/>
+      <c r="Q38" s="32" t="n"/>
+      <c r="R38" s="32" t="n"/>
+      <c r="S38" s="32" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Cash (жена)</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Сэйв — пенсионный счёт жены (Яндекс Банк)</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="9" t="n">
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="9" t="n">
         <v>605000</v>
       </c>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="n"/>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P38" s="5" t="inlineStr">
+      <c r="P39" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q38" s="5" t="n"/>
-      <c r="R38" s="5" t="inlineStr">
+      <c r="Q39" s="5" t="n"/>
+      <c r="R39" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S38" s="17" t="inlineStr">
+      <c r="S39" s="17" t="inlineStr">
         <is>
           <t>Отдельный блок: не учитывается в долях, потенциале и дивидендных расчётах основного портфеля; входит только в семейный итог. Доходность — по тарифу «Сэйв» её аккаунта.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>ВСЕГО СЕМЕЙНЫЙ ПОРТФЕЛЬ (ликвидный)</t>
         </is>
       </c>
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="24" t="n"/>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="24" t="n"/>
-      <c r="F39" s="24" t="n"/>
-      <c r="G39" s="24" t="n"/>
-      <c r="H39" s="24" t="n"/>
-      <c r="I39" s="30" t="n">
-        <v>2080434.36</v>
-      </c>
-      <c r="J39" s="31" t="n"/>
-      <c r="K39" s="34" t="inlineStr">
-        <is>
-          <t>ваш 1 475 434 ₽ + жены 605 000 ₽</t>
-        </is>
-      </c>
-      <c r="L39" s="32" t="n"/>
-      <c r="M39" s="32" t="n"/>
-      <c r="N39" s="32" t="n"/>
-      <c r="O39" s="32" t="n"/>
-      <c r="P39" s="32" t="n"/>
-      <c r="Q39" s="32" t="n"/>
-      <c r="R39" s="32" t="n"/>
-      <c r="S39" s="32" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="B40" s="24" t="n"/>
+      <c r="C40" s="24" t="n"/>
+      <c r="D40" s="24" t="n"/>
+      <c r="E40" s="24" t="n"/>
+      <c r="F40" s="24" t="n"/>
+      <c r="G40" s="24" t="n"/>
+      <c r="H40" s="24" t="n"/>
+      <c r="I40" s="30" t="n">
+        <v>2081449.3</v>
+      </c>
+      <c r="J40" s="31" t="n"/>
+      <c r="K40" s="34" t="inlineStr">
+        <is>
+          <t>ваш 1 476 449 ₽ + жены 605 000 ₽</t>
+        </is>
+      </c>
+      <c r="L40" s="32" t="n"/>
+      <c r="M40" s="32" t="n"/>
+      <c r="N40" s="32" t="n"/>
+      <c r="O40" s="32" t="n"/>
+      <c r="P40" s="32" t="n"/>
+      <c r="Q40" s="32" t="n"/>
+      <c r="R40" s="32" t="n"/>
+      <c r="S40" s="32" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>ЗАБЛОКИРОВАННЫЕ АКТИВЫ — справочно, вне ликвидного итога</t>
         </is>
       </c>
-      <c r="B40" s="36" t="n"/>
-      <c r="C40" s="36" t="n"/>
-      <c r="D40" s="36" t="n"/>
-      <c r="E40" s="36" t="n"/>
-      <c r="F40" s="36" t="n"/>
-      <c r="G40" s="36" t="n"/>
-      <c r="H40" s="36" t="n"/>
-      <c r="I40" s="36" t="n"/>
-      <c r="J40" s="36" t="n"/>
-      <c r="K40" s="36" t="n"/>
-      <c r="L40" s="36" t="n"/>
-      <c r="M40" s="36" t="n"/>
-      <c r="N40" s="36" t="n"/>
-      <c r="O40" s="36" t="n"/>
-      <c r="P40" s="36" t="n"/>
-      <c r="Q40" s="36" t="n"/>
-      <c r="R40" s="36" t="n"/>
-      <c r="S40" s="36" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="B41" s="36" t="n"/>
+      <c r="C41" s="36" t="n"/>
+      <c r="D41" s="36" t="n"/>
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="36" t="n"/>
+      <c r="G41" s="36" t="n"/>
+      <c r="H41" s="36" t="n"/>
+      <c r="I41" s="36" t="n"/>
+      <c r="J41" s="36" t="n"/>
+      <c r="K41" s="36" t="n"/>
+      <c r="L41" s="36" t="n"/>
+      <c r="M41" s="36" t="n"/>
+      <c r="N41" s="36" t="n"/>
+      <c r="O41" s="36" t="n"/>
+      <c r="P41" s="36" t="n"/>
+      <c r="Q41" s="36" t="n"/>
+      <c r="R41" s="36" t="n"/>
+      <c r="S41" s="36" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Заблокировано</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>BLT · ISIN CA06849F1080</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Barrick Mining (Barrick Gold)</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E42" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F42" s="7" t="n">
         <v>3397.47</v>
       </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="9" t="n">
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="9" t="n">
         <v>20384.83</v>
       </c>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="n"/>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P41" s="5" t="inlineStr">
+      <c r="P42" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q41" s="5" t="n"/>
-      <c r="R41" s="17" t="inlineStr">
+      <c r="Q42" s="5" t="n"/>
+      <c r="R42" s="17" t="inlineStr">
         <is>
           <t>заблокировано</t>
         </is>
       </c>
-      <c r="S41" s="17" t="inlineStr">
+      <c r="S42" s="17" t="inlineStr">
         <is>
           <t>Заморожен из-за санкционных/инфраструктурных ограничений: продажа и вывод недоступны, дивиденды не поступают. Оценка по цене 40,51 $ и курсу ЦБ 83.8675 ₽/$ (14.10.2026).</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="29" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>ИТОГО С УЧЁТОМ ЗАБЛОКИРОВАННЫХ</t>
         </is>
       </c>
-      <c r="B42" s="32" t="n"/>
-      <c r="C42" s="32" t="n"/>
-      <c r="D42" s="32" t="n"/>
-      <c r="E42" s="32" t="n"/>
-      <c r="F42" s="32" t="n"/>
-      <c r="G42" s="32" t="n"/>
-      <c r="H42" s="32" t="n"/>
-      <c r="I42" s="30" t="n">
-        <v>1495819.19</v>
-      </c>
-      <c r="J42" s="34" t="inlineStr">
-        <is>
-          <t>ликвидная часть: 1 475 434 ₽ + заблокировано 20 385 ₽</t>
-        </is>
-      </c>
-      <c r="K42" s="32" t="n"/>
-      <c r="L42" s="32" t="n"/>
-      <c r="M42" s="32" t="n"/>
-      <c r="N42" s="32" t="n"/>
-      <c r="O42" s="32" t="n"/>
-      <c r="P42" s="32" t="n"/>
-      <c r="Q42" s="32" t="n"/>
-      <c r="R42" s="32" t="n"/>
-      <c r="S42" s="32" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="32" t="n"/>
+      <c r="D43" s="32" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="32" t="n"/>
+      <c r="H43" s="32" t="n"/>
+      <c r="I43" s="30" t="n">
+        <v>1496834.13</v>
+      </c>
+      <c r="J43" s="34" t="inlineStr">
+        <is>
+          <t>ликвидная часть: 1 476 449 ₽ + заблокировано 20 385 ₽</t>
+        </is>
+      </c>
+      <c r="K43" s="32" t="n"/>
+      <c r="L43" s="32" t="n"/>
+      <c r="M43" s="32" t="n"/>
+      <c r="N43" s="32" t="n"/>
+      <c r="O43" s="32" t="n"/>
+      <c r="P43" s="32" t="n"/>
+      <c r="Q43" s="32" t="n"/>
+      <c r="R43" s="32" t="n"/>
+      <c r="S43" s="32" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A41:S41"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A40:S40"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3554,7 +3629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3572,14 +3647,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Учёт ежедневных остатков — Акции, Фонды, Счета, Сэйв жены (обновлено: 2026-10-27)</t>
+          <t>Учёт ежедневных остатков — Акции, Фонды, Счета, Сэйв жены (обновлено: 2026-10-28)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>Помесячные остатки на 1-е число за 03.2023–09.2026 — данные пользователя: «Сэйв жены», «Тинькоф — акции», «IH+БКС — фонды» (IH и БКС суммируются); кэш и заблокированные в эти месяцы не указаны, «Итого» = акции + фонды. Записи добавляются ежедневно в 18:40 МСК (GitHub Actions) и при ручных обновлениях. Категории: Акции (25 бумаг), Фонды (4 пифа), Счета — денежный остаток «Сэйв» Яндекс Банка, Сэйв жены — пенсионный счёт (семейный блок, входит только в «Семейный итог»). Заблокированные активы (Barrick, 6 шт) — справочно, вне ликвидного итога. Не учитываются: PINS-RM, FIVE, остатки на брокерском счёте Т-Банка (−4 091,15 ₽ и 2,82 $). История до 21.10 восстановлена из git-истории portfolio_data.json; 17–20.10 пересчитаны по фактическим остаткам (регрессия публикации 16.10).</t>
+          <t>Помесячные остатки на 1-е число за 03.2023–09.2026 — данные пользователя: «Сэйв жены», «Тинькоф — акции», «IH+БКС — фонды» (IH и БКС суммируются); кэш и заблокированные в эти месяцы не указаны, «Итого» = акции + фонды. Записи добавляются ежедневно в 23:45 МСК (GitHub Actions) и при ручных обновлениях. Категории: Акции (25 бумаг), Фонды (4 пифа), Счета — денежный остаток «Сэйв» Яндекс Банка, Сэйв жены — пенсионный счёт (семейный блок, входит только в «Семейный итог»). Заблокированные активы (Barrick, 6 шт) — справочно, вне ликвидного итога. Не учитываются: PINS-RM, FIVE, остатки на брокерском счёте Т-Банка (−4 091,15 ₽ и 2,82 $). История до 21.10 восстановлена из git-истории portfolio_data.json; 17–20.10 пересчитаны по фактическим остаткам (регрессия публикации 16.10).</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5334,7 @@
         <v>605000</v>
       </c>
       <c r="C57" s="9" t="n">
-        <v>626790.46</v>
+        <v>626904.96</v>
       </c>
       <c r="D57" s="9" t="n">
         <v>798643.9</v>
@@ -5268,18 +5343,54 @@
         <v>50000</v>
       </c>
       <c r="F57" s="38" t="n">
-        <v>1475434.36</v>
+        <v>1475548.86</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>20384.83</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>1495819.19</v>
+        <v>1495933.69</v>
       </c>
       <c r="I57" s="38" t="n">
-        <v>2080434.36</v>
+        <v>2080548.86</v>
       </c>
       <c r="J57" s="39" t="inlineStr">
+        <is>
+          <t>автообновление</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="40" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="B58" s="41" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C58" s="41" t="n">
+        <v>688322.89</v>
+      </c>
+      <c r="D58" s="41" t="n">
+        <v>738126.41</v>
+      </c>
+      <c r="E58" s="41" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F58" s="42" t="n">
+        <v>1476449.3</v>
+      </c>
+      <c r="G58" s="41" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H58" s="41" t="n">
+        <v>1496834.13</v>
+      </c>
+      <c r="I58" s="42" t="n">
+        <v>2081449.3</v>
+      </c>
+      <c r="J58" s="43" t="inlineStr">
         <is>
           <t>автообновление GitHub Actions</t>
         </is>
@@ -5311,21 +5422,21 @@
     <row r="1">
       <c r="B1" s="44" t="inlineStr">
         <is>
-          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 27.10.2026 (АВТООБНОВЛЕНИЕ)</t>
+          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 28.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="B2" s="45" t="inlineStr">
         <is>
-          <t>• Рекомендации: ПОКУПАТЬ — 13; ДЕРЖАТЬ — 10; ПРОДАВАТЬ — 0; без прогноза — 2 (FEES, PMSB).</t>
+          <t>• Рекомендации: ПОКУПАТЬ — 14; ДЕРЖАТЬ — 10; ПРОДАВАТЬ — 0; без прогноза — 2 (FEES, PMSB).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="45" t="inlineStr">
         <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +26.4% (без учёта дивидендов).</t>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +26.1% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5457,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="45" t="inlineStr">
         <is>
-          <t>• Дивиденды за 12 месяцев (факт): ≈ 59 165 ₽ — 4.01% годовых на портфель.</t>
+          <t>• Дивиденды за 12 месяцев (факт): ≈ 63 284 ₽ — 4.29% годовых на портфель.</t>
         </is>
       </c>
     </row>
@@ -5374,28 +5485,28 @@
     <row r="13" ht="45" customHeight="1">
       <c r="B13" s="45" t="inlineStr">
         <is>
-          <t>• ОПИФ «Флагманский»: пай 935.34 ₽ (26.10.2026); 1 мес +6.66%  1 год +9.01%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
+          <t>• ОПИФ «Флагманский»: пай 939.65 ₽ (27.10.2026); 1 мес +7.15%  1 год +10.94%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="B14" s="45" t="inlineStr">
         <is>
-          <t>• ОПИФ «Рублевые перспективы»: пай 1 727.59 ₽ (26.10.2026); 1 мес +0.93%  1 год +16.57%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+          <t>• ОПИФ «Рублевые перспективы»: пай 1 730.26 ₽ (27.10.2026); 1 мес +1.08%  1 год +16.88%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="B15" s="45" t="inlineStr">
         <is>
-          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.58 ₽ (26.10.2026); 1 мес +1.15%  1 год +15.45%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.59 ₽ (27.10.2026); 1 мес +1.18%  1 год +15.4%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="105" customHeight="1">
       <c r="B16" s="45" t="inlineStr">
         <is>
-          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.61 ₽ (26.10.2026); 1 мес +1.1%  1 год +14.69%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → 27.10.2026 продано ещё 175 паев → позиция 614 паев (средняя цена покупки 166 67 ₽ по данным приложения). Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.67 ₽ (27.10.2026); 1 мес +1.13%  1 год +14.58%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → 27.10.2026 продано ещё 175 паев → 28.10.2026 продано 375 паев → позиция 239 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5527,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="45" t="inlineStr">
         <is>
-          <t>• Семейный итог (ликвидный): 2 080 434 ₽ = ваш 1 475 434 ₽ + 605 000 ₽.</t>
+          <t>• Семейный итог (ликвидный): 2 081 449 ₽ = ваш 1 476 449 ₽ + 605 000 ₽.</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5548,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="45" t="inlineStr">
         <is>
-          <t>• Итого с учётом заблокированных: 1 495 819 ₽ (ликвидная часть 1 475 434 ₽).</t>
+          <t>• Итого с учётом заблокированных: 1 496 834 ₽ (ликвидная часть 1 476 449 ₽).</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5562,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="45" t="inlineStr">
         <is>
-          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (27.10.2026, закрытие 26.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
+          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (28.10.2026, закрытие 27.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -394,12 +394,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$58</f>
+              <f>'Остатки по дням'!$A$5:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$B$5:$B$58</f>
+              <f>'Остатки по дням'!$B$5:$B$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -434,12 +434,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$58</f>
+              <f>'Остатки по дням'!$A$5:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$C$5:$C$58</f>
+              <f>'Остатки по дням'!$C$5:$C$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -474,12 +474,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$58</f>
+              <f>'Остатки по дням'!$A$5:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$D$5:$D$58</f>
+              <f>'Остатки по дням'!$D$5:$D$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -514,12 +514,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$58</f>
+              <f>'Остатки по дням'!$A$5:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$E$5:$E$58</f>
+              <f>'Остатки по дням'!$E$5:$E$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -554,12 +554,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$58</f>
+              <f>'Остатки по дням'!$A$5:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$F$5:$F$58</f>
+              <f>'Остатки по дням'!$F$5:$F$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -594,12 +594,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$58</f>
+              <f>'Остатки по дням'!$A$5:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$I$5:$I$58</f>
+              <f>'Остатки по дням'!$I$5:$I$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -678,7 +678,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10800000" cy="5040000"/>
@@ -1015,14 +1015,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 28.10.2026 (автообновление)</t>
+          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 29.10.2026 (автообновление)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (28.10.2026, закрытие 27.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
+          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (29.10.2026, закрытие 28.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Текущая цена, ₽ (28.10.2026)</t>
+          <t>Текущая цена, ₽ (29.10.2026)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Цена за пред. торг. день, ₽ (27.10.2026)</t>
+          <t>Цена за пред. торг. день, ₽ (28.10.2026)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1146,19 +1146,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
+        <v>295.08</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>297.98</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>298.18</v>
-      </c>
       <c r="H4" s="8" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>-0.0097</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>47676.8</v>
+        <v>47212.8</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.069265167107838</v>
+        <v>0.06929763460879997</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.2732</v>
+        <v>0.2858</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="Q4" s="16" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
@@ -1219,19 +1219,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
+        <v>3453</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>3553.5</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>3529.5</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>0.0068</v>
+      <c r="H5" s="8" t="n">
+        <v>-0.0283</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>42642</v>
+        <v>41436</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.06195057671262393</v>
+        <v>0.06081860825136902</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.6368</v>
+        <v>0.6845</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="R5" s="15" t="inlineStr">
         <is>
@@ -1292,19 +1292,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
+        <v>275.94</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>277.58</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>276.98</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>0.0022</v>
+      <c r="H6" s="8" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>44412.8</v>
+        <v>44150.4</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.06452320654337095</v>
+        <v>0.06480272906992091</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.484</v>
+        <v>0.4928</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -1361,19 +1361,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
+        <v>2359</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>2347.5</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>2353.5</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>-0.0025</v>
+      <c r="H7" s="18" t="n">
+        <v>0.0049</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>46950</v>
+        <v>47180</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.06820926731057861</v>
+        <v>0.06924949168113695</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.2189</v>
+        <v>0.2129</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.261</v>
+        <v>0.26</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1434,19 +1434,19 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>116.8</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>117.25</v>
-      </c>
       <c r="H8" s="8" t="n">
-        <v>-0.0038</v>
+        <v>-0.017</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>31536</v>
+        <v>30998.7</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.04581570721845383</v>
+        <v>0.04549902962645316</v>
       </c>
       <c r="K8" s="19" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.2028</v>
+        <v>0.2237</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1501,19 +1501,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
+        <v>6243.5</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <v>6291.5</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>6341.5</v>
-      </c>
       <c r="H9" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0076</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>25166</v>
+        <v>24974</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.03656132952370653</v>
+        <v>0.03665614254439835</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>6221.5</v>
       </c>
       <c r="M9" s="20" t="n">
-        <v>-0.0111</v>
+        <v>-0.0035</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
       <c r="R9" s="15" t="inlineStr">
         <is>
@@ -1574,19 +1574,19 @@
         <v>170</v>
       </c>
       <c r="F10" s="7" t="n">
+        <v>165.79</v>
+      </c>
+      <c r="G10" s="7" t="n">
         <v>161.86</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>163.14</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>-0.007800000000000001</v>
+      <c r="H10" s="18" t="n">
+        <v>0.0243</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>27516.2</v>
+        <v>28184.3</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.03997571546690827</v>
+        <v>0.04136813158941644</v>
       </c>
       <c r="K10" s="19" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.2206</v>
+        <v>0.1917</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>0.121</v>
+        <v>0.118</v>
       </c>
       <c r="R10" s="15" t="inlineStr">
         <is>
@@ -1647,19 +1647,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="7" t="n">
+        <v>1061</v>
+      </c>
+      <c r="G11" s="7" t="n">
         <v>1077.8</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>1073</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>0.004500000000000001</v>
+      <c r="H11" s="8" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>31256.2</v>
+        <v>30769</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.04540921194702678</v>
+        <v>0.04516188235559353</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.3917</v>
+        <v>0.4138</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.189</v>
+        <v>0.192</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1720,19 +1720,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
+        <v>3835</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>3774</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>3635</v>
-      </c>
       <c r="H12" s="18" t="n">
-        <v>0.0382</v>
+        <v>0.0162</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>22644</v>
+        <v>23010</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03289735141599025</v>
+        <v>0.03377343797335653</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.4464</v>
+        <v>0.4234000000000001</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>0.057</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="R12" s="15" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         <v>180</v>
       </c>
       <c r="F13" s="7" t="n">
+        <v>114.32</v>
+      </c>
+      <c r="G13" s="7" t="n">
         <v>115.1</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>115.86</v>
-      </c>
       <c r="H13" s="8" t="n">
-        <v>-0.0066</v>
+        <v>-0.0068</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>20718</v>
+        <v>20577.6</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.03009924600938376</v>
+        <v>0.03020322891093183</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3553</v>
+        <v>0.3646</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1862,19 +1862,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
+        <v>1.7665</v>
+      </c>
+      <c r="G14" s="7" t="n">
         <v>1.798</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>1.823</v>
-      </c>
       <c r="H14" s="8" t="n">
-        <v>-0.0137</v>
+        <v>-0.0175</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>21576</v>
+        <v>21198</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03134575402541095</v>
+        <v>0.03111383477441164</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1457</v>
+        <v>0.1661</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
@@ -1935,19 +1935,19 @@
         <v>35</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>569.35</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>577.3</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>573.35</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>0.0069</v>
+      <c r="H15" s="8" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>20205.5</v>
+        <v>19927.25</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.02935468265482207</v>
+        <v>0.02924866327051582</v>
       </c>
       <c r="K15" s="19" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>563.15</v>
       </c>
       <c r="M15" s="20" t="n">
-        <v>-0.0245</v>
+        <v>-0.0109</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>0.122</v>
+        <v>0.124</v>
       </c>
       <c r="R15" s="15" t="inlineStr">
         <is>
@@ -2004,19 +2004,19 @@
         <v>4</v>
       </c>
       <c r="F16" s="7" t="n">
+        <v>5486</v>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>5590</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>5683</v>
-      </c>
       <c r="H16" s="8" t="n">
-        <v>-0.0164</v>
+        <v>-0.0186</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>22360</v>
+        <v>21944</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.03248475435707216</v>
+        <v>0.03220879282430837</v>
       </c>
       <c r="K16" s="19" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.1067</v>
+        <v>0.1277</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -2075,19 +2075,19 @@
         <v>39</v>
       </c>
       <c r="F17" s="7" t="n">
+        <v>803.5</v>
+      </c>
+      <c r="G17" s="7" t="n">
         <v>808</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>801</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>0.008699999999999999</v>
+      <c r="H17" s="8" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>31512</v>
+        <v>31336.5</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.04578083986136216</v>
+        <v>0.04599484307049487</v>
       </c>
       <c r="K17" s="19" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1547</v>
+        <v>0.1612</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -2148,19 +2148,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>177.7</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>179.1</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>176.9</v>
-      </c>
-      <c r="H18" s="18" t="n">
-        <v>0.0124</v>
+      <c r="H18" s="8" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>21492</v>
+        <v>21324</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.03122371827559011</v>
+        <v>0.0312987740697025</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3543</v>
+        <v>0.3649</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>0.195</v>
+        <v>0.197</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -2221,19 +2221,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="G19" s="7" t="n">
         <v>71.36</v>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>71.45</v>
-      </c>
       <c r="H19" s="8" t="n">
-        <v>-0.0013</v>
+        <v>-0.002</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>22407.04</v>
+        <v>22363.08</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.03255309437697183</v>
+        <v>0.03282390679153455</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.1211</v>
+        <v>0.1233</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -2288,19 +2288,19 @@
         <v>30000</v>
       </c>
       <c r="F20" s="21" t="n">
+        <v>0.6734</v>
+      </c>
+      <c r="G20" s="21" t="n">
         <v>0.6982</v>
       </c>
-      <c r="G20" s="21" t="n">
-        <v>0.715</v>
-      </c>
       <c r="H20" s="8" t="n">
-        <v>-0.0235</v>
+        <v>-0.0355</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>20946</v>
+        <v>20202</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.03043048590175463</v>
+        <v>0.02965193367830285</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>0.7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.0026</v>
+        <v>0.0395</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="Q20" s="16" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="R20" s="15" t="inlineStr">
         <is>
@@ -2361,19 +2361,19 @@
         <v>400</v>
       </c>
       <c r="F21" s="7" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="G21" s="7" t="n">
         <v>75.56</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>76.22</v>
-      </c>
       <c r="H21" s="8" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0143</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>30224</v>
+        <v>29792</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.04390962503077589</v>
+        <v>0.04372786893099686</v>
       </c>
       <c r="K21" s="19" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1683</v>
+        <v>0.1853</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2428,19 +2428,19 @@
         <v>470000</v>
       </c>
       <c r="F22" s="21" t="n">
+        <v>0.06496</v>
+      </c>
+      <c r="G22" s="21" t="n">
         <v>0.06451999999999999</v>
       </c>
-      <c r="G22" s="21" t="n">
-        <v>0.06551999999999999</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>-0.0153</v>
+      <c r="H22" s="18" t="n">
+        <v>0.0068</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>30324.4</v>
+        <v>30531.2</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.04405548680794271</v>
+        <v>0.04481284613003663</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -2491,19 +2491,19 @@
         <v>19</v>
       </c>
       <c r="F23" s="7" t="n">
+        <v>1051.6</v>
+      </c>
+      <c r="G23" s="7" t="n">
         <v>1098.4</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>1112.4</v>
-      </c>
       <c r="H23" s="8" t="n">
-        <v>-0.0126</v>
+        <v>-0.0426</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>20869.6</v>
+        <v>19980.4</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.03031949148167947</v>
+        <v>0.0293266753621405</v>
       </c>
       <c r="K23" s="19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.2216</v>
+        <v>0.276</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>0.111</v>
+        <v>0.116</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -2564,19 +2564,19 @@
         <v>540</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>37.24</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>38.05</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>37.51</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>0.0144</v>
+      <c r="H24" s="8" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>20547</v>
+        <v>20109.6</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02985081609010562</v>
+        <v>0.02951631152842288</v>
       </c>
       <c r="K24" s="19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.128</v>
+        <v>0.1525</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.139</v>
+        <v>0.142</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2637,19 +2637,19 @@
         <v>463</v>
       </c>
       <c r="F25" s="7" t="n">
+        <v>57.735</v>
+      </c>
+      <c r="G25" s="7" t="n">
         <v>57.95</v>
       </c>
-      <c r="G25" s="7" t="n">
-        <v>58.07</v>
-      </c>
       <c r="H25" s="8" t="n">
-        <v>-0.0021</v>
+        <v>-0.0037</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>26830.85</v>
+        <v>26731.31</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.03898003450095928</v>
+        <v>0.0392354732825539</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5453</v>
+        <v>0.5511</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2710,19 +2710,19 @@
         <v>50</v>
       </c>
       <c r="F26" s="7" t="n">
+        <v>472.1</v>
+      </c>
+      <c r="G26" s="7" t="n">
         <v>487.8</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>490.1</v>
-      </c>
       <c r="H26" s="8" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.0322</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>24390</v>
+        <v>23605</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.03543395164440921</v>
+        <v>0.03464676242334119</v>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.119</v>
+        <v>0.123</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2779,19 +2779,19 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="G27" s="7" t="n">
         <v>43.25</v>
       </c>
-      <c r="G27" s="7" t="n">
-        <v>43.7</v>
-      </c>
       <c r="H27" s="8" t="n">
-        <v>-0.0103</v>
+        <v>-0.0046</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7352.5</v>
+        <v>7318.5</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.01068176012568752</v>
+        <v>0.01074189073481138</v>
       </c>
       <c r="K27" s="19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>42.5</v>
       </c>
       <c r="M27" s="20" t="n">
-        <v>-0.0173</v>
+        <v>-0.0128</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2846,19 +2846,19 @@
         <v>340</v>
       </c>
       <c r="F28" s="7" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="G28" s="7" t="n">
         <v>43.5</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>-0.0091</v>
+      <c r="H28" s="18" t="n">
+        <v>0.0023</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>14790</v>
+        <v>14824</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.02148700880774138</v>
+        <v>0.02175825486818936</v>
       </c>
       <c r="K28" s="19" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.1494</v>
+        <v>0.1468</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2913,19 +2913,19 @@
         <v>10</v>
       </c>
       <c r="F29" s="7" t="n">
+        <v>1162.5</v>
+      </c>
+      <c r="G29" s="7" t="n">
         <v>1197.8</v>
       </c>
-      <c r="G29" s="7" t="n">
-        <v>1198</v>
-      </c>
       <c r="H29" s="8" t="n">
-        <v>-0.0002</v>
+        <v>-0.0295</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>11978</v>
+        <v>11625</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.01740171680183409</v>
+        <v>0.01706285164886005</v>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>1437.8</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.2004</v>
+        <v>0.2368</v>
       </c>
       <c r="N29" s="13" t="inlineStr">
         <is>
@@ -2979,14 +2979,14 @@
       <c r="G30" s="24" t="n"/>
       <c r="H30" s="24" t="n"/>
       <c r="I30" s="25" t="n">
-        <v>688322.89</v>
+        <v>681304.64</v>
       </c>
       <c r="J30" s="26" t="n">
-        <v>0.4662015079014227</v>
+        <v>0.4631199146331634</v>
       </c>
       <c r="K30" s="27" t="inlineStr">
         <is>
-          <t>Срвзв. потенциал: +26.1% · Покупать 14 / Держать 10 / без прогноза 2</t>
+          <t>Срвзв. потенциал: +27.4% · Покупать 14 / Держать 10 / без прогноза 2</t>
         </is>
       </c>
       <c r="L30" s="28" t="n"/>
@@ -3021,15 +3021,15 @@
         <v>341.3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>939.65</v>
+        <v>944.24</v>
       </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="9" t="n">
-        <v>320702.54</v>
+        <v>322269.11</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.4344818660532686</v>
+        <v>0.4356079053043894</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -3084,15 +3084,15 @@
         <v>146.3</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>1730.26</v>
+        <v>1731.01</v>
       </c>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="9" t="n">
-        <v>253137.04</v>
+        <v>253246.76</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.3429453770662399</v>
+        <v>0.3423110910280028</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>124452.7</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.16860621475392</v>
+        <v>0.1682214592533413</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -3210,15 +3210,15 @@
         <v>239</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>166.67</v>
+        <v>166.72</v>
       </c>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="9" t="n">
-        <v>39834.13</v>
+        <v>39846.08</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.05396654212657151</v>
+        <v>0.05385954441426646</v>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
@@ -3264,10 +3264,10 @@
       <c r="G35" s="24" t="n"/>
       <c r="H35" s="24" t="n"/>
       <c r="I35" s="25" t="n">
-        <v>738126.41</v>
+        <v>739814.65</v>
       </c>
       <c r="J35" s="26" t="n">
-        <v>0.4999334619888404</v>
+        <v>0.5028923589194456</v>
       </c>
       <c r="K35" s="28" t="n"/>
       <c r="L35" s="28" t="n"/>
@@ -3306,7 +3306,7 @@
         <v>50000</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.03386503010973692</v>
+        <v>0.03398772644739095</v>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>50000</v>
       </c>
       <c r="J37" s="26" t="n">
-        <v>0.03386503010973692</v>
+        <v>0.03398772644739095</v>
       </c>
       <c r="K37" s="28" t="n"/>
       <c r="L37" s="28" t="n"/>
@@ -3381,7 +3381,7 @@
       <c r="G38" s="24" t="n"/>
       <c r="H38" s="24" t="n"/>
       <c r="I38" s="30" t="n">
-        <v>1476449.3</v>
+        <v>1471119.29</v>
       </c>
       <c r="J38" s="31" t="n">
         <v>1</v>
@@ -3473,12 +3473,12 @@
       <c r="G40" s="24" t="n"/>
       <c r="H40" s="24" t="n"/>
       <c r="I40" s="30" t="n">
-        <v>2081449.3</v>
+        <v>2076119.29</v>
       </c>
       <c r="J40" s="31" t="n"/>
       <c r="K40" s="34" t="inlineStr">
         <is>
-          <t>ваш 1 476 449 ₽ + жены 605 000 ₽</t>
+          <t>ваш 1 471 119 ₽ + жены 605 000 ₽</t>
         </is>
       </c>
       <c r="L40" s="32" t="n"/>
@@ -3590,11 +3590,11 @@
       <c r="G43" s="32" t="n"/>
       <c r="H43" s="32" t="n"/>
       <c r="I43" s="30" t="n">
-        <v>1496834.13</v>
+        <v>1491504.12</v>
       </c>
       <c r="J43" s="34" t="inlineStr">
         <is>
-          <t>ликвидная часть: 1 476 449 ₽ + заблокировано 20 385 ₽</t>
+          <t>ликвидная часть: 1 471 119 ₽ + заблокировано 20 385 ₽</t>
         </is>
       </c>
       <c r="K43" s="32" t="n"/>
@@ -3629,7 +3629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3647,7 +3647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Учёт ежедневных остатков — Акции, Фонды, Счета, Сэйв жены (обновлено: 2026-10-28)</t>
+          <t>Учёт ежедневных остатков — Акции, Фонды, Счета, Сэйв жены (обновлено: 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -5391,6 +5391,42 @@
         <v>2081449.3</v>
       </c>
       <c r="J58" s="43" t="inlineStr">
+        <is>
+          <t>автообновление GitHub Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>29.10.2026</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>681304.64</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>739814.65</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F59" s="38" t="n">
+        <v>1471119.29</v>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>1491504.12</v>
+      </c>
+      <c r="I59" s="38" t="n">
+        <v>2076119.29</v>
+      </c>
+      <c r="J59" s="39" t="inlineStr">
         <is>
           <t>автообновление GitHub Actions</t>
         </is>
@@ -5422,7 +5458,7 @@
     <row r="1">
       <c r="B1" s="44" t="inlineStr">
         <is>
-          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 28.10.2026 (АВТООБНОВЛЕНИЕ)</t>
+          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 29.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5472,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="45" t="inlineStr">
         <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +26.1% (без учёта дивидендов).</t>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +27.4% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5493,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="45" t="inlineStr">
         <is>
-          <t>• Дивиденды за 12 месяцев (факт): ≈ 63 284 ₽ — 4.29% годовых на портфель.</t>
+          <t>• Дивиденды за 12 месяцев (факт): ≈ 63 284 ₽ — 4.3% годовых на портфель.</t>
         </is>
       </c>
     </row>
@@ -5485,28 +5521,28 @@
     <row r="13" ht="45" customHeight="1">
       <c r="B13" s="45" t="inlineStr">
         <is>
-          <t>• ОПИФ «Флагманский»: пай 939.65 ₽ (27.10.2026); 1 мес +7.15%  1 год +10.94%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
+          <t>• ОПИФ «Флагманский»: пай 944.24 ₽ (28.10.2026); 1 мес +8.08%  1 год +10.65%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="B14" s="45" t="inlineStr">
         <is>
-          <t>• ОПИФ «Рублевые перспективы»: пай 1 730.26 ₽ (27.10.2026); 1 мес +1.08%  1 год +16.88%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+          <t>• ОПИФ «Рублевые перспективы»: пай 1 731.01 ₽ (28.10.2026); 1 мес +1.07%  1 год +16.56%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="B15" s="45" t="inlineStr">
         <is>
-          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.59 ₽ (27.10.2026); 1 мес +1.18%  1 год +15.4%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.59 ₽ (28.10.2026); 1 мес +1.11%  1 год +15.35%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="105" customHeight="1">
       <c r="B16" s="45" t="inlineStr">
         <is>
-          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.67 ₽ (27.10.2026); 1 мес +1.13%  1 год +14.58%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → 27.10.2026 продано ещё 175 паев → 28.10.2026 продано 375 паев → позиция 239 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.72 ₽ (28.10.2026); 1 мес +1.05%  1 год +14.57%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → 27.10.2026 продано ещё 175 паев → 28.10.2026 продано 375 паев → позиция 239 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5563,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="45" t="inlineStr">
         <is>
-          <t>• Семейный итог (ликвидный): 2 081 449 ₽ = ваш 1 476 449 ₽ + 605 000 ₽.</t>
+          <t>• Семейный итог (ликвидный): 2 076 119 ₽ = ваш 1 471 119 ₽ + 605 000 ₽.</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="45" t="inlineStr">
         <is>
-          <t>• Итого с учётом заблокированных: 1 496 834 ₽ (ликвидная часть 1 476 449 ₽).</t>
+          <t>• Итого с учётом заблокированных: 1 491 504 ₽ (ликвидная часть 1 471 119 ₽).</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5598,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="45" t="inlineStr">
         <is>
-          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (28.10.2026, закрытие 27.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
+          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (29.10.2026, закрытие 28.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>

--- a/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
+++ b/Портфель_и_прогнозы_ТБанк_08.10.2026.xlsx
@@ -52,15 +52,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
@@ -74,6 +70,10 @@
     <font>
       <b val="1"/>
       <color rgb="009C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -200,23 +200,23 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -394,12 +394,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$59</f>
+              <f>'Остатки по дням'!$A$5:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$B$5:$B$59</f>
+              <f>'Остатки по дням'!$B$5:$B$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -434,12 +434,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$59</f>
+              <f>'Остатки по дням'!$A$5:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$C$5:$C$59</f>
+              <f>'Остатки по дням'!$C$5:$C$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -474,12 +474,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$59</f>
+              <f>'Остатки по дням'!$A$5:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$D$5:$D$59</f>
+              <f>'Остатки по дням'!$D$5:$D$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -514,12 +514,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$59</f>
+              <f>'Остатки по дням'!$A$5:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$E$5:$E$59</f>
+              <f>'Остатки по дням'!$E$5:$E$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -554,12 +554,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$59</f>
+              <f>'Остатки по дням'!$A$5:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$F$5:$F$59</f>
+              <f>'Остатки по дням'!$F$5:$F$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -594,12 +594,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Остатки по дням'!$A$5:$A$59</f>
+              <f>'Остатки по дням'!$A$5:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Остатки по дням'!$I$5:$I$59</f>
+              <f>'Остатки по дням'!$I$5:$I$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -678,7 +678,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10800000" cy="5040000"/>
@@ -1015,14 +1015,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 29.10.2026 (автообновление)</t>
+          <t>Инвестиционный портфель — сводные прогнозы Т-Банка (Т-Инвестиции) и дивиденды на 30.10.2026 (автообновление)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (29.10.2026, закрытие 28.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
+          <t>Источники: сводный прогноз Т-Банка — на 08.10.2026; цены — MOEX ISS (30.10.2026, закрытие 29.10.2026); паи — investfunds.ru; дивиденды — tbank.ru + smart-lab.ru. * Доли: в строках акций — внутри акции-части, фондов — внутри фондов, в итогах и кэше — в портфеле.</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Текущая цена, ₽ (29.10.2026)</t>
+          <t>Текущая цена, ₽ (30.10.2026)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Цена за пред. торг. день, ₽ (28.10.2026)</t>
+          <t>Цена за пред. торг. день, ₽ (29.10.2026)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1146,19 +1146,19 @@
         <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
+        <v>296.25</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>295.08</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>297.98</v>
-      </c>
       <c r="H4" s="8" t="n">
-        <v>-0.0097</v>
+        <v>0.004</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>47212.8</v>
+        <v>47400</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.06929763460879997</v>
+        <v>0.06941182324680452</v>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>379.4</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>0.2858</v>
+        <v>0.2807</v>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="Q4" s="16" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
@@ -1219,19 +1219,19 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
+        <v>3474</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>3453</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>3553.5</v>
-      </c>
       <c r="H5" s="8" t="n">
-        <v>-0.0283</v>
+        <v>0.0061</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>41436</v>
+        <v>41688</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.06081860825136902</v>
+        <v>0.06104725923022757</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>5816.5</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>0.6845</v>
+        <v>0.6743000000000001</v>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="R5" s="15" t="inlineStr">
         <is>
@@ -1292,19 +1292,19 @@
         <v>160</v>
       </c>
       <c r="F6" s="7" t="n">
+        <v>277.12</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>275.94</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>277.58</v>
-      </c>
       <c r="H6" s="8" t="n">
-        <v>-0.0059</v>
+        <v>0.0043</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>44150.4</v>
+        <v>44339.2</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.06480272906992091</v>
+        <v>0.06492963530178722</v>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>411.93</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0.4928</v>
+        <v>0.4865</v>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
@@ -1361,19 +1361,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="7" t="n">
+        <v>2394.5</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>2359</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>2347.5</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>0.0049</v>
+      <c r="H7" s="8" t="n">
+        <v>0.015</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>47180</v>
+        <v>47890</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.06924949168113695</v>
+        <v>0.0701293716305795</v>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>2861.3</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>0.2129</v>
+        <v>0.1949</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>0.26</v>
+        <v>0.256</v>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         <v>270</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>114.81</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>116.8</v>
-      </c>
       <c r="H8" s="8" t="n">
-        <v>-0.017</v>
+        <v>0.0173</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>30998.7</v>
+        <v>31536</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.04549902962645316</v>
-      </c>
-      <c r="K8" s="19" t="inlineStr">
+        <v>0.04618082822597525</v>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1457,7 +1457,7 @@
         <v>140.49</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.2237</v>
+        <v>0.2028</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1501,19 +1501,19 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
+        <v>6289</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <v>6243.5</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>6291.5</v>
-      </c>
       <c r="H9" s="8" t="n">
-        <v>-0.0076</v>
+        <v>0.0073</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>24974</v>
+        <v>25156</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.03665614254439835</v>
+        <v>0.03683805539233363</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1523,8 +1523,8 @@
       <c r="L9" s="7" t="n">
         <v>6221.5</v>
       </c>
-      <c r="M9" s="20" t="n">
-        <v>-0.0035</v>
+      <c r="M9" s="19" t="n">
+        <v>-0.0107</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>0.108</v>
+        <v>0.107</v>
       </c>
       <c r="R9" s="15" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         <v>170</v>
       </c>
       <c r="F10" s="7" t="n">
+        <v>165.64</v>
+      </c>
+      <c r="G10" s="7" t="n">
         <v>165.79</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>161.86</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>0.0243</v>
+      <c r="H10" s="20" t="n">
+        <v>-0.0009</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>28184.3</v>
+        <v>28158.8</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.04136813158941644</v>
-      </c>
-      <c r="K10" s="19" t="inlineStr">
+        <v>0.04123530903886326</v>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1597,7 +1597,7 @@
         <v>197.57</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>0.1917</v>
+        <v>0.1928</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1647,19 +1647,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="7" t="n">
+        <v>1066.2</v>
+      </c>
+      <c r="G11" s="7" t="n">
         <v>1061</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>1077.8</v>
-      </c>
       <c r="H11" s="8" t="n">
-        <v>-0.0156</v>
+        <v>0.0049</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>30769</v>
+        <v>30919.8</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.04516188235559353</v>
+        <v>0.04527847452376679</v>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>1500</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.4138</v>
+        <v>0.4069</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>0.192</v>
+        <v>0.191</v>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
@@ -1720,19 +1720,19 @@
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
+        <v>3804</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>3835</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>3774</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>0.0162</v>
+      <c r="H12" s="20" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>23010</v>
+        <v>22824</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.03377343797335653</v>
+        <v>0.03342311083934739</v>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>5458.75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.4234000000000001</v>
+        <v>0.435</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1796,16 +1796,16 @@
         <v>114.32</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>115.1</v>
+        <v>114.32</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>-0.0068</v>
+        <v>0</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>20577.6</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.03020322891093183</v>
+        <v>0.03013351759585326</v>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1862,19 +1862,19 @@
         <v>12000</v>
       </c>
       <c r="F14" s="7" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="G14" s="7" t="n">
         <v>1.7665</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>1.798</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>-0.0175</v>
+      <c r="H14" s="20" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>21198</v>
+        <v>20700</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03111383477441164</v>
+        <v>0.03031275825335134</v>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>2.06</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1661</v>
+        <v>0.1942</v>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>0.106</v>
+        <v>0.108</v>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         <v>35</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>564.85</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>569.35</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>577.3</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>-0.0138</v>
+      <c r="H15" s="20" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>19927.25</v>
+        <v>19769.75</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.02924866327051582</v>
-      </c>
-      <c r="K15" s="19" t="inlineStr">
+        <v>0.02895051461252138</v>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -1957,8 +1957,8 @@
       <c r="L15" s="7" t="n">
         <v>563.15</v>
       </c>
-      <c r="M15" s="20" t="n">
-        <v>-0.0109</v>
+      <c r="M15" s="19" t="n">
+        <v>-0.003</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="R15" s="15" t="inlineStr">
         <is>
@@ -2004,21 +2004,21 @@
         <v>4</v>
       </c>
       <c r="F16" s="7" t="n">
+        <v>5415</v>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>5486</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>5590</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>-0.0186</v>
+      <c r="H16" s="20" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>21944</v>
+        <v>21660</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.03220879282430837</v>
-      </c>
-      <c r="K16" s="19" t="inlineStr">
+        <v>0.03171856733176763</v>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2027,7 +2027,7 @@
         <v>6186.37</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.1277</v>
+        <v>0.1425</v>
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         <v>39</v>
       </c>
       <c r="F17" s="7" t="n">
+        <v>800</v>
+      </c>
+      <c r="G17" s="7" t="n">
         <v>803.5</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>808</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>-0.005600000000000001</v>
+      <c r="H17" s="20" t="n">
+        <v>-0.0044</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>31336.5</v>
+        <v>31200</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.04599484307049487</v>
-      </c>
-      <c r="K17" s="19" t="inlineStr">
+        <v>0.04568879504852955</v>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2098,7 +2098,7 @@
         <v>933</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1612</v>
+        <v>0.1662</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="Q17" s="16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
@@ -2148,19 +2148,19 @@
         <v>120</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>176.8</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>177.7</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>179.1</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>-0.007800000000000001</v>
+      <c r="H18" s="20" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>21324</v>
+        <v>21216</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.0312987740697025</v>
+        <v>0.0310683806330001</v>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>242.55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3649</v>
+        <v>0.3719</v>
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>0.197</v>
+        <v>0.198</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -2221,19 +2221,19 @@
         <v>314</v>
       </c>
       <c r="F19" s="7" t="n">
+        <v>72.20999999999999</v>
+      </c>
+      <c r="G19" s="7" t="n">
         <v>71.22</v>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>71.36</v>
-      </c>
       <c r="H19" s="8" t="n">
-        <v>-0.002</v>
+        <v>0.0139</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>22363.08</v>
+        <v>22673.94</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.03282390679153455</v>
+        <v>0.03320336530777744</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.1233</v>
+        <v>0.1079</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -2288,19 +2288,19 @@
         <v>30000</v>
       </c>
       <c r="F20" s="21" t="n">
+        <v>0.6854</v>
+      </c>
+      <c r="G20" s="21" t="n">
         <v>0.6734</v>
       </c>
-      <c r="G20" s="21" t="n">
-        <v>0.6982</v>
-      </c>
       <c r="H20" s="8" t="n">
-        <v>-0.0355</v>
+        <v>0.0178</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>20202</v>
+        <v>20562</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.02965193367830285</v>
+        <v>0.030110673198329</v>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>0.7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.0395</v>
+        <v>0.0213</v>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="Q20" s="16" t="n">
-        <v>0.091</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="R20" s="15" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         <v>400</v>
       </c>
       <c r="F21" s="7" t="n">
+        <v>74.98</v>
+      </c>
+      <c r="G21" s="7" t="n">
         <v>74.48</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>75.56</v>
-      </c>
       <c r="H21" s="8" t="n">
-        <v>-0.0143</v>
+        <v>0.0067</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>29792</v>
+        <v>29992</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.04372786893099686</v>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
+        <v>0.04391981862485572</v>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2384,7 +2384,7 @@
         <v>88.28</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1853</v>
+        <v>0.1774</v>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
@@ -2428,19 +2428,19 @@
         <v>470000</v>
       </c>
       <c r="F22" s="21" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="G22" s="21" t="n">
         <v>0.06496</v>
       </c>
-      <c r="G22" s="21" t="n">
-        <v>0.06451999999999999</v>
-      </c>
-      <c r="H22" s="18" t="n">
+      <c r="H22" s="8" t="n">
         <v>0.0068</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>30531.2</v>
+        <v>30738</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.04481284613003663</v>
+        <v>0.04501224942954171</v>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
@@ -2491,21 +2491,21 @@
         <v>19</v>
       </c>
       <c r="F23" s="7" t="n">
+        <v>1045.4</v>
+      </c>
+      <c r="G23" s="7" t="n">
         <v>1051.6</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>1098.4</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>-0.0426</v>
+      <c r="H23" s="20" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>19980.4</v>
+        <v>19862.6</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.0293266753621405</v>
-      </c>
-      <c r="K23" s="19" t="inlineStr">
+        <v>0.02908648270932446</v>
+      </c>
+      <c r="K23" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2514,7 +2514,7 @@
         <v>1341.8</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.276</v>
+        <v>0.2835</v>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -2564,21 +2564,21 @@
         <v>540</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>37.24</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>38.05</v>
-      </c>
       <c r="H24" s="8" t="n">
-        <v>-0.0213</v>
+        <v>0.0102</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>20109.6</v>
+        <v>20314.8</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.02951631152842288</v>
-      </c>
-      <c r="K24" s="19" t="inlineStr">
+        <v>0.0297486773606368</v>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2587,7 +2587,7 @@
         <v>42.92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.1525</v>
+        <v>0.1409</v>
       </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -2637,19 +2637,19 @@
         <v>463</v>
       </c>
       <c r="F25" s="7" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="G25" s="7" t="n">
         <v>57.735</v>
       </c>
-      <c r="G25" s="7" t="n">
-        <v>57.95</v>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>-0.0037</v>
+      <c r="H25" s="20" t="n">
+        <v>-0.0243</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>26731.31</v>
+        <v>26080.79</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.0392354732825539</v>
+        <v>0.0381923034940301</v>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>89.55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5511</v>
+        <v>0.5897</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>0.168</v>
+        <v>0.172</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -2710,19 +2710,19 @@
         <v>50</v>
       </c>
       <c r="F26" s="7" t="n">
+        <v>474.6</v>
+      </c>
+      <c r="G26" s="7" t="n">
         <v>472.1</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>487.8</v>
-      </c>
       <c r="H26" s="8" t="n">
-        <v>-0.0322</v>
+        <v>0.0053</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>23605</v>
+        <v>23730</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.03464676242334119</v>
+        <v>0.03474984315710276</v>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>0.123</v>
+        <v>0.122</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         <v>170</v>
       </c>
       <c r="F27" s="7" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="G27" s="7" t="n">
         <v>43.05</v>
       </c>
-      <c r="G27" s="7" t="n">
-        <v>43.25</v>
-      </c>
       <c r="H27" s="8" t="n">
-        <v>-0.0046</v>
+        <v>0.0023</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7318.5</v>
+        <v>7335.5</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.01074189073481138</v>
-      </c>
-      <c r="K27" s="19" t="inlineStr">
+        <v>0.01074199218200284</v>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2801,8 +2801,8 @@
       <c r="L27" s="7" t="n">
         <v>42.5</v>
       </c>
-      <c r="M27" s="20" t="n">
-        <v>-0.0128</v>
+      <c r="M27" s="19" t="n">
+        <v>-0.0151</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         <v>340</v>
       </c>
       <c r="F28" s="7" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="G28" s="7" t="n">
         <v>43.6</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>0.0023</v>
+      <c r="H28" s="20" t="n">
+        <v>-0.0011</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>14824</v>
+        <v>14807</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.02175825486818936</v>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
+        <v>0.02168314065011465</v>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
         <is>
           <t>Держать</t>
         </is>
@@ -2869,7 +2869,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.1468</v>
+        <v>0.1481</v>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
@@ -2913,19 +2913,19 @@
         <v>10</v>
       </c>
       <c r="F29" s="7" t="n">
+        <v>1174.9</v>
+      </c>
+      <c r="G29" s="7" t="n">
         <v>1162.5</v>
       </c>
-      <c r="G29" s="7" t="n">
-        <v>1197.8</v>
-      </c>
       <c r="H29" s="8" t="n">
-        <v>-0.0295</v>
+        <v>0.0107</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>11625</v>
+        <v>11749</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.01706285164886005</v>
+        <v>0.01720505298157608</v>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>1437.8</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.2368</v>
+        <v>0.2238</v>
       </c>
       <c r="N29" s="13" t="inlineStr">
         <is>
@@ -2979,14 +2979,14 @@
       <c r="G30" s="24" t="n"/>
       <c r="H30" s="24" t="n"/>
       <c r="I30" s="25" t="n">
-        <v>681304.64</v>
+        <v>682880.78</v>
       </c>
       <c r="J30" s="26" t="n">
-        <v>0.4631199146331634</v>
+        <v>0.4645763805781851</v>
       </c>
       <c r="K30" s="27" t="inlineStr">
         <is>
-          <t>Срвзв. потенциал: +27.4% · Покупать 14 / Держать 10 / без прогноза 2</t>
+          <t>Срвзв. потенциал: +27.2% · Покупать 14 / Держать 10 / без прогноза 2</t>
         </is>
       </c>
       <c r="L30" s="28" t="n"/>
@@ -3021,15 +3021,15 @@
         <v>341.3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>944.24</v>
+        <v>935.2</v>
       </c>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="9" t="n">
-        <v>322269.11</v>
+        <v>319183.76</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.4356079053043894</v>
+        <v>0.433073914919956</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -3084,15 +3084,15 @@
         <v>146.3</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>1731.01</v>
+        <v>1732.31</v>
       </c>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="9" t="n">
-        <v>253246.76</v>
+        <v>253436.95</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.3423110910280028</v>
+        <v>0.3438675329906294</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -3147,15 +3147,15 @@
         <v>8530</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>14.59</v>
+        <v>14.6</v>
       </c>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="9" t="n">
-        <v>124452.7</v>
+        <v>124538</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.1682214592533413</v>
+        <v>0.1689752611984441</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -3210,15 +3210,15 @@
         <v>239</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>166.72</v>
+        <v>166.78</v>
       </c>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="9" t="n">
-        <v>39846.08</v>
+        <v>39860.42</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.05385954441426646</v>
+        <v>0.05408329089097049</v>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
@@ -3264,10 +3264,10 @@
       <c r="G35" s="24" t="n"/>
       <c r="H35" s="24" t="n"/>
       <c r="I35" s="25" t="n">
-        <v>739814.65</v>
+        <v>737019.13</v>
       </c>
       <c r="J35" s="26" t="n">
-        <v>0.5028923589194456</v>
+        <v>0.501407697888763</v>
       </c>
       <c r="K35" s="28" t="n"/>
       <c r="L35" s="28" t="n"/>
@@ -3306,7 +3306,7 @@
         <v>50000</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.03398772644739095</v>
+        <v>0.03401592153305187</v>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>50000</v>
       </c>
       <c r="J37" s="26" t="n">
-        <v>0.03398772644739095</v>
+        <v>0.03401592153305187</v>
       </c>
       <c r="K37" s="28" t="n"/>
       <c r="L37" s="28" t="n"/>
@@ -3381,7 +3381,7 @@
       <c r="G38" s="24" t="n"/>
       <c r="H38" s="24" t="n"/>
       <c r="I38" s="30" t="n">
-        <v>1471119.29</v>
+        <v>1469899.91</v>
       </c>
       <c r="J38" s="31" t="n">
         <v>1</v>
@@ -3473,12 +3473,12 @@
       <c r="G40" s="24" t="n"/>
       <c r="H40" s="24" t="n"/>
       <c r="I40" s="30" t="n">
-        <v>2076119.29</v>
+        <v>2074899.91</v>
       </c>
       <c r="J40" s="31" t="n"/>
       <c r="K40" s="34" t="inlineStr">
         <is>
-          <t>ваш 1 471 119 ₽ + жены 605 000 ₽</t>
+          <t>ваш 1 469 900 ₽ + жены 605 000 ₽</t>
         </is>
       </c>
       <c r="L40" s="32" t="n"/>
@@ -3590,11 +3590,11 @@
       <c r="G43" s="32" t="n"/>
       <c r="H43" s="32" t="n"/>
       <c r="I43" s="30" t="n">
-        <v>1491504.12</v>
+        <v>1490284.74</v>
       </c>
       <c r="J43" s="34" t="inlineStr">
         <is>
-          <t>ликвидная часть: 1 471 119 ₽ + заблокировано 20 385 ₽</t>
+          <t>ликвидная часть: 1 469 900 ₽ + заблокировано 20 385 ₽</t>
         </is>
       </c>
       <c r="K43" s="32" t="n"/>
@@ -3629,7 +3629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3647,7 +3647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Учёт ежедневных остатков — Акции, Фонды, Счета, Сэйв жены (обновлено: 2026-10-29)</t>
+          <t>Учёт ежедневных остатков — Акции, Фонды, Счета, Сэйв жены (обновлено: 2026-10-30)</t>
         </is>
       </c>
     </row>
@@ -5427,6 +5427,42 @@
         <v>2076119.29</v>
       </c>
       <c r="J59" s="39" t="inlineStr">
+        <is>
+          <t>автообновление GitHub Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="40" t="inlineStr">
+        <is>
+          <t>30.10.2026</t>
+        </is>
+      </c>
+      <c r="B60" s="41" t="n">
+        <v>605000</v>
+      </c>
+      <c r="C60" s="41" t="n">
+        <v>682880.78</v>
+      </c>
+      <c r="D60" s="41" t="n">
+        <v>737019.13</v>
+      </c>
+      <c r="E60" s="41" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F60" s="42" t="n">
+        <v>1469899.91</v>
+      </c>
+      <c r="G60" s="41" t="n">
+        <v>20384.83</v>
+      </c>
+      <c r="H60" s="41" t="n">
+        <v>1490284.74</v>
+      </c>
+      <c r="I60" s="42" t="n">
+        <v>2074899.91</v>
+      </c>
+      <c r="J60" s="43" t="inlineStr">
         <is>
           <t>автообновление GitHub Actions</t>
         </is>
@@ -5458,7 +5494,7 @@
     <row r="1">
       <c r="B1" s="44" t="inlineStr">
         <is>
-          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 29.10.2026 (АВТООБНОВЛЕНИЕ)</t>
+          <t>СВОДКА: ПРОГНОЗЫ Т-БАНКА (08.10.2026), ЦЕНЫ И СОСТАВ НА 30.10.2026 (АВТООБНОВЛЕНИЕ)</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5508,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="45" t="inlineStr">
         <is>
-          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +27.4% (без учёта дивидендов).</t>
+          <t>• Средневзвешенный потенциал роста акций к целевым ценам: +27.2% (без учёта дивидендов).</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5529,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="45" t="inlineStr">
         <is>
-          <t>• Дивиденды за 12 месяцев (факт): ≈ 63 284 ₽ — 4.3% годовых на портфель.</t>
+          <t>• Дивиденды за 12 месяцев (факт): ≈ 63 284 ₽ — 4.31% годовых на портфель.</t>
         </is>
       </c>
     </row>
@@ -5521,28 +5557,28 @@
     <row r="13" ht="45" customHeight="1">
       <c r="B13" s="45" t="inlineStr">
         <is>
-          <t>• ОПИФ «Флагманский»: пай 944.24 ₽ (28.10.2026); 1 мес +8.08%  1 год +10.65%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
+          <t>• ОПИФ «Флагманский»: пай 935.20 ₽ (29.10.2026); 1 мес +7.2%  1 год +8.94%. Целевых цен аналитиков на фонды нет. Перспектива = рынок акций и облигаций: Т-Инвестиции ждут IMOEX 2300–2500 п. к концу 2026 и 2600–2900 п. за 12 мес. Выплат нет — доход реинвестируется в пай.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="B14" s="45" t="inlineStr">
         <is>
-          <t>• ОПИФ «Рублевые перспективы»: пай 1 731.01 ₽ (28.10.2026); 1 мес +1.07%  1 год +16.56%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
+          <t>• ОПИФ «Рублевые перспективы»: пай 1 732.31 ₽ (29.10.2026); 1 мес +1.22%  1 год +16.37%. Цель УК — «ключевая ставка +1–2%» ≈ 15–16% годовых при ставке 14%. При снижении ставки ЦБ — дополнительный рост за счёт переоценки облигаций. Выплат нет.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="B15" s="45" t="inlineStr">
         <is>
-          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.59 ₽ (28.10.2026); 1 мес +1.11%  1 год +15.35%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
+          <t>• БПИФ «БКС Денежный рынок» (BCSD): пай 14.60 ₽ (29.10.2026); 1 мес +1.11%  1 год +15.39%. Доходность ≈ ключевая ставка минус комиссии (~13 5–14 5% годовых сейчас); при снижении ставки ЦБ будет постепенно падать. Просадок нет — «парковочный» актив.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="105" customHeight="1">
       <c r="B16" s="45" t="inlineStr">
         <is>
-          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.72 ₽ (28.10.2026); 1 мес +1.05%  1 год +14.57%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → 27.10.2026 продано ещё 175 паев → 28.10.2026 продано 375 паев → позиция 239 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
+          <t>• БПИФ «Т-Капитал Денежный рынок» (TMON): пай 166.78 ₽ (29.10.2026); 1 мес +1.05%  1 год +14.56%. Доходность ≈ ставка денежного рынка ON минус расходы (~13 5% годовых); за 1 год +14 7%. Дивиденды и купоны реинвестируются. Первые 2 пая куплены по 161 06 ₽; 08.10.2026 докуплено 180 паев по ~165 57 ₽; 12.10.2026 докуплено 220 паев по ~165 84 ₽ (новые средства) → 13.10.2026 продано 200 паев → 14.10.2026 продано 43 пая → 17.10.2026 переведено 130 000 ₽ с «Сэйва» и куплено 780 паев по ~165.96 ₽ → 21.10.2026 продано 150 паев → 27.10.2026 продано ещё 175 паев → 28.10.2026 продано 375 паев → позиция 239 паев. Аналог BCSD: при снижении ставки ЦБ доходность падает.</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5599,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="45" t="inlineStr">
         <is>
-          <t>• Семейный итог (ликвидный): 2 076 119 ₽ = ваш 1 471 119 ₽ + 605 000 ₽.</t>
+          <t>• Семейный итог (ликвидный): 2 074 900 ₽ = ваш 1 469 900 ₽ + 605 000 ₽.</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5620,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="45" t="inlineStr">
         <is>
-          <t>• Итого с учётом заблокированных: 1 491 504 ₽ (ликвидная часть 1 471 119 ₽).</t>
+          <t>• Итого с учётом заблокированных: 1 490 285 ₽ (ликвидная часть 1 469 900 ₽).</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5634,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="45" t="inlineStr">
         <is>
-          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (29.10.2026, закрытие 28.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
+          <t>• tbank.ru/invest (08.10.2026); MOEX ISS (30.10.2026, закрытие 29.10.2026); investfunds.ru; smart-lab.ru/dividends; cbr.ru. Состав и количества обновляются вручную.</t>
         </is>
       </c>
     </row>
